--- a/research/traditional_assets/database/data/netherlands/netherlands_food_processing.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_food_processing.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,40 +593,40 @@
         <v>0.096</v>
       </c>
       <c r="G2">
-        <v>0.1230156529070477</v>
+        <v>0.1226887763003607</v>
       </c>
       <c r="H2">
-        <v>0.1230156529070477</v>
+        <v>0.1226887763003607</v>
       </c>
       <c r="I2">
-        <v>0.124372573020639</v>
+        <v>0.1225615262483624</v>
       </c>
       <c r="J2">
-        <v>0.08478254947734948</v>
+        <v>0.1030547588324106</v>
       </c>
       <c r="K2">
-        <v>570</v>
+        <v>549.6</v>
       </c>
       <c r="L2">
-        <v>0.0632328633393608</v>
+        <v>0.06079780526117835</v>
       </c>
       <c r="M2">
         <v>369.61</v>
       </c>
       <c r="N2">
-        <v>0.04426944221532859</v>
+        <v>0.04399961906122399</v>
       </c>
       <c r="O2">
-        <v>0.648438596491228</v>
+        <v>0.6725072780203784</v>
       </c>
       <c r="P2">
         <v>366.4</v>
       </c>
       <c r="Q2">
-        <v>0.04388496963744595</v>
+        <v>0.04361748985155291</v>
       </c>
       <c r="R2">
-        <v>0.6428070175438596</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S2">
         <v>3.20999999999998</v>
@@ -635,73 +635,73 @@
         <v>0.008684829955899408</v>
       </c>
       <c r="U2">
-        <v>1291.1</v>
+        <v>1304.7</v>
       </c>
       <c r="V2">
-        <v>0.1546394222131727</v>
+        <v>0.155315881575658</v>
       </c>
       <c r="W2">
-        <v>0.04834892656900749</v>
+        <v>-0.08433617501336858</v>
       </c>
       <c r="X2">
-        <v>0.08764946130387148</v>
+        <v>0.102418271854776</v>
       </c>
       <c r="Y2">
-        <v>-0.03930053473486399</v>
+        <v>-0.1867544468681446</v>
       </c>
       <c r="Z2">
-        <v>0.5515545767137298</v>
+        <v>0.5476614902647517</v>
       </c>
       <c r="AA2">
-        <v>0.04676220318969035</v>
+        <v>-0.01717438568547926</v>
       </c>
       <c r="AB2">
-        <v>0.06887636918231013</v>
+        <v>0.06662497235632198</v>
       </c>
       <c r="AC2">
-        <v>-0.02211416599261978</v>
+        <v>-0.08379935804180123</v>
       </c>
       <c r="AD2">
-        <v>6391.3</v>
+        <v>6507.1</v>
       </c>
       <c r="AE2">
         <v>4.941575100267599</v>
       </c>
       <c r="AF2">
-        <v>6396.241575100268</v>
+        <v>6512.041575100268</v>
       </c>
       <c r="AG2">
-        <v>5105.141575100268</v>
+        <v>5207.341575100269</v>
       </c>
       <c r="AH2">
-        <v>0.4337804955228223</v>
+        <v>0.4366880641986959</v>
       </c>
       <c r="AI2">
-        <v>0.3526754030637464</v>
+        <v>0.3553474774085314</v>
       </c>
       <c r="AJ2">
-        <v>0.3794447681501676</v>
+        <v>0.3826777437045991</v>
       </c>
       <c r="AK2">
-        <v>0.303061345385893</v>
+        <v>0.3059337443452051</v>
       </c>
       <c r="AL2">
-        <v>132.9</v>
+        <v>138.08</v>
       </c>
       <c r="AM2">
-        <v>36.5</v>
+        <v>41.68000000000001</v>
       </c>
       <c r="AN2">
-        <v>4.440499680404636</v>
+        <v>4.528001224705654</v>
       </c>
       <c r="AO2">
-        <v>8.418359668924003</v>
+        <v>8.006952491309384</v>
       </c>
       <c r="AP2">
-        <v>3.546912135661471</v>
+        <v>3.62355719591134</v>
       </c>
       <c r="AQ2">
-        <v>30.65205479452055</v>
+        <v>26.52591170825335</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +775,10 @@
         <v>0.04834892656900749</v>
       </c>
       <c r="X3">
-        <v>0.08764946130387148</v>
+        <v>0.08762255582111092</v>
       </c>
       <c r="Y3">
-        <v>-0.03930053473486399</v>
+        <v>-0.03927362925210343</v>
       </c>
       <c r="Z3">
         <v>0.5515545767137298</v>
@@ -787,10 +787,10 @@
         <v>0.04676220318969035</v>
       </c>
       <c r="AB3">
-        <v>0.06887636918231013</v>
+        <v>0.06886113477319372</v>
       </c>
       <c r="AC3">
-        <v>-0.02211416599261978</v>
+        <v>-0.02209893158350337</v>
       </c>
       <c r="AD3">
         <v>6391.3</v>
@@ -833,6 +833,131 @@
       </c>
       <c r="AQ3">
         <v>30.65205479452055</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Kingfish Company N.V. (OB:KING)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Food Processing</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.007137254901960784</v>
+      </c>
+      <c r="H4">
+        <v>0.007137254901960784</v>
+      </c>
+      <c r="I4">
+        <v>-0.5176470588235293</v>
+      </c>
+      <c r="J4">
+        <v>-0.5176470588235293</v>
+      </c>
+      <c r="K4">
+        <v>-20.4</v>
+      </c>
+      <c r="L4">
+        <v>-0.7999999999999999</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>13.6</v>
+      </c>
+      <c r="V4">
+        <v>0.265625</v>
+      </c>
+      <c r="W4">
+        <v>-0.2170212765957447</v>
+      </c>
+      <c r="X4">
+        <v>0.1172139878884411</v>
+      </c>
+      <c r="Y4">
+        <v>-0.3342352644841858</v>
+      </c>
+      <c r="Z4">
+        <v>0.1566916554012535</v>
+      </c>
+      <c r="AA4">
+        <v>-0.08111097456064888</v>
+      </c>
+      <c r="AB4">
+        <v>0.06438880993945022</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1454997845000991</v>
+      </c>
+      <c r="AD4">
+        <v>115.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>115.8</v>
+      </c>
+      <c r="AG4">
+        <v>102.2</v>
+      </c>
+      <c r="AH4">
+        <v>0.6934131736526946</v>
+      </c>
+      <c r="AI4">
+        <v>0.6110817941952507</v>
+      </c>
+      <c r="AJ4">
+        <v>0.666232073011734</v>
+      </c>
+      <c r="AK4">
+        <v>0.5810119386014782</v>
+      </c>
+      <c r="AL4">
+        <v>5.18</v>
+      </c>
+      <c r="AM4">
+        <v>5.18</v>
+      </c>
+      <c r="AN4">
+        <v>-51.69642857142856</v>
+      </c>
+      <c r="AO4">
+        <v>-2.548262548262548</v>
+      </c>
+      <c r="AP4">
+        <v>-45.625</v>
+      </c>
+      <c r="AQ4">
+        <v>-2.548262548262548</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1252,49 @@
         <v>8.44334085778781</v>
       </c>
       <c r="F2">
-        <v>3.05659181857414</v>
+        <v>3.05806576279045</v>
       </c>
       <c r="G2">
         <v>4.44393295104651</v>
       </c>
       <c r="H2">
-        <v>4.40520306623483</v>
+        <v>4.61009623210622</v>
       </c>
       <c r="I2">
         <v>0.433780495522822</v>
       </c>
       <c r="J2">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="K2">
         <v>8349.1</v>
       </c>
       <c r="L2">
-        <v>8748.525043579801</v>
+        <v>9138.16855774931</v>
       </c>
       <c r="M2">
         <v>13454.2415751003</v>
       </c>
       <c r="N2">
-        <v>13797.9219208729</v>
+        <v>14482.4722665444</v>
       </c>
       <c r="O2">
         <v>6396.24157510027</v>
       </c>
       <c r="P2">
-        <v>6340.49687729312</v>
+        <v>6635.40370879512</v>
       </c>
       <c r="Q2">
-        <v>0.0688763691823101</v>
+        <v>0.06886113477319369</v>
       </c>
       <c r="R2">
-        <v>0.068301580124564</v>
+        <v>0.0672238337573924</v>
       </c>
       <c r="S2">
         <v>0.0443716</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1307,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0876494613038715</v>
+        <v>0.08762255582111091</v>
       </c>
       <c r="X2">
-        <v>0.0874175546044982</v>
+        <v>0.0886530250134407</v>
       </c>
       <c r="Y2">
         <v>0.965878887323578</v>
       </c>
       <c r="Z2">
-        <v>0.960526517716545</v>
+        <v>0.98967725204251</v>
       </c>
       <c r="AA2">
         <v>6391.3</v>
@@ -1224,7 +1349,7 @@
         <v>8349.1</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1537,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07248212058192244</v>
+        <v>0.07246496635070977</v>
       </c>
       <c r="C2">
-        <v>12927.17085507856</v>
+        <v>12926.96985836322</v>
       </c>
       <c r="D2">
-        <v>11636.07085507856</v>
+        <v>11635.86985836322</v>
       </c>
       <c r="E2">
         <v>-6396.241575100268</v>
@@ -1463,19 +1588,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07248212058192244</v>
+        <v>0.07246496635070977</v>
       </c>
       <c r="T2">
         <v>0.6158190843120042</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1619,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07233889471082108</v>
+        <v>0.07231139673752494</v>
       </c>
       <c r="C3">
-        <v>12842.51532155195</v>
+        <v>12846.91824912242</v>
       </c>
       <c r="D3">
-        <v>11698.86873730296</v>
+        <v>11703.27166487343</v>
       </c>
       <c r="E3">
         <v>-6248.788159349266</v>
@@ -1527,37 +1652,37 @@
         <v>1122.12</v>
       </c>
       <c r="M3">
-        <v>7.62334159432684</v>
+        <v>7.416906812275435</v>
       </c>
       <c r="N3">
-        <v>1114.496658405673</v>
+        <v>1114.703093187725</v>
       </c>
       <c r="O3">
-        <v>287.5401378686637</v>
+        <v>287.593398042433</v>
       </c>
       <c r="P3">
-        <v>826.9565205370094</v>
+        <v>827.1096951452917</v>
       </c>
       <c r="Q3">
-        <v>1144.156520537009</v>
+        <v>1144.309695145292</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07268210172810211</v>
+        <v>0.07266481892679287</v>
       </c>
       <c r="T3">
         <v>0.6204346172469486</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>147.1952930503682</v>
+        <v>151.2921799344738</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1701,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07219566883971971</v>
+        <v>0.07215782712434012</v>
       </c>
       <c r="C4">
-        <v>12758.5412847845</v>
+        <v>12767.65205131216</v>
       </c>
       <c r="D4">
-        <v>11762.3481162865</v>
+        <v>11771.45888281416</v>
       </c>
       <c r="E4">
         <v>-6101.334743598263</v>
@@ -1609,37 +1734,37 @@
         <v>1122.12</v>
       </c>
       <c r="M4">
-        <v>15.24668318865368</v>
+        <v>14.83381362455087</v>
       </c>
       <c r="N4">
-        <v>1106.873316811346</v>
+        <v>1107.286186375449</v>
       </c>
       <c r="O4">
-        <v>285.5733157373273</v>
+        <v>285.6798360848658</v>
       </c>
       <c r="P4">
-        <v>821.300001074019</v>
+        <v>821.6063502905831</v>
       </c>
       <c r="Q4">
-        <v>1138.500001074019</v>
+        <v>1138.806350290583</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07288616412216298</v>
+        <v>0.07286875012687767</v>
       </c>
       <c r="T4">
         <v>0.625144344731586</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.59764652518408</v>
+        <v>75.64608996723692</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1783,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07205244296861835</v>
+        <v>0.07200425751115527</v>
       </c>
       <c r="C5">
-        <v>12675.25989893435</v>
+        <v>12689.18507360411</v>
       </c>
       <c r="D5">
-        <v>11826.52014618736</v>
+        <v>11840.44532085712</v>
       </c>
       <c r="E5">
         <v>-5953.88132784726</v>
@@ -1691,37 +1816,37 @@
         <v>1122.12</v>
       </c>
       <c r="M5">
-        <v>22.87002478298051</v>
+        <v>22.2507204368263</v>
       </c>
       <c r="N5">
-        <v>1099.249975217019</v>
+        <v>1099.869279563174</v>
       </c>
       <c r="O5">
-        <v>283.606493605991</v>
+        <v>283.7662741272988</v>
       </c>
       <c r="P5">
-        <v>815.6434816110284</v>
+        <v>816.1030054358748</v>
       </c>
       <c r="Q5">
-        <v>1132.843481611028</v>
+        <v>1133.303005435875</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07309443398826634</v>
+        <v>0.07307688609397452</v>
       </c>
       <c r="T5">
         <v>0.6299511799994115</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.06509768345606</v>
+        <v>50.43072664482462</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1865,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07190921709751701</v>
+        <v>0.07185068789797046</v>
       </c>
       <c r="C6">
-        <v>12592.68256291062</v>
+        <v>12611.53145028015</v>
       </c>
       <c r="D6">
-        <v>11891.39622591463</v>
+        <v>11910.24511328416</v>
       </c>
       <c r="E6">
         <v>-5806.427912096257</v>
@@ -1773,37 +1898,37 @@
         <v>1122.12</v>
       </c>
       <c r="M6">
-        <v>30.49336637730736</v>
+        <v>29.66762724910174</v>
       </c>
       <c r="N6">
-        <v>1091.626633622692</v>
+        <v>1092.452372750898</v>
       </c>
       <c r="O6">
-        <v>281.6396714746547</v>
+        <v>281.8527121697317</v>
       </c>
       <c r="P6">
-        <v>809.9869621480377</v>
+        <v>810.5996605811664</v>
       </c>
       <c r="Q6">
-        <v>1127.186962148038</v>
+        <v>1127.799660581166</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07330704280991354</v>
+        <v>0.07328935822705256</v>
       </c>
       <c r="T6">
         <v>0.6348581576686503</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.79882326259203</v>
+        <v>37.82304498361846</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1947,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07176599122641564</v>
+        <v>0.0716971182847856</v>
       </c>
       <c r="C7">
-        <v>12510.82092712354</v>
+        <v>12534.70565088669</v>
       </c>
       <c r="D7">
-        <v>11956.98800587855</v>
+        <v>11980.87272964171</v>
       </c>
       <c r="E7">
         <v>-5658.974496345255</v>
@@ -1855,37 +1980,37 @@
         <v>1122.12</v>
       </c>
       <c r="M7">
-        <v>38.1167079716342</v>
+        <v>37.08453406137718</v>
       </c>
       <c r="N7">
-        <v>1084.003292028366</v>
+        <v>1085.035465938623</v>
       </c>
       <c r="O7">
-        <v>279.6728493433183</v>
+        <v>279.9391502121647</v>
       </c>
       <c r="P7">
-        <v>804.3304426850473</v>
+        <v>805.0963157264581</v>
       </c>
       <c r="Q7">
-        <v>1121.530442685047</v>
+        <v>1122.296315726458</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07352412760675331</v>
+        <v>0.07350630345766906</v>
       </c>
       <c r="T7">
         <v>0.6398684401309256</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.43905861007363</v>
+        <v>30.25843598689477</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +2029,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07162276535531428</v>
+        <v>0.07154354867160079</v>
       </c>
       <c r="C8">
-        <v>12429.68690045911</v>
+        <v>12458.72249023449</v>
       </c>
       <c r="D8">
-        <v>12023.30739496513</v>
+        <v>12052.3429847405</v>
       </c>
       <c r="E8">
         <v>-5511.521080594252</v>
@@ -1937,37 +2062,37 @@
         <v>1122.12</v>
       </c>
       <c r="M8">
-        <v>45.74004956596103</v>
+        <v>44.50144087365261</v>
       </c>
       <c r="N8">
-        <v>1076.379950434039</v>
+        <v>1077.618559126347</v>
       </c>
       <c r="O8">
-        <v>277.706027211982</v>
+        <v>278.0255882545976</v>
       </c>
       <c r="P8">
-        <v>798.6739232220568</v>
+        <v>799.5929708717497</v>
       </c>
       <c r="Q8">
-        <v>1115.873923222057</v>
+        <v>1116.79297087175</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07374583122905776</v>
+        <v>0.07372786454425616</v>
       </c>
       <c r="T8">
         <v>0.6449853243477174</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.53254884172803</v>
+        <v>25.21536332241231</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +2111,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07147953948421293</v>
+        <v>0.07138997905841594</v>
       </c>
       <c r="C9">
-        <v>12349.29265748735</v>
+        <v>12383.59713875867</v>
       </c>
       <c r="D9">
-        <v>12090.36656774437</v>
+        <v>12124.67104901569</v>
       </c>
       <c r="E9">
         <v>-5364.067664843249</v>
@@ -2019,37 +2144,37 @@
         <v>1122.12</v>
       </c>
       <c r="M9">
-        <v>53.36339116028788</v>
+        <v>51.91834768592805</v>
       </c>
       <c r="N9">
-        <v>1068.756608839712</v>
+        <v>1070.201652314072</v>
       </c>
       <c r="O9">
-        <v>275.7392050806457</v>
+        <v>276.1120262970306</v>
       </c>
       <c r="P9">
-        <v>793.0174037590664</v>
+        <v>794.0896260170414</v>
       </c>
       <c r="Q9">
-        <v>1110.217403759066</v>
+        <v>1111.289626017041</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0739723026711967</v>
+        <v>0.0739541903853935</v>
       </c>
       <c r="T9">
         <v>0.6502122490853004</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.02789900719545</v>
+        <v>21.61316856206769</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2193,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07133631361311157</v>
+        <v>0.07123640944523113</v>
       </c>
       <c r="C10">
-        <v>12269.65064591298</v>
+        <v>12309.34513325386</v>
       </c>
       <c r="D10">
-        <v>12158.177971921</v>
+        <v>12197.87245926188</v>
       </c>
       <c r="E10">
         <v>-5216.614249092247</v>
@@ -2101,37 +2226,37 @@
         <v>1122.12</v>
       </c>
       <c r="M10">
-        <v>60.98673275461472</v>
+        <v>59.33525449820348</v>
       </c>
       <c r="N10">
-        <v>1061.133267245385</v>
+        <v>1062.784745501796</v>
       </c>
       <c r="O10">
-        <v>273.7723829493094</v>
+        <v>274.1984643394634</v>
       </c>
       <c r="P10">
-        <v>787.3608842960758</v>
+        <v>788.5862811623329</v>
       </c>
       <c r="Q10">
-        <v>1104.560884296076</v>
+        <v>1105.786281162333</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07420369740555605</v>
+        <v>0.07418543635351209</v>
       </c>
       <c r="T10">
         <v>0.6555528026215265</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.39941163129602</v>
+        <v>18.91152249180923</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2275,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07119308774201021</v>
+        <v>0.0710828398320463</v>
       </c>
       <c r="C11">
-        <v>12190.7735942783</v>
+        <v>12235.98238800073</v>
       </c>
       <c r="D11">
-        <v>12226.75433603733</v>
+        <v>12271.96312975975</v>
       </c>
       <c r="E11">
         <v>-5069.160833341244</v>
@@ -2183,37 +2308,37 @@
         <v>1122.12</v>
       </c>
       <c r="M11">
-        <v>68.61007434894155</v>
+        <v>66.75216131047891</v>
       </c>
       <c r="N11">
-        <v>1053.509925651058</v>
+        <v>1055.367838689521</v>
       </c>
       <c r="O11">
-        <v>271.8055608179731</v>
+        <v>272.2849023818964</v>
       </c>
       <c r="P11">
-        <v>781.7043648330854</v>
+        <v>783.0829363076245</v>
       </c>
       <c r="Q11">
-        <v>1098.904364833085</v>
+        <v>1100.282936307625</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07444017773847275</v>
+        <v>0.07442176465060032</v>
       </c>
       <c r="T11">
         <v>0.6610107309607466</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.35503256115202</v>
+        <v>16.81024221494154</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2357,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07104986187090885</v>
+        <v>0.07092927021886147</v>
       </c>
       <c r="C12">
-        <v>12112.67451992822</v>
+        <v>12163.52520630037</v>
       </c>
       <c r="D12">
-        <v>12296.10867743825</v>
+        <v>12346.9593638104</v>
       </c>
       <c r="E12">
         <v>-4921.707417590242</v>
@@ -2265,37 +2390,37 @@
         <v>1122.12</v>
       </c>
       <c r="M12">
-        <v>76.2334159432684</v>
+        <v>74.16906812275435</v>
       </c>
       <c r="N12">
-        <v>1045.886584056731</v>
+        <v>1047.950931877245</v>
       </c>
       <c r="O12">
-        <v>269.8387386866367</v>
+        <v>270.3713404243293</v>
       </c>
       <c r="P12">
-        <v>776.0478453700947</v>
+        <v>777.5795914529161</v>
       </c>
       <c r="Q12">
-        <v>1093.247845370095</v>
+        <v>1094.779591452916</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07468191318989872</v>
+        <v>0.07466334468762385</v>
       </c>
       <c r="T12">
         <v>0.6665899465963939</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.71952930503681</v>
+        <v>15.12921799344738</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2439,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.0709066359998075</v>
+        <v>0.07077570060567663</v>
       </c>
       <c r="C13">
-        <v>12035.36673724796</v>
+        <v>12091.99029243429</v>
       </c>
       <c r="D13">
-        <v>12366.25431050899</v>
+        <v>12422.87786569532</v>
       </c>
       <c r="E13">
         <v>-4774.254001839238</v>
@@ -2347,37 +2472,37 @@
         <v>1122.12</v>
       </c>
       <c r="M13">
-        <v>83.85675753759524</v>
+        <v>81.58597493502978</v>
       </c>
       <c r="N13">
-        <v>1038.263242462405</v>
+        <v>1040.53402506497</v>
       </c>
       <c r="O13">
-        <v>267.8719165553004</v>
+        <v>268.4577784667623</v>
       </c>
       <c r="P13">
-        <v>770.3913259071041</v>
+        <v>772.0762465982078</v>
       </c>
       <c r="Q13">
-        <v>1087.591325907104</v>
+        <v>1089.276246598208</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.0749290808986601</v>
+        <v>0.0749103534895243</v>
       </c>
       <c r="T13">
         <v>0.6722945378643027</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.38139027730619</v>
+        <v>13.75383453949762</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2521,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07076341012870613</v>
+        <v>0.0706221309924918</v>
       </c>
       <c r="C14">
-        <v>11958.86386618424</v>
+        <v>12021.39476406831</v>
       </c>
       <c r="D14">
-        <v>12437.20485519627</v>
+        <v>12499.73575308034</v>
       </c>
       <c r="E14">
         <v>-4626.800586088236</v>
@@ -2429,37 +2554,37 @@
         <v>1122.12</v>
       </c>
       <c r="M14">
-        <v>91.48009913192206</v>
+        <v>89.00288174730521</v>
       </c>
       <c r="N14">
-        <v>1030.639900868078</v>
+        <v>1033.117118252695</v>
       </c>
       <c r="O14">
-        <v>265.9050944239641</v>
+        <v>266.5442165091952</v>
       </c>
       <c r="P14">
-        <v>764.7348064441137</v>
+        <v>766.5729017434994</v>
       </c>
       <c r="Q14">
-        <v>1081.934806444114</v>
+        <v>1083.772901743499</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07518186605534788</v>
+        <v>0.0751629761278316</v>
       </c>
       <c r="T14">
         <v>0.6781287789337552</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.26627442086401</v>
+        <v>12.60768166120615</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2603,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07062018425760477</v>
+        <v>0.07046856137930696</v>
       </c>
       <c r="C15">
-        <v>11883.17984106158</v>
+        <v>11951.75616511986</v>
       </c>
       <c r="D15">
-        <v>12508.97424582461</v>
+        <v>12577.5505698829</v>
       </c>
       <c r="E15">
         <v>-4479.347170337233</v>
@@ -2511,37 +2636,37 @@
         <v>1122.12</v>
       </c>
       <c r="M15">
-        <v>99.10344072624892</v>
+        <v>96.41978855958065</v>
       </c>
       <c r="N15">
-        <v>1023.016559273751</v>
+        <v>1025.700211440419</v>
       </c>
       <c r="O15">
-        <v>263.9382722926277</v>
+        <v>264.6306545516282</v>
       </c>
       <c r="P15">
-        <v>759.0782869811233</v>
+        <v>761.0695568887911</v>
       </c>
       <c r="Q15">
-        <v>1076.278286981123</v>
+        <v>1078.269556888791</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07544046236506295</v>
+        <v>0.07542140618311145</v>
       </c>
       <c r="T15">
         <v>0.6840971404875626</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.32271485002832</v>
+        <v>11.63785999495953</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2685,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0704769583865034</v>
+        <v>0.07031499176612215</v>
       </c>
       <c r="C16">
-        <v>11808.32891970562</v>
+        <v>11883.09247910879</v>
       </c>
       <c r="D16">
-        <v>12581.57674021965</v>
+        <v>12656.34029962283</v>
       </c>
       <c r="E16">
         <v>-4331.89375458623</v>
@@ -2593,37 +2718,37 @@
         <v>1122.12</v>
       </c>
       <c r="M16">
-        <v>106.7267823205758</v>
+        <v>103.8366953718561</v>
       </c>
       <c r="N16">
-        <v>1015.393217679424</v>
+        <v>1018.283304628144</v>
       </c>
       <c r="O16">
-        <v>261.9714501612914</v>
+        <v>262.7170925940611</v>
       </c>
       <c r="P16">
-        <v>753.4217675181328</v>
+        <v>755.5662120340827</v>
       </c>
       <c r="Q16">
-        <v>1070.621767518133</v>
+        <v>1072.766212034083</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07570507254244582</v>
+        <v>0.0756858462396769</v>
       </c>
       <c r="T16">
         <v>0.6902043011472728</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.51394950359773</v>
+        <v>10.80658428103385</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2767,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07033373251540204</v>
+        <v>0.0701614221529373</v>
       </c>
       <c r="C17">
-        <v>11734.32569288593</v>
+        <v>11815.42214301328</v>
       </c>
       <c r="D17">
-        <v>12655.02692915097</v>
+        <v>12736.12337927832</v>
       </c>
       <c r="E17">
         <v>-4184.440338835228</v>
@@ -2675,37 +2800,37 @@
         <v>1122.12</v>
       </c>
       <c r="M17">
-        <v>114.3501239149026</v>
+        <v>111.2536021841315</v>
       </c>
       <c r="N17">
-        <v>1007.769876085097</v>
+        <v>1010.866397815868</v>
       </c>
       <c r="O17">
-        <v>260.0046280299551</v>
+        <v>260.803530636494</v>
       </c>
       <c r="P17">
-        <v>747.7652480551421</v>
+        <v>750.0628671793743</v>
       </c>
       <c r="Q17">
-        <v>1064.965248055142</v>
+        <v>1067.262867179374</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07597590884164947</v>
+        <v>0.07595650841522036</v>
       </c>
       <c r="T17">
         <v>0.6964551597048584</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.813019536691211</v>
+        <v>10.08614532896492</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2849,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07019050664430068</v>
+        <v>0.07000785253975247</v>
       </c>
       <c r="C18">
-        <v>11661.18509409161</v>
+        <v>11748.76406165297</v>
       </c>
       <c r="D18">
-        <v>12729.33974610766</v>
+        <v>12816.91871366901</v>
       </c>
       <c r="E18">
         <v>-4036.986923084225</v>
@@ -2757,37 +2882,37 @@
         <v>1122.12</v>
       </c>
       <c r="M18">
-        <v>121.9734655092294</v>
+        <v>118.670508996407</v>
       </c>
       <c r="N18">
-        <v>1000.14653449077</v>
+        <v>1003.449491003593</v>
       </c>
       <c r="O18">
-        <v>258.0378058986188</v>
+        <v>258.889968678927</v>
       </c>
       <c r="P18">
-        <v>742.1087285921517</v>
+        <v>744.559522324666</v>
       </c>
       <c r="Q18">
-        <v>1059.308728592152</v>
+        <v>1061.759522324666</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07625319362416748</v>
+        <v>0.07623361492827675</v>
       </c>
       <c r="T18">
         <v>0.7028548482281007</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.199705815648009</v>
+        <v>9.455761245904615</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2931,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07018603477319932</v>
+        <v>0.06985428292656765</v>
       </c>
       <c r="C19">
-        <v>11516.06596380684</v>
+        <v>11683.13762262326</v>
       </c>
       <c r="D19">
-        <v>12731.67403157389</v>
+        <v>12898.7456903903</v>
       </c>
       <c r="E19">
         <v>-3889.533507333222</v>
@@ -2839,45 +2964,45 @@
         <v>1122.12</v>
       </c>
       <c r="M19">
-        <v>132.3541859781</v>
+        <v>126.0874158086824</v>
       </c>
       <c r="N19">
-        <v>989.7658140218998</v>
+        <v>996.0325841913175</v>
       </c>
       <c r="O19">
-        <v>255.3595800176502</v>
+        <v>256.9764067213599</v>
       </c>
       <c r="P19">
-        <v>734.4062340042497</v>
+        <v>739.0561774699576</v>
       </c>
       <c r="Q19">
-        <v>1051.60623400425</v>
+        <v>1056.256177469957</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07653715996771003</v>
+        <v>0.07651739870670801</v>
       </c>
       <c r="T19">
         <v>0.709408746113349</v>
       </c>
       <c r="U19">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0391776</v>
+        <v>0.0373226</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>8.478160261479537</v>
+        <v>8.899539996145519</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +3013,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07005097090209797</v>
+        <v>0.06990105331338281</v>
       </c>
       <c r="C20">
-        <v>11439.52060312905</v>
+        <v>11510.65296373422</v>
       </c>
       <c r="D20">
-        <v>12802.5820866471</v>
+        <v>12873.71444725227</v>
       </c>
       <c r="E20">
         <v>-3742.08009158222</v>
@@ -2921,37 +3046,37 @@
         <v>1122.12</v>
       </c>
       <c r="M20">
-        <v>140.1397263297529</v>
+        <v>137.4855648462349</v>
       </c>
       <c r="N20">
-        <v>981.980273670247</v>
+        <v>984.634435153765</v>
       </c>
       <c r="O20">
-        <v>253.3509106069237</v>
+        <v>254.0356842696714</v>
       </c>
       <c r="P20">
-        <v>728.6293630633232</v>
+        <v>730.5987508840936</v>
       </c>
       <c r="Q20">
-        <v>1045.829363063323</v>
+        <v>1047.798750884094</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07682805231963166</v>
+        <v>0.07680810404071074</v>
       </c>
       <c r="T20">
         <v>0.71612249516653</v>
       </c>
       <c r="U20">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.007151358064011</v>
+        <v>8.161729569609648</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +3095,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06991590703099661</v>
+        <v>0.06975861370019799</v>
       </c>
       <c r="C21">
-        <v>11363.76949965239</v>
+        <v>11439.73681883972</v>
       </c>
       <c r="D21">
-        <v>12874.28439892144</v>
+        <v>12950.25171810877</v>
       </c>
       <c r="E21">
         <v>-3594.626675831217</v>
@@ -3003,37 +3128,37 @@
         <v>1122.12</v>
       </c>
       <c r="M21">
-        <v>147.9252666814059</v>
+        <v>145.1236517821368</v>
       </c>
       <c r="N21">
-        <v>974.194733318594</v>
+        <v>976.996348217863</v>
       </c>
       <c r="O21">
-        <v>251.3422411961973</v>
+        <v>252.0650578402087</v>
       </c>
       <c r="P21">
-        <v>722.8524921223967</v>
+        <v>724.9312903776544</v>
       </c>
       <c r="Q21">
-        <v>1040.052492122397</v>
+        <v>1042.131290377654</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07712612719876125</v>
+        <v>0.07710598728419504</v>
       </c>
       <c r="T21">
         <v>0.7230020158012713</v>
       </c>
       <c r="U21">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.585722339218535</v>
+        <v>7.732164855419664</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3177,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06978084315989526</v>
+        <v>0.06961617408701315</v>
       </c>
       <c r="C22">
-        <v>11288.82607352035</v>
+        <v>11369.73618113083</v>
       </c>
       <c r="D22">
-        <v>12946.79438854041</v>
+        <v>13027.70449615089</v>
       </c>
       <c r="E22">
         <v>-3447.173260080214</v>
@@ -3085,37 +3210,37 @@
         <v>1122.12</v>
       </c>
       <c r="M22">
-        <v>155.7108070330588</v>
+        <v>152.7617387180388</v>
       </c>
       <c r="N22">
-        <v>966.4091929669411</v>
+        <v>969.3582612819611</v>
       </c>
       <c r="O22">
-        <v>249.3335717854708</v>
+        <v>250.094431410746</v>
       </c>
       <c r="P22">
-        <v>717.0756211814703</v>
+        <v>719.2638298712151</v>
       </c>
       <c r="Q22">
-        <v>1034.27562118147</v>
+        <v>1036.463829871215</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07743165394986906</v>
+        <v>0.07741131760876643</v>
       </c>
       <c r="T22">
         <v>0.730053524451881</v>
       </c>
       <c r="U22">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.206436222257608</v>
+        <v>7.34555661264868</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3259,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.0696457792887939</v>
+        <v>0.06947373447382831</v>
       </c>
       <c r="C23">
-        <v>11214.70404892633</v>
+        <v>11300.667575819</v>
       </c>
       <c r="D23">
-        <v>13020.12577969739</v>
+        <v>13106.08930659005</v>
       </c>
       <c r="E23">
         <v>-3299.719844329212</v>
@@ -3167,37 +3292,37 @@
         <v>1122.12</v>
       </c>
       <c r="M23">
-        <v>163.4963473847118</v>
+        <v>160.3998256539407</v>
       </c>
       <c r="N23">
-        <v>958.6236526152882</v>
+        <v>961.7201743460591</v>
       </c>
       <c r="O23">
-        <v>247.3249023747443</v>
+        <v>248.1238049812833</v>
       </c>
       <c r="P23">
-        <v>711.2987502405438</v>
+        <v>713.5963693647759</v>
       </c>
       <c r="Q23">
-        <v>1028.498750240544</v>
+        <v>1030.796369364776</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07774491555543531</v>
+        <v>0.07772437781497255</v>
       </c>
       <c r="T23">
         <v>0.7372835523088351</v>
       </c>
       <c r="U23">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.863272592626293</v>
+        <v>6.995768202522553</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3341,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06986984341769252</v>
+        <v>0.0696088028606435</v>
       </c>
       <c r="C24">
-        <v>10946.04738767212</v>
+        <v>11078.86273843381</v>
       </c>
       <c r="D24">
-        <v>12898.92253419418</v>
+        <v>13031.73788495587</v>
       </c>
       <c r="E24">
         <v>-3152.266428578209</v>
@@ -3249,37 +3374,37 @@
         <v>1122.12</v>
       </c>
       <c r="M24">
-        <v>178.4186330587133</v>
+        <v>173.5526703389302</v>
       </c>
       <c r="N24">
-        <v>943.7013669412867</v>
+        <v>948.5673296610697</v>
       </c>
       <c r="O24">
-        <v>243.474952670852</v>
+        <v>244.730371052556</v>
       </c>
       <c r="P24">
-        <v>700.2264142704347</v>
+        <v>703.8369586085137</v>
       </c>
       <c r="Q24">
-        <v>1017.426414270435</v>
+        <v>1021.036958608514</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07806620950986221</v>
+        <v>0.07804546520595319</v>
       </c>
       <c r="T24">
         <v>0.7446989654954549</v>
       </c>
       <c r="U24">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.289253430333912</v>
+        <v>6.465587638661031</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3423,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06975110354659117</v>
+        <v>0.06947897724745866</v>
       </c>
       <c r="C25">
-        <v>10862.54160573587</v>
+        <v>11002.85891884136</v>
       </c>
       <c r="D25">
-        <v>12962.87016800893</v>
+        <v>13103.18748111442</v>
       </c>
       <c r="E25">
         <v>-3004.813012827206</v>
@@ -3331,37 +3456,37 @@
         <v>1122.12</v>
       </c>
       <c r="M25">
-        <v>186.5285709250184</v>
+        <v>181.4414280816088</v>
       </c>
       <c r="N25">
-        <v>935.5914290749815</v>
+        <v>940.6785719183911</v>
       </c>
       <c r="O25">
-        <v>241.3825887013452</v>
+        <v>242.6950715549449</v>
       </c>
       <c r="P25">
-        <v>694.2088403736363</v>
+        <v>697.9835003634462</v>
       </c>
       <c r="Q25">
-        <v>1011.408840373636</v>
+        <v>1015.183500363446</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07839584876180672</v>
+        <v>0.07837489252916709</v>
       </c>
       <c r="T25">
         <v>0.752306986816792</v>
       </c>
       <c r="U25">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.015807629015047</v>
+        <v>6.184475132632291</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3505,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06963236367548981</v>
+        <v>0.06934915163427383</v>
       </c>
       <c r="C26">
-        <v>10779.6730357774</v>
+        <v>10927.64289727893</v>
       </c>
       <c r="D26">
-        <v>13027.45501380146</v>
+        <v>13175.42487530299</v>
       </c>
       <c r="E26">
         <v>-2857.359597076204</v>
@@ -3413,37 +3538,37 @@
         <v>1122.12</v>
       </c>
       <c r="M26">
-        <v>194.6385087913235</v>
+        <v>189.3301858242874</v>
       </c>
       <c r="N26">
-        <v>927.4814912086763</v>
+        <v>932.7898141757124</v>
       </c>
       <c r="O26">
-        <v>239.2902247318385</v>
+        <v>240.6597720573338</v>
       </c>
       <c r="P26">
-        <v>688.1912664768378</v>
+        <v>692.1300421183786</v>
       </c>
       <c r="Q26">
-        <v>1005.391266476838</v>
+        <v>1009.330042118379</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07873416273090764</v>
+        <v>0.07871298899246557</v>
       </c>
       <c r="T26">
         <v>0.7601152192255327</v>
       </c>
       <c r="U26">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.765148977806086</v>
+        <v>5.926788668772613</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3587,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06979187380438845</v>
+        <v>0.069219326021089</v>
       </c>
       <c r="C27">
-        <v>10545.60650070878</v>
+        <v>10853.22777528012</v>
       </c>
       <c r="D27">
-        <v>12940.84189448385</v>
+        <v>13248.46316905519</v>
       </c>
       <c r="E27">
         <v>-2709.906181325201</v>
@@ -3495,45 +3620,45 @@
         <v>1122.12</v>
       </c>
       <c r="M27">
-        <v>208.2779497482913</v>
+        <v>197.2189435669661</v>
       </c>
       <c r="N27">
-        <v>913.8420502517085</v>
+        <v>924.9010564330338</v>
       </c>
       <c r="O27">
-        <v>235.7712489649408</v>
+        <v>238.6244725597227</v>
       </c>
       <c r="P27">
-        <v>678.0708012867677</v>
+        <v>686.276583873311</v>
       </c>
       <c r="Q27">
-        <v>995.2708012867678</v>
+        <v>1003.476583873311</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07908149840585127</v>
+        <v>0.079060101361452</v>
       </c>
       <c r="T27">
         <v>0.7681316711651732</v>
       </c>
       <c r="U27">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.041923</v>
+        <v>0.039697</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>5.387608248286042</v>
+        <v>5.689717122021707</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3669,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06968426393328708</v>
+        <v>0.06924383640790416</v>
       </c>
       <c r="C28">
-        <v>10456.45767965235</v>
+        <v>10691.92317274681</v>
       </c>
       <c r="D28">
-        <v>12999.14648917842</v>
+        <v>13234.61198227288</v>
       </c>
       <c r="E28">
         <v>-2562.452765574198</v>
@@ -3577,37 +3702,37 @@
         <v>1122.12</v>
       </c>
       <c r="M28">
-        <v>216.609067738223</v>
+        <v>208.1747323572656</v>
       </c>
       <c r="N28">
-        <v>905.5109322617769</v>
+        <v>913.9452676427343</v>
       </c>
       <c r="O28">
-        <v>233.6218205235384</v>
+        <v>235.7978790518254</v>
       </c>
       <c r="P28">
-        <v>671.8891117382385</v>
+        <v>678.1473885909088</v>
       </c>
       <c r="Q28">
-        <v>989.0891117382386</v>
+        <v>995.3473885909088</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07943822153146904</v>
+        <v>0.07941659514581643</v>
       </c>
       <c r="T28">
         <v>0.7763647839680472</v>
       </c>
       <c r="U28">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.180392546428886</v>
+        <v>5.390279537260259</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3751,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06957665406218573</v>
+        <v>0.06911994679471933</v>
       </c>
       <c r="C29">
-        <v>10367.83661577346</v>
+        <v>10614.77999284533</v>
       </c>
       <c r="D29">
-        <v>13057.97884105054</v>
+        <v>13304.9222181224</v>
       </c>
       <c r="E29">
         <v>-2414.999349823195</v>
@@ -3659,37 +3784,37 @@
         <v>1122.12</v>
       </c>
       <c r="M29">
-        <v>224.9401857281546</v>
+        <v>216.1814528325451</v>
       </c>
       <c r="N29">
-        <v>897.1798142718453</v>
+        <v>905.9385471674548</v>
       </c>
       <c r="O29">
-        <v>231.4723920821361</v>
+        <v>233.7321451692033</v>
       </c>
       <c r="P29">
-        <v>665.7074221897092</v>
+        <v>672.2064019982514</v>
       </c>
       <c r="Q29">
-        <v>982.9074221897092</v>
+        <v>989.4064019982515</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07980471789340511</v>
+        <v>0.07978285588317717</v>
       </c>
       <c r="T29">
         <v>0.7848234615052466</v>
       </c>
       <c r="U29">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.988526155820408</v>
+        <v>5.190639554398767</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3833,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06946904419108436</v>
+        <v>0.0689960571815345</v>
       </c>
       <c r="C30">
-        <v>10279.75050731994</v>
+        <v>10538.38786368098</v>
       </c>
       <c r="D30">
-        <v>13117.34614834802</v>
+        <v>13375.98350470906</v>
       </c>
       <c r="E30">
         <v>-2267.545934072193</v>
@@ -3741,37 +3866,37 @@
         <v>1122.12</v>
       </c>
       <c r="M30">
-        <v>233.2713037180863</v>
+        <v>224.1881733078245</v>
       </c>
       <c r="N30">
-        <v>888.8486962819136</v>
+        <v>897.9318266921754</v>
       </c>
       <c r="O30">
-        <v>229.3229636407337</v>
+        <v>231.6664112865813</v>
       </c>
       <c r="P30">
-        <v>659.5257326411798</v>
+        <v>666.2654154055941</v>
       </c>
       <c r="Q30">
-        <v>976.7257326411799</v>
+        <v>983.4654154055942</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.0801813947098394</v>
+        <v>0.08015929052990903</v>
       </c>
       <c r="T30">
         <v>0.793517102307368</v>
       </c>
       <c r="U30">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.810364507398251</v>
+        <v>5.005259570313097</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3915,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.069361434319983</v>
+        <v>0.06887216756834967</v>
       </c>
       <c r="C31">
-        <v>10192.20668404305</v>
+        <v>10462.75888390704</v>
       </c>
       <c r="D31">
-        <v>13177.25574082213</v>
+        <v>13447.80794068612</v>
       </c>
       <c r="E31">
         <v>-2120.09251832119</v>
@@ -3823,37 +3948,37 @@
         <v>1122.12</v>
       </c>
       <c r="M31">
-        <v>241.6024217080179</v>
+        <v>232.1948937831039</v>
       </c>
       <c r="N31">
-        <v>880.517578291982</v>
+        <v>889.925106216896</v>
       </c>
       <c r="O31">
-        <v>227.1735351993314</v>
+        <v>229.6006774039592</v>
       </c>
       <c r="P31">
-        <v>653.3440430926506</v>
+        <v>660.3244288129368</v>
       </c>
       <c r="Q31">
-        <v>970.5440430926507</v>
+        <v>977.5244288129369</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08056868214082114</v>
+        <v>0.08054632896950659</v>
       </c>
       <c r="T31">
         <v>0.8024556343996901</v>
       </c>
       <c r="U31">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.644489869212105</v>
+        <v>4.832664412716094</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3997,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06925382444888165</v>
+        <v>0.06874827795516483</v>
       </c>
       <c r="C32">
-        <v>10105.2126102143</v>
+        <v>10387.90541344216</v>
       </c>
       <c r="D32">
-        <v>13237.71508274438</v>
+        <v>13520.40788597224</v>
       </c>
       <c r="E32">
         <v>-1972.639102570188</v>
@@ -3905,37 +4030,37 @@
         <v>1122.12</v>
       </c>
       <c r="M32">
-        <v>249.9335396979496</v>
+        <v>240.2016142583834</v>
       </c>
       <c r="N32">
-        <v>872.1864603020504</v>
+        <v>881.9183857416165</v>
       </c>
       <c r="O32">
-        <v>225.024106757929</v>
+        <v>227.5349435213371</v>
       </c>
       <c r="P32">
-        <v>647.1623535441214</v>
+        <v>654.3834422202794</v>
       </c>
       <c r="Q32">
-        <v>964.3623535441214</v>
+        <v>971.5834422202795</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08096703492697378</v>
+        <v>0.08094442565023549</v>
       </c>
       <c r="T32">
         <v>0.8116495531232215</v>
       </c>
       <c r="U32">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.489673540238368</v>
+        <v>4.671575598958892</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +4079,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06914621457778029</v>
+        <v>0.06862438834197999</v>
       </c>
       <c r="C33">
-        <v>10018.7758877257</v>
+        <v>10313.84008056098</v>
       </c>
       <c r="D33">
-        <v>13298.73177600678</v>
+        <v>13593.79596884206</v>
       </c>
       <c r="E33">
         <v>-1825.185686819185</v>
@@ -3987,37 +4112,37 @@
         <v>1122.12</v>
       </c>
       <c r="M33">
-        <v>258.2646576878812</v>
+        <v>248.2083347336628</v>
       </c>
       <c r="N33">
-        <v>863.8553423121186</v>
+        <v>873.9116652663371</v>
       </c>
       <c r="O33">
-        <v>222.8746783165266</v>
+        <v>225.469209638715</v>
       </c>
       <c r="P33">
-        <v>640.9806639955921</v>
+        <v>648.4424556276222</v>
       </c>
       <c r="Q33">
-        <v>958.1806639955921</v>
+        <v>965.6424556276222</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08137693417069608</v>
+        <v>0.08135406136518841</v>
       </c>
       <c r="T33">
         <v>0.8211099622445365</v>
       </c>
       <c r="U33">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.344845361521001</v>
+        <v>4.520879611895701</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4161,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06937102070667892</v>
+        <v>0.06850049872879517</v>
       </c>
       <c r="C34">
-        <v>9744.48721748875</v>
+        <v>10240.57578921705</v>
       </c>
       <c r="D34">
-        <v>13171.89652152084</v>
+        <v>13667.98509324914</v>
       </c>
       <c r="E34">
         <v>-1677.732271068182</v>
@@ -4069,45 +4194,45 @@
         <v>1122.12</v>
       </c>
       <c r="M34">
-        <v>273.2016887034578</v>
+        <v>256.2150552089423</v>
       </c>
       <c r="N34">
-        <v>848.918311296542</v>
+        <v>865.9049447910577</v>
       </c>
       <c r="O34">
-        <v>219.0209243145079</v>
+        <v>223.4034757560929</v>
       </c>
       <c r="P34">
-        <v>629.8973869820342</v>
+        <v>642.5014690349648</v>
       </c>
       <c r="Q34">
-        <v>947.0973869820342</v>
+        <v>959.7014690349648</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08179888927452783</v>
+        <v>0.08177574518940467</v>
       </c>
       <c r="T34">
         <v>0.8308486186929488</v>
       </c>
       <c r="U34">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.107295256208999</v>
+        <v>4.379602124023961</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4243,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06927379883557756</v>
+        <v>0.06862146911561035</v>
       </c>
       <c r="C35">
-        <v>9651.588091597074</v>
+        <v>10020.67211028017</v>
       </c>
       <c r="D35">
-        <v>13226.45081138016</v>
+        <v>13595.53483006326</v>
       </c>
       <c r="E35">
         <v>-1530.278855317179</v>
@@ -4151,37 +4276,37 @@
         <v>1122.12</v>
       </c>
       <c r="M35">
-        <v>281.7392414754408</v>
+        <v>269.0877384040048</v>
       </c>
       <c r="N35">
-        <v>840.380758524559</v>
+        <v>853.0322615959951</v>
       </c>
       <c r="O35">
-        <v>216.8182356993362</v>
+        <v>220.0823234917667</v>
       </c>
       <c r="P35">
-        <v>623.5625228252228</v>
+        <v>632.9499381042284</v>
       </c>
       <c r="Q35">
-        <v>940.7625228252228</v>
+        <v>950.1499381042285</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08223344005310085</v>
+        <v>0.0822100165904632</v>
       </c>
       <c r="T35">
         <v>0.8408779813040002</v>
       </c>
       <c r="U35">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.982831763596605</v>
+        <v>4.170089676532431</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4325,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06917657696447621</v>
+        <v>0.0685049995024255</v>
       </c>
       <c r="C36">
-        <v>9559.142742162472</v>
+        <v>9942.959576158759</v>
       </c>
       <c r="D36">
-        <v>13281.45887769656</v>
+        <v>13665.27571169285</v>
       </c>
       <c r="E36">
         <v>-1382.825439566176</v>
@@ -4233,37 +4358,37 @@
         <v>1122.12</v>
       </c>
       <c r="M36">
-        <v>290.2767942474239</v>
+        <v>277.2419122950353</v>
       </c>
       <c r="N36">
-        <v>831.843205752576</v>
+        <v>844.8780877049646</v>
       </c>
       <c r="O36">
-        <v>214.6155470841646</v>
+        <v>217.9785466278809</v>
       </c>
       <c r="P36">
-        <v>617.2276586684113</v>
+        <v>626.8995410770838</v>
       </c>
       <c r="Q36">
-        <v>934.4276586684114</v>
+        <v>944.0995410770838</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08268115903708517</v>
+        <v>0.08265744773094774</v>
       </c>
       <c r="T36">
         <v>0.8512112639941745</v>
       </c>
       <c r="U36">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.865689652902587</v>
+        <v>4.04743998016383</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4407,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06907935509337484</v>
+        <v>0.06838852988924067</v>
       </c>
       <c r="C37">
-        <v>9467.156854522374</v>
+        <v>9865.96622947861</v>
       </c>
       <c r="D37">
-        <v>13336.92640580747</v>
+        <v>13735.73578076371</v>
       </c>
       <c r="E37">
         <v>-1235.372023815174</v>
@@ -4315,37 +4440,37 @@
         <v>1122.12</v>
       </c>
       <c r="M37">
-        <v>298.814347019407</v>
+        <v>285.3960861860658</v>
       </c>
       <c r="N37">
-        <v>823.3056529805929</v>
+        <v>836.7239138139341</v>
       </c>
       <c r="O37">
-        <v>212.412858468993</v>
+        <v>215.874769763995</v>
       </c>
       <c r="P37">
-        <v>610.8927945116</v>
+        <v>620.8491440499391</v>
       </c>
       <c r="Q37">
-        <v>928.0927945116</v>
+        <v>938.0491440499392</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08314265398980746</v>
+        <v>0.0831186459834472</v>
       </c>
       <c r="T37">
         <v>0.8618624938440465</v>
       </c>
       <c r="U37">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.75524137710537</v>
+        <v>3.931798837873434</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4489,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06898213322227349</v>
+        <v>0.06827206027605585</v>
       </c>
       <c r="C38">
-        <v>9375.636209387487</v>
+        <v>9789.703252589992</v>
       </c>
       <c r="D38">
-        <v>13392.85917642358</v>
+        <v>13806.92621962609</v>
       </c>
       <c r="E38">
         <v>-1087.918608064172</v>
@@ -4397,37 +4522,37 @@
         <v>1122.12</v>
       </c>
       <c r="M38">
-        <v>307.3518997913899</v>
+        <v>293.5502600770961</v>
       </c>
       <c r="N38">
-        <v>814.7681002086099</v>
+        <v>828.5697399229038</v>
       </c>
       <c r="O38">
-        <v>210.2101698538214</v>
+        <v>213.7709929001092</v>
       </c>
       <c r="P38">
-        <v>604.5579303547886</v>
+        <v>614.7987470227946</v>
       </c>
       <c r="Q38">
-        <v>921.7579303547886</v>
+        <v>931.9987470227946</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08361857065980233</v>
+        <v>0.08359425668133727</v>
       </c>
       <c r="T38">
         <v>0.8728465746267269</v>
       </c>
       <c r="U38">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.650929116630222</v>
+        <v>3.822582203488062</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4571,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.06888491135117214</v>
+        <v>0.06815559066287102</v>
       </c>
       <c r="C39">
-        <v>9284.586684850157</v>
+        <v>9714.182060877341</v>
       </c>
       <c r="D39">
-        <v>13449.26306763726</v>
+        <v>13878.85844366444</v>
       </c>
       <c r="E39">
         <v>-940.4651923131687</v>
@@ -4479,37 +4604,37 @@
         <v>1122.12</v>
       </c>
       <c r="M39">
-        <v>315.8894525633731</v>
+        <v>301.7044339681266</v>
       </c>
       <c r="N39">
-        <v>806.2305474366268</v>
+        <v>820.4155660318733</v>
       </c>
       <c r="O39">
-        <v>208.0074812386497</v>
+        <v>211.6672160362233</v>
       </c>
       <c r="P39">
-        <v>598.2230661979771</v>
+        <v>608.74834999565</v>
       </c>
       <c r="Q39">
-        <v>915.4230661979772</v>
+        <v>925.94834999565</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08410959579551132</v>
+        <v>0.0840849661315413</v>
       </c>
       <c r="T39">
         <v>0.8841793563866354</v>
       </c>
       <c r="U39">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.552255356721296</v>
+        <v>3.719269170961357</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4653,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06878768948007077</v>
+        <v>0.06803912104968619</v>
       </c>
       <c r="C40">
-        <v>9194.014258443636</v>
+        <v>9639.414308861393</v>
       </c>
       <c r="D40">
-        <v>13506.14405698174</v>
+        <v>13951.54410739949</v>
       </c>
       <c r="E40">
         <v>-793.0117765621662</v>
@@ -4561,37 +4686,37 @@
         <v>1122.12</v>
       </c>
       <c r="M40">
-        <v>324.4270053353561</v>
+        <v>309.8586078591571</v>
       </c>
       <c r="N40">
-        <v>797.6929946646437</v>
+        <v>812.2613921408429</v>
       </c>
       <c r="O40">
-        <v>205.8047926234781</v>
+        <v>209.5634391723375</v>
       </c>
       <c r="P40">
-        <v>591.8882020411656</v>
+        <v>602.6979529685054</v>
       </c>
       <c r="Q40">
-        <v>909.0882020411657</v>
+        <v>919.8979529685055</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08461646045172705</v>
+        <v>0.08459150491884869</v>
       </c>
       <c r="T40">
         <v>0.8958777117517021</v>
       </c>
       <c r="U40">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.458774952597052</v>
+        <v>3.621393666462374</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4735,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06869046760896941</v>
+        <v>0.06792265143650136</v>
       </c>
       <c r="C41">
-        <v>9103.925009253822</v>
+        <v>9565.411896494137</v>
       </c>
       <c r="D41">
-        <v>13563.50822354293</v>
+        <v>14024.99511078324</v>
       </c>
       <c r="E41">
         <v>-645.5583608111629</v>
@@ -4643,37 +4768,37 @@
         <v>1122.12</v>
       </c>
       <c r="M41">
-        <v>332.9645581073392</v>
+        <v>318.0127817501875</v>
       </c>
       <c r="N41">
-        <v>789.1554418926607</v>
+        <v>804.1072182498124</v>
       </c>
       <c r="O41">
-        <v>203.6021040083065</v>
+        <v>207.4596623084516</v>
       </c>
       <c r="P41">
-        <v>585.5533378843543</v>
+        <v>596.6475559413608</v>
       </c>
       <c r="Q41">
-        <v>902.7533378843543</v>
+        <v>913.8475559413608</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08513994362126132</v>
+        <v>0.08511465153524814</v>
       </c>
       <c r="T41">
         <v>0.907959619751689</v>
       </c>
       <c r="U41">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.370088415350974</v>
+        <v>3.528537418604365</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4817,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06859324573786804</v>
+        <v>0.06780618182331653</v>
       </c>
       <c r="C42">
-        <v>9014.325120085074</v>
+        <v>9492.186975653656</v>
       </c>
       <c r="D42">
-        <v>13621.36175012518</v>
+        <v>14099.22360569376</v>
       </c>
       <c r="E42">
         <v>-498.1049450601604</v>
@@ -4725,37 +4850,37 @@
         <v>1122.12</v>
       </c>
       <c r="M42">
-        <v>341.5021108793222</v>
+        <v>326.166955641218</v>
       </c>
       <c r="N42">
-        <v>780.6178891206777</v>
+        <v>795.9530443587819</v>
       </c>
       <c r="O42">
-        <v>201.3994153931348</v>
+        <v>205.3558854445657</v>
       </c>
       <c r="P42">
-        <v>579.2184737275428</v>
+        <v>590.5971589142162</v>
       </c>
       <c r="Q42">
-        <v>896.4184737275428</v>
+        <v>907.7971589142162</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08568087622978007</v>
+        <v>0.08565523637219422</v>
       </c>
       <c r="T42">
         <v>0.9204442580183423</v>
       </c>
       <c r="U42">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.285836204967199</v>
+        <v>3.440323983139256</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4899,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06849602386676668</v>
+        <v>0.0676897122101317</v>
       </c>
       <c r="C43">
-        <v>8925.220879681694</v>
+        <v>9419.751956846287</v>
       </c>
       <c r="D43">
-        <v>13679.7109254728</v>
+        <v>14174.2420026374</v>
       </c>
       <c r="E43">
         <v>-350.6515293091579</v>
@@ -4807,37 +4932,37 @@
         <v>1122.12</v>
       </c>
       <c r="M43">
-        <v>350.0396636513053</v>
+        <v>334.3211295322484</v>
       </c>
       <c r="N43">
-        <v>772.0803363486946</v>
+        <v>787.7988704677515</v>
       </c>
       <c r="O43">
-        <v>199.1967267779632</v>
+        <v>203.2521085806799</v>
       </c>
       <c r="P43">
-        <v>572.8836095707313</v>
+        <v>584.5467618870716</v>
       </c>
       <c r="Q43">
-        <v>890.0836095707314</v>
+        <v>901.7467618870717</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08624014553689269</v>
+        <v>0.08621414611886728</v>
       </c>
       <c r="T43">
         <v>0.9333521043618311</v>
       </c>
       <c r="U43">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.205693858504585</v>
+        <v>3.356413642087079</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4981,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06839880199566534</v>
+        <v>0.06757324259694687</v>
       </c>
       <c r="C44">
-        <v>8836.618685006701</v>
+        <v>9348.119516123914</v>
       </c>
       <c r="D44">
-        <v>13738.56214654881</v>
+        <v>14250.06297766603</v>
       </c>
       <c r="E44">
         <v>-203.1981135581555</v>
@@ -4889,37 +5014,37 @@
         <v>1122.12</v>
       </c>
       <c r="M44">
-        <v>358.5772164232883</v>
+        <v>342.4753034232788</v>
       </c>
       <c r="N44">
-        <v>763.5427835767116</v>
+        <v>779.6446965767211</v>
       </c>
       <c r="O44">
-        <v>196.9940381627916</v>
+        <v>201.148331716794</v>
       </c>
       <c r="P44">
-        <v>566.54874541392</v>
+        <v>578.4963648599271</v>
       </c>
       <c r="Q44">
-        <v>883.74874541392</v>
+        <v>895.6963648599271</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08681869999252642</v>
+        <v>0.08679232861542563</v>
       </c>
       <c r="T44">
         <v>0.9467050488550955</v>
       </c>
       <c r="U44">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.258</v>
       </c>
       <c r="W44">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.129367814254476</v>
+        <v>3.276499031561196</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +5063,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06830158012456397</v>
+        <v>0.06745677298376203</v>
       </c>
       <c r="C45">
-        <v>8748.525043579803</v>
+        <v>9277.30260222445</v>
       </c>
       <c r="D45">
-        <v>13797.92192087292</v>
+        <v>14326.69947951757</v>
       </c>
       <c r="E45">
         <v>-55.74469780715299</v>
@@ -4971,37 +5096,37 @@
         <v>1122.12</v>
       </c>
       <c r="M45">
-        <v>367.1147691952714</v>
+        <v>350.6294773143093</v>
       </c>
       <c r="N45">
-        <v>755.0052308047285</v>
+        <v>771.4905226856906</v>
       </c>
       <c r="O45">
-        <v>194.79134954762</v>
+        <v>199.0445548529082</v>
       </c>
       <c r="P45">
-        <v>560.2138812571086</v>
+        <v>572.4459678327825</v>
       </c>
       <c r="Q45">
-        <v>877.4138812571086</v>
+        <v>889.6459678327825</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08741755460449818</v>
+        <v>0.08739079821712636</v>
       </c>
       <c r="T45">
         <v>0.9605265177165446</v>
       </c>
       <c r="U45">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.056591818574139</v>
+        <v>3.200301379664424</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5145,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06905320625346262</v>
+        <v>0.0673403033705772</v>
       </c>
       <c r="C46">
-        <v>8155.073836075365</v>
+        <v>9207.314443943957</v>
       </c>
       <c r="D46">
-        <v>13351.92412911948</v>
+        <v>14404.16473698808</v>
       </c>
       <c r="E46">
         <v>91.70871794385039</v>
@@ -5053,45 +5178,45 @@
         <v>1122.12</v>
       </c>
       <c r="M46">
-        <v>392.5209927291692</v>
+        <v>358.7836512053398</v>
       </c>
       <c r="N46">
-        <v>729.5990072708307</v>
+        <v>763.3363487946601</v>
       </c>
       <c r="O46">
-        <v>188.2365438758743</v>
+        <v>196.9407779890223</v>
       </c>
       <c r="P46">
-        <v>541.3624633949564</v>
+        <v>566.3955708056378</v>
       </c>
       <c r="Q46">
-        <v>858.5624633949565</v>
+        <v>883.5955708056379</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08803779688118323</v>
+        <v>0.08801064173317358</v>
       </c>
       <c r="T46">
         <v>0.9748416104659026</v>
       </c>
       <c r="U46">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.858751559242688</v>
+        <v>3.127567257399323</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5227,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06897527638236126</v>
+        <v>0.06722383375739238</v>
       </c>
       <c r="C47">
-        <v>8052.517996049904</v>
+        <v>9138.168557749308</v>
       </c>
       <c r="D47">
-        <v>13396.82170484502</v>
+        <v>14482.47226654443</v>
       </c>
       <c r="E47">
         <v>239.1621336948529</v>
@@ -5135,45 +5260,45 @@
         <v>1122.12</v>
       </c>
       <c r="M47">
-        <v>401.4419243821048</v>
+        <v>366.9378250963702</v>
       </c>
       <c r="N47">
-        <v>720.678075617895</v>
+        <v>755.1821749036296</v>
       </c>
       <c r="O47">
-        <v>185.9349435094169</v>
+        <v>194.8370011251365</v>
       </c>
       <c r="P47">
-        <v>534.7431321084781</v>
+        <v>560.3451737784932</v>
       </c>
       <c r="Q47">
-        <v>851.9431321084782</v>
+        <v>877.5451737784932</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.088680593422475</v>
+        <v>0.08865302501344068</v>
       </c>
       <c r="T47">
         <v>0.98967725204251</v>
       </c>
       <c r="U47">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.795223746815072</v>
+        <v>3.05806576279045</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5309,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.06889734651125989</v>
+        <v>0.06796066414420755</v>
       </c>
       <c r="C48">
-        <v>7950.265122626027</v>
+        <v>8509.180582710866</v>
       </c>
       <c r="D48">
-        <v>13442.02224717215</v>
+        <v>14000.93770725699</v>
       </c>
       <c r="E48">
         <v>386.6155494458553</v>
@@ -5217,37 +5342,37 @@
         <v>1122.12</v>
       </c>
       <c r="M48">
-        <v>410.3628560350405</v>
+        <v>392.049141798766</v>
       </c>
       <c r="N48">
-        <v>711.7571439649594</v>
+        <v>730.0708582012339</v>
       </c>
       <c r="O48">
-        <v>183.6333431429595</v>
+        <v>188.3582814159184</v>
       </c>
       <c r="P48">
-        <v>528.1238008219998</v>
+        <v>541.7125767853156</v>
       </c>
       <c r="Q48">
-        <v>845.3238008219998</v>
+        <v>858.9125767853157</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08934719724307387</v>
+        <v>0.08931920026705101</v>
       </c>
       <c r="T48">
         <v>1.005062361825658</v>
       </c>
       <c r="U48">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.258</v>
       </c>
       <c r="W48">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.734458013188657</v>
+        <v>2.862192211036571</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5391,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.06881941664015853</v>
+        <v>0.06786274453102271</v>
       </c>
       <c r="C49">
-        <v>7848.318292790686</v>
+        <v>8423.866598551969</v>
       </c>
       <c r="D49">
-        <v>13487.52883308781</v>
+        <v>14063.0771388491</v>
       </c>
       <c r="E49">
         <v>534.0689651968587</v>
@@ -5299,37 +5424,37 @@
         <v>1122.12</v>
       </c>
       <c r="M49">
-        <v>419.2837876879761</v>
+        <v>400.571949229174</v>
       </c>
       <c r="N49">
-        <v>702.8362123120237</v>
+        <v>721.548050770826</v>
       </c>
       <c r="O49">
-        <v>181.3317427765021</v>
+        <v>186.1593970988731</v>
       </c>
       <c r="P49">
-        <v>521.5044695355216</v>
+        <v>535.3886536719529</v>
       </c>
       <c r="Q49">
-        <v>838.7044695355216</v>
+        <v>852.5886536719529</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09003895592482741</v>
+        <v>0.09001051420947681</v>
       </c>
       <c r="T49">
         <v>1.021028041789303</v>
       </c>
       <c r="U49">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.676278055461239</v>
+        <v>2.801294504418771</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5473,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.06874148676905717</v>
+        <v>0.06776482491783788</v>
       </c>
       <c r="C50">
-        <v>7746.680625339663</v>
+        <v>8339.106651962487</v>
       </c>
       <c r="D50">
-        <v>13533.34458138779</v>
+        <v>14125.77060801062</v>
       </c>
       <c r="E50">
         <v>681.5223809478603</v>
@@ -5381,37 +5506,37 @@
         <v>1122.12</v>
       </c>
       <c r="M50">
-        <v>428.2047193409118</v>
+        <v>409.0947566595818</v>
       </c>
       <c r="N50">
-        <v>693.9152806590881</v>
+        <v>713.025243340418</v>
       </c>
       <c r="O50">
-        <v>179.0301424100447</v>
+        <v>183.9605127818278</v>
       </c>
       <c r="P50">
-        <v>514.8851382490434</v>
+        <v>529.0647305585901</v>
       </c>
       <c r="Q50">
-        <v>832.0851382490434</v>
+        <v>846.2647305585901</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09075732070972532</v>
+        <v>0.09072841714968821</v>
       </c>
       <c r="T50">
         <v>1.037607786366934</v>
       </c>
       <c r="U50">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.62052226263913</v>
+        <v>2.74293420224338</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5555,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.06866355689795581</v>
+        <v>0.06766690530465305</v>
       </c>
       <c r="C51">
-        <v>7645.355281590097</v>
+        <v>8254.908185853566</v>
       </c>
       <c r="D51">
-        <v>13579.47265338923</v>
+        <v>14189.0255576527</v>
       </c>
       <c r="E51">
         <v>828.9757966988636</v>
@@ -5463,37 +5588,37 @@
         <v>1122.12</v>
       </c>
       <c r="M51">
-        <v>437.1256509938474</v>
+        <v>417.6175640899899</v>
       </c>
       <c r="N51">
-        <v>684.9943490061524</v>
+        <v>704.50243591001</v>
       </c>
       <c r="O51">
-        <v>176.7285420435873</v>
+        <v>181.7616284647826</v>
       </c>
       <c r="P51">
-        <v>508.2658069625651</v>
+        <v>522.7408074452275</v>
       </c>
       <c r="Q51">
-        <v>825.4658069625651</v>
+        <v>839.9408074452275</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09150385666265845</v>
+        <v>0.09147447314637852</v>
       </c>
       <c r="T51">
         <v>1.054837717006432</v>
       </c>
       <c r="U51">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.567042216462822</v>
+        <v>2.686955953218005</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5637,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.06858562702685445</v>
+        <v>0.06756898569146821</v>
       </c>
       <c r="C52">
-        <v>7544.345466107627</v>
+        <v>8171.278777052948</v>
       </c>
       <c r="D52">
-        <v>13625.91625365776</v>
+        <v>14252.84956460308</v>
       </c>
       <c r="E52">
         <v>976.4292124498661</v>
@@ -5545,37 +5670,37 @@
         <v>1122.12</v>
       </c>
       <c r="M52">
-        <v>446.0465826467831</v>
+        <v>426.1403715203978</v>
       </c>
       <c r="N52">
-        <v>676.0734173532168</v>
+        <v>695.9796284796021</v>
       </c>
       <c r="O52">
-        <v>174.4269416771299</v>
+        <v>179.5627441477373</v>
       </c>
       <c r="P52">
-        <v>501.6464756760869</v>
+        <v>516.4168843318647</v>
       </c>
       <c r="Q52">
-        <v>818.8464756760869</v>
+        <v>833.6168843318648</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.0922802540537089</v>
+        <v>0.09225037138293643</v>
       </c>
       <c r="T52">
         <v>1.072756844871511</v>
       </c>
       <c r="U52">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.515701372133565</v>
+        <v>2.633216834153645</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5719,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.06952943115575309</v>
+        <v>0.06747106607828339</v>
       </c>
       <c r="C53">
-        <v>6854.940752164148</v>
+        <v>8088.226139330398</v>
       </c>
       <c r="D53">
-        <v>13083.96495546528</v>
+        <v>14317.25034263153</v>
       </c>
       <c r="E53">
         <v>1123.882628200869</v>
@@ -5627,45 +5752,45 @@
         <v>1122.12</v>
       </c>
       <c r="M53">
-        <v>475.2718496486319</v>
+        <v>434.6631789508057</v>
       </c>
       <c r="N53">
-        <v>646.8481503513681</v>
+        <v>687.4568210491941</v>
       </c>
       <c r="O53">
-        <v>166.886822790653</v>
+        <v>177.3638598306921</v>
       </c>
       <c r="P53">
-        <v>479.9613275607151</v>
+        <v>510.092961218502</v>
       </c>
       <c r="Q53">
-        <v>797.1613275607151</v>
+        <v>827.2929612185021</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09308834113418998</v>
+        <v>0.09305793893527221</v>
       </c>
       <c r="T53">
         <v>1.091407365710675</v>
       </c>
       <c r="U53">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.258</v>
       </c>
       <c r="W53">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.361006655095568</v>
+        <v>2.581585131523181</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5801,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.06947153528465173</v>
+        <v>0.06737314646509855</v>
       </c>
       <c r="C54">
-        <v>6739.488114539584</v>
+        <v>8005.758126505621</v>
       </c>
       <c r="D54">
-        <v>13115.96573359172</v>
+        <v>14382.23574555776</v>
       </c>
       <c r="E54">
         <v>1271.336043951872</v>
@@ -5709,45 +5834,45 @@
         <v>1122.12</v>
       </c>
       <c r="M54">
-        <v>484.5909055240953</v>
+        <v>443.1859863812138</v>
       </c>
       <c r="N54">
-        <v>637.5290944759046</v>
+        <v>678.9340136187861</v>
       </c>
       <c r="O54">
-        <v>164.4825063747834</v>
+        <v>175.1649755136468</v>
       </c>
       <c r="P54">
-        <v>473.0465881011212</v>
+        <v>503.7690381051393</v>
       </c>
       <c r="Q54">
-        <v>790.2465881011212</v>
+        <v>820.9690381051394</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.0939300985096911</v>
+        <v>0.09389915513562198</v>
       </c>
       <c r="T54">
         <v>1.110834991584803</v>
       </c>
       <c r="U54">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.315602680959114</v>
+        <v>2.531939263609273</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5883,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.06941363941355037</v>
+        <v>0.06865163685191372</v>
       </c>
       <c r="C55">
-        <v>6624.19239579509</v>
+        <v>7053.655561953482</v>
       </c>
       <c r="D55">
-        <v>13148.12343059823</v>
+        <v>13577.58659675662</v>
       </c>
       <c r="E55">
         <v>1418.789459702874</v>
@@ -5791,37 +5916,37 @@
         <v>1122.12</v>
       </c>
       <c r="M55">
-        <v>493.9099613995587</v>
+        <v>479.0614024334326</v>
       </c>
       <c r="N55">
-        <v>628.2100386004413</v>
+        <v>643.0585975665672</v>
       </c>
       <c r="O55">
-        <v>162.0781899589139</v>
+        <v>165.9091181721743</v>
       </c>
       <c r="P55">
-        <v>466.1318486415274</v>
+        <v>477.1494793943929</v>
       </c>
       <c r="Q55">
-        <v>783.3318486415275</v>
+        <v>794.3494793943929</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09480767534797951</v>
+        <v>0.0947761677700292</v>
       </c>
       <c r="T55">
         <v>1.131089324942938</v>
       </c>
       <c r="U55">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.258</v>
       </c>
       <c r="W55">
-        <v>0.0468944</v>
+        <v>0.0454846</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.271912064337244</v>
+        <v>2.342330219675593</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5965,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.071238939542449</v>
+        <v>0.06857968723872888</v>
       </c>
       <c r="C56">
-        <v>5533.332068266205</v>
+        <v>6949.086936207821</v>
       </c>
       <c r="D56">
-        <v>12204.71651882035</v>
+        <v>13620.47138676197</v>
       </c>
       <c r="E56">
         <v>1566.242875453878</v>
@@ -5873,45 +5998,45 @@
         <v>1122.12</v>
       </c>
       <c r="M56">
-        <v>540.6526941926265</v>
+        <v>488.1002968189691</v>
       </c>
       <c r="N56">
-        <v>581.4673058073734</v>
+        <v>634.0197031810308</v>
       </c>
       <c r="O56">
-        <v>150.0185648983023</v>
+        <v>163.5770834207059</v>
       </c>
       <c r="P56">
-        <v>431.448740909071</v>
+        <v>470.4426197603248</v>
       </c>
       <c r="Q56">
-        <v>748.6487409090711</v>
+        <v>787.6426197603248</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09572340770097611</v>
+        <v>0.09569131138854106</v>
       </c>
       <c r="T56">
         <v>1.152224281490556</v>
       </c>
       <c r="U56">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V56">
         <v>0.258</v>
       </c>
       <c r="W56">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.075491368216886</v>
+        <v>2.298953734126045</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +6047,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07121591767134766</v>
+        <v>0.06850773762554406</v>
       </c>
       <c r="C57">
-        <v>5396.933748544312</v>
+        <v>6844.79007192983</v>
       </c>
       <c r="D57">
-        <v>12215.77161484946</v>
+        <v>13663.62793823498</v>
       </c>
       <c r="E57">
         <v>1713.69629120488</v>
@@ -5955,45 +6080,45 @@
         <v>1122.12</v>
       </c>
       <c r="M57">
-        <v>550.6647811221196</v>
+        <v>497.1391912045056</v>
       </c>
       <c r="N57">
-        <v>571.4552188778803</v>
+        <v>624.9808087954943</v>
       </c>
       <c r="O57">
-        <v>147.4354464704931</v>
+        <v>161.2450486692375</v>
       </c>
       <c r="P57">
-        <v>424.0197724073872</v>
+        <v>463.7357601262568</v>
       </c>
       <c r="Q57">
-        <v>741.2197724073872</v>
+        <v>780.9357601262568</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09667983926966145</v>
+        <v>0.09664712805676458</v>
       </c>
       <c r="T57">
         <v>1.174298569440291</v>
       </c>
       <c r="U57">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.037755161522033</v>
+        <v>2.257154575323753</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6129,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07119289580024629</v>
+        <v>0.06959924401235923</v>
       </c>
       <c r="C58">
-        <v>5260.555474507479</v>
+        <v>6070.680735767884</v>
       </c>
       <c r="D58">
-        <v>12226.84675656363</v>
+        <v>13036.97201782403</v>
       </c>
       <c r="E58">
         <v>1861.149706955883</v>
@@ -6037,37 +6162,37 @@
         <v>1122.12</v>
       </c>
       <c r="M58">
-        <v>560.6768680516127</v>
+        <v>529.2987811797993</v>
       </c>
       <c r="N58">
-        <v>561.4431319483872</v>
+        <v>592.8212188202006</v>
       </c>
       <c r="O58">
-        <v>144.8523280426839</v>
+        <v>152.9478744556118</v>
       </c>
       <c r="P58">
-        <v>416.5908039057033</v>
+        <v>439.8733443645888</v>
       </c>
       <c r="Q58">
-        <v>733.7908039057033</v>
+        <v>757.0733443645888</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09767974500055976</v>
+        <v>0.09764639093718007</v>
       </c>
       <c r="T58">
         <v>1.197376234115013</v>
       </c>
       <c r="U58">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0503818</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.001366676494854</v>
+        <v>2.120012438907965</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6211,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07709103392914493</v>
+        <v>0.06954807039917441</v>
       </c>
       <c r="C59">
-        <v>2808.42809961577</v>
+        <v>5951.32008511011</v>
       </c>
       <c r="D59">
-        <v>9922.172797422923</v>
+        <v>13065.06478291726</v>
       </c>
       <c r="E59">
         <v>2008.603122706885</v>
@@ -6119,45 +6244,45 @@
         <v>1122.12</v>
       </c>
       <c r="M59">
-        <v>688.3567807504058</v>
+        <v>538.7505451294386</v>
       </c>
       <c r="N59">
-        <v>433.763219249594</v>
+        <v>583.3694548705613</v>
       </c>
       <c r="O59">
-        <v>111.9109105663953</v>
+        <v>150.5093193566048</v>
       </c>
       <c r="P59">
-        <v>321.8523086831988</v>
+        <v>432.8601355139565</v>
       </c>
       <c r="Q59">
-        <v>639.0523086831988</v>
+        <v>750.0601355139565</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09872615797475565</v>
+        <v>0.09869213116087069</v>
       </c>
       <c r="T59">
         <v>1.221527278542049</v>
       </c>
       <c r="U59">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V59">
         <v>0.258</v>
       </c>
       <c r="W59">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.630143017951724</v>
+        <v>2.08281923822537</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6293,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07717189205804356</v>
+        <v>0.06949689678598957</v>
       </c>
       <c r="C60">
-        <v>2635.401207916166</v>
+        <v>5832.080767494996</v>
       </c>
       <c r="D60">
-        <v>9896.599321474321</v>
+        <v>13093.27888105315</v>
       </c>
       <c r="E60">
         <v>2156.056538457888</v>
@@ -6201,45 +6326,45 @@
         <v>1122.12</v>
       </c>
       <c r="M60">
-        <v>700.433215500413</v>
+        <v>548.2023090790778</v>
       </c>
       <c r="N60">
-        <v>421.6867844995869</v>
+        <v>573.917690920922</v>
       </c>
       <c r="O60">
-        <v>108.7951904008934</v>
+        <v>148.0707642575979</v>
       </c>
       <c r="P60">
-        <v>312.8915940986935</v>
+        <v>425.8469266633242</v>
       </c>
       <c r="Q60">
-        <v>630.0915940986936</v>
+        <v>743.0469266633243</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09982240013819897</v>
+        <v>0.09978766853807039</v>
       </c>
       <c r="T60">
         <v>1.246828372703704</v>
       </c>
       <c r="U60">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.602037103849108</v>
+        <v>2.046908561704242</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6375,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07725275018694221</v>
+        <v>0.06944572317280473</v>
       </c>
       <c r="C61">
-        <v>2462.505803822718</v>
+        <v>5712.963570682341</v>
       </c>
       <c r="D61">
-        <v>9871.157333131876</v>
+        <v>13121.6150999915</v>
       </c>
       <c r="E61">
         <v>2303.50995420889</v>
@@ -6283,45 +6408,45 @@
         <v>1122.12</v>
       </c>
       <c r="M61">
-        <v>712.5096502504201</v>
+        <v>557.6540730287171</v>
       </c>
       <c r="N61">
-        <v>409.6103497495798</v>
+        <v>564.4659269712828</v>
       </c>
       <c r="O61">
-        <v>105.6794702353916</v>
+        <v>145.632209158591</v>
       </c>
       <c r="P61">
-        <v>303.9308795141882</v>
+        <v>418.8337178126918</v>
       </c>
       <c r="Q61">
-        <v>621.1308795141882</v>
+        <v>736.0337178126919</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1009721175291273</v>
+        <v>0.1009366467629384</v>
       </c>
       <c r="T61">
         <v>1.273363666580563</v>
       </c>
       <c r="U61">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.574883932597428</v>
+        <v>2.012215196251629</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6457,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07733360831584085</v>
+        <v>0.07286710955961989</v>
       </c>
       <c r="C62">
-        <v>2289.740875858246</v>
+        <v>3906.887715869188</v>
       </c>
       <c r="D62">
-        <v>9845.845820918406</v>
+        <v>11462.99266092935</v>
       </c>
       <c r="E62">
         <v>2450.963369959893</v>
@@ -6365,45 +6490,45 @@
         <v>1122.12</v>
       </c>
       <c r="M62">
-        <v>724.5860850004271</v>
+        <v>636.1140355498256</v>
       </c>
       <c r="N62">
-        <v>397.5339149995727</v>
+        <v>486.0059644501742</v>
       </c>
       <c r="O62">
-        <v>102.5637500698898</v>
+        <v>125.389538828145</v>
       </c>
       <c r="P62">
-        <v>294.970164929683</v>
+        <v>360.6164256220293</v>
       </c>
       <c r="Q62">
-        <v>612.1701649296831</v>
+        <v>677.8164256220293</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1021793207896021</v>
+        <v>0.1021430738990497</v>
       </c>
       <c r="T62">
         <v>1.301225725151264</v>
       </c>
       <c r="U62">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.548635867054138</v>
+        <v>1.764023331178497</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6539,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.07741446644473948</v>
+        <v>0.07463902994643508</v>
       </c>
       <c r="C63">
-        <v>2117.105422893506</v>
+        <v>3055.128003147045</v>
       </c>
       <c r="D63">
-        <v>9820.663783704669</v>
+        <v>10758.68636395821</v>
       </c>
       <c r="E63">
         <v>2598.416785710895</v>
@@ -6447,37 +6572,37 @@
         <v>1122.12</v>
       </c>
       <c r="M63">
-        <v>736.6625197504343</v>
+        <v>681.7951037494862</v>
       </c>
       <c r="N63">
-        <v>385.4574802495656</v>
+        <v>440.3248962505137</v>
       </c>
       <c r="O63">
-        <v>99.44802990438792</v>
+        <v>113.6038232326325</v>
       </c>
       <c r="P63">
-        <v>286.0094503451777</v>
+        <v>326.7210730178812</v>
       </c>
       <c r="Q63">
-        <v>603.2094503451777</v>
+        <v>643.9210730178812</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1034484319095884</v>
+        <v>0.1034113690934233</v>
       </c>
       <c r="T63">
         <v>1.330516607238413</v>
       </c>
       <c r="U63">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.258</v>
       </c>
       <c r="W63">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.523248393823742</v>
+        <v>1.645831707838582</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6621,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1016082575002928</v>
+        <v>0.07467467033325023</v>
       </c>
       <c r="C64">
-        <v>-2287.766128669102</v>
+        <v>2894.394998773594</v>
       </c>
       <c r="D64">
-        <v>5563.245647893064</v>
+        <v>10745.40677533576</v>
       </c>
       <c r="E64">
         <v>2745.870201461898</v>
@@ -6529,45 +6654,45 @@
         <v>1122.12</v>
       </c>
       <c r="M64">
-        <v>1196.702431551987</v>
+        <v>692.9720726634122</v>
       </c>
       <c r="N64">
-        <v>-74.58243155198738</v>
+        <v>429.1479273365877</v>
       </c>
       <c r="O64">
-        <v>-19.24226734041275</v>
+        <v>110.7201652528396</v>
       </c>
       <c r="P64">
-        <v>-55.34016421157464</v>
+        <v>318.4277620837481</v>
       </c>
       <c r="Q64">
-        <v>261.8598357884254</v>
+        <v>635.6277620837482</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1054843391029191</v>
+        <v>0.104746416666448</v>
       </c>
       <c r="T64">
-        <v>1.377505020310444</v>
+        <v>1.361349114698568</v>
       </c>
       <c r="U64">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
-        <v>0.2419205914243379</v>
+        <v>0.258</v>
       </c>
       <c r="W64">
-        <v>0.09923259458255416</v>
+        <v>0.0562436</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.937676710947046</v>
+        <v>1.619286035131508</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6703,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1024592575002928</v>
+        <v>0.07471031072006541</v>
       </c>
       <c r="C65">
-        <v>-2518.777329241635</v>
+        <v>2733.69473632946</v>
       </c>
       <c r="D65">
-        <v>5479.687863071535</v>
+        <v>10732.15992864263</v>
       </c>
       <c r="E65">
         <v>2893.323617212902</v>
@@ -6611,45 +6736,45 @@
         <v>1122.12</v>
       </c>
       <c r="M65">
-        <v>1216.004083673794</v>
+        <v>704.1490415773384</v>
       </c>
       <c r="N65">
-        <v>-93.88408367379407</v>
+        <v>417.9709584226615</v>
       </c>
       <c r="O65">
-        <v>-24.22209358783887</v>
+        <v>107.8365072730467</v>
       </c>
       <c r="P65">
-        <v>-69.6619900859552</v>
+        <v>310.1344511496148</v>
       </c>
       <c r="Q65">
-        <v>247.5380099140448</v>
+        <v>627.3344511496149</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1070974293489439</v>
+        <v>0.1061536289731498</v>
       </c>
       <c r="T65">
-        <v>1.414734885724239</v>
+        <v>1.393848244183597</v>
       </c>
       <c r="U65">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
-        <v>0.2380805820366499</v>
+        <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.09973525181140253</v>
+        <v>0.0562436</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.9227929536304259</v>
+        <v>1.593583082192912</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6785,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1033102575002929</v>
+        <v>0.07474595110688056</v>
       </c>
       <c r="C66">
-        <v>-2747.315660521839</v>
+        <v>2573.027094871844</v>
       </c>
       <c r="D66">
-        <v>5398.602947542333</v>
+        <v>10718.94570293602</v>
       </c>
       <c r="E66">
         <v>3040.777032963904</v>
@@ -6693,45 +6818,45 @@
         <v>1122.12</v>
       </c>
       <c r="M66">
-        <v>1235.3057357956</v>
+        <v>715.3260104912644</v>
       </c>
       <c r="N66">
-        <v>-113.1857357956001</v>
+        <v>406.7939895087355</v>
       </c>
       <c r="O66">
-        <v>-29.20191983526482</v>
+        <v>104.9528492932538</v>
       </c>
       <c r="P66">
-        <v>-83.98381596033525</v>
+        <v>301.8411402154817</v>
       </c>
       <c r="Q66">
-        <v>233.2161840396648</v>
+        <v>619.0411402154818</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1088001357197479</v>
+        <v>0.1076390197413349</v>
       </c>
       <c r="T66">
-        <v>1.454033076994357</v>
+        <v>1.428152880862239</v>
       </c>
       <c r="U66">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
-        <v>0.2343605729423273</v>
+        <v>0.258</v>
       </c>
       <c r="W66">
-        <v>0.1002222010018494</v>
+        <v>0.0562436</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.9083743137299507</v>
+        <v>1.568683346533648</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6867,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1041612575002928</v>
+        <v>0.07478159149369575</v>
       </c>
       <c r="C67">
-        <v>-2973.489297617207</v>
+        <v>2412.391954052822</v>
       </c>
       <c r="D67">
-        <v>5319.882726197969</v>
+        <v>10705.763977868</v>
       </c>
       <c r="E67">
         <v>3188.230448714907</v>
@@ -6775,45 +6900,45 @@
         <v>1122.12</v>
       </c>
       <c r="M67">
-        <v>1254.607387917406</v>
+        <v>726.5029794051903</v>
       </c>
       <c r="N67">
-        <v>-132.4873879174063</v>
+        <v>395.6170205948096</v>
       </c>
       <c r="O67">
-        <v>-34.18174608269082</v>
+        <v>102.0691913134609</v>
       </c>
       <c r="P67">
-        <v>-98.30564183471547</v>
+        <v>293.5478292813487</v>
       </c>
       <c r="Q67">
-        <v>218.8943581652846</v>
+        <v>610.7478292813487</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.110600139597455</v>
+        <v>0.1092092899819878</v>
       </c>
       <c r="T67">
-        <v>1.495576879194196</v>
+        <v>1.464417782493946</v>
       </c>
       <c r="U67">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
-        <v>0.2307550256662915</v>
+        <v>0.258</v>
       </c>
       <c r="W67">
-        <v>0.1006941671402824</v>
+        <v>0.0562436</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8943993242879514</v>
+        <v>1.544549756586977</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6949,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1050122575002928</v>
+        <v>0.07481723188051093</v>
       </c>
       <c r="C68">
-        <v>-3197.40019685416</v>
+        <v>2251.78919411577</v>
       </c>
       <c r="D68">
-        <v>5243.425242712018</v>
+        <v>10692.61463368195</v>
       </c>
       <c r="E68">
         <v>3335.683864465909</v>
@@ -6857,45 +6982,45 @@
         <v>1122.12</v>
       </c>
       <c r="M68">
-        <v>1273.909040039212</v>
+        <v>737.6799483191163</v>
       </c>
       <c r="N68">
-        <v>-151.7890400392125</v>
+        <v>384.4400516808836</v>
       </c>
       <c r="O68">
-        <v>-39.16157233011683</v>
+        <v>99.18553333366796</v>
       </c>
       <c r="P68">
-        <v>-112.6274677090957</v>
+        <v>285.2545183472156</v>
       </c>
       <c r="Q68">
-        <v>204.5725322909043</v>
+        <v>602.4545183472156</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1125060260562037</v>
+        <v>0.1108719290603262</v>
       </c>
       <c r="T68">
-        <v>1.539564434464614</v>
+        <v>1.502815913633401</v>
       </c>
       <c r="U68">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V68">
-        <v>0.2272587373986204</v>
+        <v>0.258</v>
       </c>
       <c r="W68">
-        <v>0.1011518312745206</v>
+        <v>0.0562436</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8808478193744976</v>
+        <v>1.52114748754778</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +7031,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1058632575002929</v>
+        <v>0.08191226026732609</v>
       </c>
       <c r="C69">
-        <v>-3419.144536328808</v>
+        <v>3.542203173081361</v>
       </c>
       <c r="D69">
-        <v>5169.134318988373</v>
+        <v>8591.821058490261</v>
       </c>
       <c r="E69">
         <v>3483.137280216912</v>
@@ -6939,45 +7064,45 @@
         <v>1122.12</v>
       </c>
       <c r="M69">
-        <v>1293.210692161019</v>
+        <v>889.1440969785461</v>
       </c>
       <c r="N69">
-        <v>-171.0906921610188</v>
+        <v>232.9759030214537</v>
       </c>
       <c r="O69">
-        <v>-44.14139857754284</v>
+        <v>60.10778297953507</v>
       </c>
       <c r="P69">
-        <v>-126.9492935834759</v>
+        <v>172.8681200419187</v>
       </c>
       <c r="Q69">
-        <v>190.2507064165241</v>
+        <v>490.0681200419187</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1145274207851796</v>
+        <v>0.1126353341434124</v>
       </c>
       <c r="T69">
-        <v>1.586217902175662</v>
+        <v>1.543541204235852</v>
       </c>
       <c r="U69">
-        <v>0.1309</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
-        <v>0.2238668159449096</v>
+        <v>0.258</v>
       </c>
       <c r="W69">
-        <v>0.1015958337928113</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.8677008369957738</v>
+        <v>1.262022661808297</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +7113,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1067142575002928</v>
+        <v>0.09792088843270538</v>
       </c>
       <c r="C70">
-        <v>-3638.813119529534</v>
+        <v>-2782.839149626267</v>
       </c>
       <c r="D70">
-        <v>5096.919151538651</v>
+        <v>5952.893121441918</v>
       </c>
       <c r="E70">
         <v>3630.590695967916</v>
@@ -7021,37 +7146,37 @@
         <v>1122.12</v>
       </c>
       <c r="M70">
-        <v>1312.512344282825</v>
+        <v>1189.182307348687</v>
       </c>
       <c r="N70">
-        <v>-190.3923442828252</v>
+        <v>-67.06230734868677</v>
       </c>
       <c r="O70">
-        <v>-49.12122482496891</v>
+        <v>-17.30207529596119</v>
       </c>
       <c r="P70">
-        <v>-141.2711194578563</v>
+        <v>-49.76023205272558</v>
       </c>
       <c r="Q70">
-        <v>175.9288805421438</v>
+        <v>267.4397679472744</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1166751526847164</v>
+        <v>0.1153333743485056</v>
       </c>
       <c r="T70">
-        <v>1.635787211618652</v>
+        <v>1.605851601582115</v>
       </c>
       <c r="U70">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2205746568868962</v>
+        <v>0.243450443393716</v>
       </c>
       <c r="W70">
-        <v>0.1020267774135053</v>
+        <v>0.08972677741350531</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8549405305693653</v>
+        <v>0.9436063697430851</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7195,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1075652575002928</v>
+        <v>0.09864888843270538</v>
       </c>
       <c r="C71">
-        <v>-3856.491745592964</v>
+        <v>-3012.294407250027</v>
       </c>
       <c r="D71">
-        <v>5026.693941226223</v>
+        <v>5870.89127956916</v>
       </c>
       <c r="E71">
         <v>3778.044111718918</v>
@@ -7103,37 +7228,37 @@
         <v>1122.12</v>
       </c>
       <c r="M71">
-        <v>1331.813996404631</v>
+        <v>1206.670282456756</v>
       </c>
       <c r="N71">
-        <v>-209.6939964046314</v>
+        <v>-84.55028245675567</v>
       </c>
       <c r="O71">
-        <v>-54.10105107239491</v>
+        <v>-21.81397287384296</v>
       </c>
       <c r="P71">
-        <v>-155.5929453322365</v>
+        <v>-62.7363095829127</v>
       </c>
       <c r="Q71">
-        <v>161.6070546677635</v>
+        <v>254.4636904170873</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1189614479326105</v>
+        <v>0.1175763864242638</v>
       </c>
       <c r="T71">
-        <v>1.688554541025705</v>
+        <v>1.65765326614928</v>
       </c>
       <c r="U71">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2173779227291151</v>
+        <v>0.2399221760981549</v>
       </c>
       <c r="W71">
-        <v>0.1024452299147588</v>
+        <v>0.09014522991475883</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8425500880973456</v>
+        <v>0.9299309151091274</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7277,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1084162575002928</v>
+        <v>0.0993768884327054</v>
       </c>
       <c r="C72">
-        <v>-4072.261549367689</v>
+        <v>-3239.521191267735</v>
       </c>
       <c r="D72">
-        <v>4958.377553202499</v>
+        <v>5791.117911302454</v>
       </c>
       <c r="E72">
         <v>3925.497527469921</v>
@@ -7185,37 +7310,37 @@
         <v>1122.12</v>
       </c>
       <c r="M72">
-        <v>1351.115648526438</v>
+        <v>1224.158257564824</v>
       </c>
       <c r="N72">
-        <v>-228.9956485264377</v>
+        <v>-102.0382575648246</v>
       </c>
       <c r="O72">
-        <v>-59.08087731982092</v>
+        <v>-26.32587045172474</v>
       </c>
       <c r="P72">
-        <v>-169.9147712066167</v>
+        <v>-75.71238711309982</v>
       </c>
       <c r="Q72">
-        <v>147.2852287933833</v>
+        <v>241.4876128869002</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1214001628636975</v>
+        <v>0.119968932638406</v>
       </c>
       <c r="T72">
-        <v>1.744839692393229</v>
+        <v>1.712908375020923</v>
       </c>
       <c r="U72">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.2142725238329849</v>
+        <v>0.2364947164396098</v>
       </c>
       <c r="W72">
-        <v>0.1028517266302623</v>
+        <v>0.09055172663026229</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8305136582673834</v>
+        <v>0.9166461877504256</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7359,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1092672575002928</v>
+        <v>0.1001048884327054</v>
       </c>
       <c r="C73">
-        <v>-4286.199314119525</v>
+        <v>-3464.609125035515</v>
       </c>
       <c r="D73">
-        <v>4891.893204201664</v>
+        <v>5713.483393285675</v>
       </c>
       <c r="E73">
         <v>4072.950943220922</v>
@@ -7267,37 +7392,37 @@
         <v>1122.12</v>
       </c>
       <c r="M73">
-        <v>1370.417300648244</v>
+        <v>1241.646232672893</v>
       </c>
       <c r="N73">
-        <v>-248.2973006482437</v>
+        <v>-119.5262326728932</v>
       </c>
       <c r="O73">
-        <v>-64.06070356724686</v>
+        <v>-30.83776802960645</v>
       </c>
       <c r="P73">
-        <v>-184.2365970809968</v>
+        <v>-88.68846464328678</v>
       </c>
       <c r="Q73">
-        <v>132.9634029190032</v>
+        <v>228.5115353567133</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1240070650314112</v>
+        <v>0.1225264820397303</v>
       </c>
       <c r="T73">
-        <v>1.805006578337822</v>
+        <v>1.771974181056127</v>
       </c>
       <c r="U73">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.2112546009620979</v>
+        <v>0.2331638049404604</v>
       </c>
       <c r="W73">
-        <v>0.1032467727340614</v>
+        <v>0.0909467727340614</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8188162827988289</v>
+        <v>0.9037356780638001</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7441,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1101182575002928</v>
+        <v>0.1008328884327054</v>
       </c>
       <c r="C74">
-        <v>-4498.377759412206</v>
+        <v>-3687.643089595949</v>
       </c>
       <c r="D74">
-        <v>4827.168174659986</v>
+        <v>5637.902844476243</v>
       </c>
       <c r="E74">
         <v>4220.404358971924</v>
@@ -7349,37 +7474,37 @@
         <v>1122.12</v>
       </c>
       <c r="M74">
-        <v>1389.71895277005</v>
+        <v>1259.134207780962</v>
       </c>
       <c r="N74">
-        <v>-267.5989527700499</v>
+        <v>-137.0142077809621</v>
       </c>
       <c r="O74">
-        <v>-69.04052981467288</v>
+        <v>-35.34966560748823</v>
       </c>
       <c r="P74">
-        <v>-198.558422955377</v>
+        <v>-101.6645421734739</v>
       </c>
       <c r="Q74">
-        <v>118.641577044623</v>
+        <v>215.5354578265261</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1268001744968188</v>
+        <v>0.1252667135411492</v>
       </c>
       <c r="T74">
-        <v>1.869471098992745</v>
+        <v>1.835258973236703</v>
       </c>
       <c r="U74">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.2083205092820687</v>
+        <v>0.2299254187607318</v>
       </c>
       <c r="W74">
-        <v>0.1036308453349772</v>
+        <v>0.09133084533497722</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8074438344266229</v>
+        <v>0.8911837936462472</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7523,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1745207518898519</v>
+        <v>0.1015608884327054</v>
       </c>
       <c r="C75">
-        <v>-7060.99474996911</v>
+        <v>-3908.703533250249</v>
       </c>
       <c r="D75">
-        <v>2412.004599854087</v>
+        <v>5564.295816572948</v>
       </c>
       <c r="E75">
         <v>4367.857774722928</v>
@@ -7431,45 +7556,45 @@
         <v>1122.12</v>
       </c>
       <c r="M75">
-        <v>2322.892639691846</v>
+        <v>1276.622182889031</v>
       </c>
       <c r="N75">
-        <v>-1200.772639691846</v>
+        <v>-154.5021828890312</v>
       </c>
       <c r="O75">
-        <v>-309.7993410404963</v>
+        <v>-39.86156318537006</v>
       </c>
       <c r="P75">
-        <v>-890.9732986513498</v>
+        <v>-114.6406197036612</v>
       </c>
       <c r="Q75">
-        <v>-573.7732986513497</v>
+        <v>202.5593802963389</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1356316416617344</v>
+        <v>0.1282099251537844</v>
       </c>
       <c r="T75">
-        <v>2.073299951573323</v>
+        <v>1.903231527801025</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.124632088049668</v>
+        <v>0.2267757554900368</v>
       </c>
       <c r="W75">
-        <v>0.1889043953988817</v>
+        <v>0.09170439539888164</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4830701087196436</v>
+        <v>0.8789757964730108</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7605,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1762207518898519</v>
+        <v>0.1022888884327054</v>
       </c>
       <c r="C76">
-        <v>-7239.888007619007</v>
+        <v>-4127.866757192834</v>
       </c>
       <c r="D76">
-        <v>2380.564757955192</v>
+        <v>5492.586008381365</v>
       </c>
       <c r="E76">
         <v>4515.311190473931</v>
@@ -7513,45 +7638,45 @@
         <v>1122.12</v>
       </c>
       <c r="M76">
-        <v>2354.713086810913</v>
+        <v>1294.1101579971</v>
       </c>
       <c r="N76">
-        <v>-1232.593086810913</v>
+        <v>-171.9901579971001</v>
       </c>
       <c r="O76">
-        <v>-318.0090163972155</v>
+        <v>-44.37346076325183</v>
       </c>
       <c r="P76">
-        <v>-914.5840704136972</v>
+        <v>-127.6166972338483</v>
       </c>
       <c r="Q76">
-        <v>-597.3840704136971</v>
+        <v>189.5833027661517</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1390867048025703</v>
+        <v>0.1313795376596991</v>
       </c>
       <c r="T76">
-        <v>2.153042257403066</v>
+        <v>1.976432740408757</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.1229478706435914</v>
+        <v>0.223711218253685</v>
       </c>
       <c r="W76">
-        <v>0.189267849515113</v>
+        <v>0.09206784951511297</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4765421342774862</v>
+        <v>0.8670977451693216</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7687,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1779207518898519</v>
+        <v>0.1030168884327054</v>
       </c>
       <c r="C77">
-        <v>-7417.972191289782</v>
+        <v>-4345.205179340235</v>
       </c>
       <c r="D77">
-        <v>2349.933990035419</v>
+        <v>5422.701001984966</v>
       </c>
       <c r="E77">
         <v>4662.764606224933</v>
@@ -7595,45 +7720,45 @@
         <v>1122.12</v>
       </c>
       <c r="M77">
-        <v>2386.533533929979</v>
+        <v>1311.598133105169</v>
       </c>
       <c r="N77">
-        <v>-1264.413533929979</v>
+        <v>-189.478133105169</v>
       </c>
       <c r="O77">
-        <v>-326.2186917539345</v>
+        <v>-48.88535834113361</v>
       </c>
       <c r="P77">
-        <v>-938.1948421760442</v>
+        <v>-140.5927747640354</v>
       </c>
       <c r="Q77">
-        <v>-620.9948421760441</v>
+        <v>176.6072252359646</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1428181729946732</v>
+        <v>0.1348027191660871</v>
       </c>
       <c r="T77">
-        <v>2.239163947699189</v>
+        <v>2.055490050025107</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.1213085657016769</v>
+        <v>0.2207284020103025</v>
       </c>
       <c r="W77">
-        <v>0.1896216115215781</v>
+        <v>0.09242161152157813</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4701882391537865</v>
+        <v>0.8555364419003972</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7769,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1796207518898519</v>
+        <v>0.1037448884327054</v>
       </c>
       <c r="C78">
-        <v>-7595.278135341838</v>
+        <v>-4560.787578272037</v>
       </c>
       <c r="D78">
-        <v>2320.081461734366</v>
+        <v>5354.572018804167</v>
       </c>
       <c r="E78">
         <v>4810.218021975936</v>
@@ -7677,45 +7802,45 @@
         <v>1122.12</v>
       </c>
       <c r="M78">
-        <v>2418.353981049045</v>
+        <v>1329.086108213238</v>
       </c>
       <c r="N78">
-        <v>-1296.233981049045</v>
+        <v>-206.9661082132379</v>
       </c>
       <c r="O78">
-        <v>-334.4283671106537</v>
+        <v>-53.39725591901539</v>
       </c>
       <c r="P78">
-        <v>-961.8056139383916</v>
+        <v>-153.5688522942226</v>
       </c>
       <c r="Q78">
-        <v>-644.6056139383916</v>
+        <v>163.6311477057775</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1468605968694512</v>
+        <v>0.1385111657980074</v>
       </c>
       <c r="T78">
-        <v>2.332462445519988</v>
+        <v>2.141135468776154</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.1197124003634969</v>
+        <v>0.2178240809312196</v>
       </c>
       <c r="W78">
-        <v>0.1899660640015574</v>
+        <v>0.09276606400155737</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4640015517964997</v>
+        <v>0.8442793834543394</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7851,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1813207518898519</v>
+        <v>0.1044728884327054</v>
       </c>
       <c r="C79">
-        <v>-7771.835126965516</v>
+        <v>-4774.679319011255</v>
       </c>
       <c r="D79">
-        <v>2290.977885861691</v>
+        <v>5288.133693815951</v>
       </c>
       <c r="E79">
         <v>4957.671437726938</v>
@@ -7759,45 +7884,45 @@
         <v>1122.12</v>
       </c>
       <c r="M79">
-        <v>2450.174428168111</v>
+        <v>1346.574083321307</v>
       </c>
       <c r="N79">
-        <v>-1328.054428168111</v>
+        <v>-224.4540833213068</v>
       </c>
       <c r="O79">
-        <v>-342.6380424673728</v>
+        <v>-57.90915349689716</v>
       </c>
       <c r="P79">
-        <v>-985.4163857007386</v>
+        <v>-166.5449298244097</v>
       </c>
       <c r="Q79">
-        <v>-668.2163857007386</v>
+        <v>150.6550701755904</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1512545358637752</v>
+        <v>0.1425420860500947</v>
       </c>
       <c r="T79">
-        <v>2.43387385619477</v>
+        <v>2.234228315244682</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V79">
-        <v>0.1181576938652697</v>
+        <v>0.2149951967632817</v>
       </c>
       <c r="W79">
-        <v>0.1903015696638748</v>
+        <v>0.0931015696638748</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4579755576173244</v>
+        <v>0.8333147161367507</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7933,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1830207518898519</v>
+        <v>0.1052008884327054</v>
       </c>
       <c r="C80">
-        <v>-7947.671002018968</v>
+        <v>-4986.942562202119</v>
       </c>
       <c r="D80">
-        <v>2262.595426559242</v>
+        <v>5223.323866376092</v>
       </c>
       <c r="E80">
         <v>5105.124853477942</v>
@@ -7841,45 +7966,45 @@
         <v>1122.12</v>
       </c>
       <c r="M80">
-        <v>2481.994875287178</v>
+        <v>1364.062058429376</v>
       </c>
       <c r="N80">
-        <v>-1359.874875287178</v>
+        <v>-241.9420584293759</v>
       </c>
       <c r="O80">
-        <v>-350.8477178240921</v>
+        <v>-62.42105107477899</v>
       </c>
       <c r="P80">
-        <v>-1009.027157463086</v>
+        <v>-179.5210073545969</v>
       </c>
       <c r="Q80">
-        <v>-691.8271574630862</v>
+        <v>137.6789926454031</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1560479238575831</v>
+        <v>0.1469394535978263</v>
       </c>
       <c r="T80">
-        <v>2.544504486021805</v>
+        <v>2.335784147755804</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V80">
-        <v>0.1166428516362278</v>
+        <v>0.2122388480868293</v>
       </c>
       <c r="W80">
-        <v>0.1906284726169021</v>
+        <v>0.09342847261690204</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4521040761094099</v>
+        <v>0.8226311941349973</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +8015,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1847207518898519</v>
+        <v>0.1059288884327054</v>
       </c>
       <c r="C81">
-        <v>-8122.812233829305</v>
+        <v>-5197.636458092344</v>
       </c>
       <c r="D81">
-        <v>2234.907610499908</v>
+        <v>5160.08338623687</v>
       </c>
       <c r="E81">
         <v>5252.578269228945</v>
@@ -7923,45 +8048,45 @@
         <v>1122.12</v>
       </c>
       <c r="M81">
-        <v>2513.815322406244</v>
+        <v>1381.550033537445</v>
       </c>
       <c r="N81">
-        <v>-1391.695322406244</v>
+        <v>-259.4300335374448</v>
       </c>
       <c r="O81">
-        <v>-359.0573931808111</v>
+        <v>-66.93294865266077</v>
       </c>
       <c r="P81">
-        <v>-1032.637929225433</v>
+        <v>-192.4970848847841</v>
       </c>
       <c r="Q81">
-        <v>-715.4379292254334</v>
+        <v>124.702915115216</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1612978249936586</v>
+        <v>0.1517556180548656</v>
       </c>
       <c r="T81">
-        <v>2.665671366308559</v>
+        <v>2.447011964315605</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V81">
-        <v>0.1151663598433641</v>
+        <v>0.2095522803895277</v>
       </c>
       <c r="W81">
-        <v>0.1909470995458021</v>
+        <v>0.09374709954580203</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.4463812397029617</v>
+        <v>0.8122181410446809</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +8097,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1864207518898519</v>
+        <v>0.1066568884327054</v>
       </c>
       <c r="C82">
-        <v>-8297.284015552535</v>
+        <v>-5406.817326592334</v>
       </c>
       <c r="D82">
-        <v>2207.88924452768</v>
+        <v>5098.355933487881</v>
       </c>
       <c r="E82">
         <v>5400.031684979947</v>
@@ -8005,45 +8130,45 @@
         <v>1122.12</v>
       </c>
       <c r="M82">
-        <v>2545.635769525311</v>
+        <v>1399.038008645514</v>
       </c>
       <c r="N82">
-        <v>-1423.515769525311</v>
+        <v>-276.9180086455137</v>
       </c>
       <c r="O82">
-        <v>-367.2670685375302</v>
+        <v>-71.44484623054255</v>
       </c>
       <c r="P82">
-        <v>-1056.248700987781</v>
+        <v>-205.4731624149712</v>
       </c>
       <c r="Q82">
-        <v>-739.0487009877809</v>
+        <v>111.7268375850289</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1670727162433415</v>
+        <v>0.1570533989576089</v>
       </c>
       <c r="T82">
-        <v>2.798954934623986</v>
+        <v>2.569362562531385</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V82">
-        <v>0.1137267803453221</v>
+        <v>0.2069328768846586</v>
       </c>
       <c r="W82">
-        <v>0.1912577608014795</v>
+        <v>0.0940577608014795</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.4408014742066747</v>
+        <v>0.8020654142816224</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8179,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1881207518898519</v>
+        <v>0.175773932034126</v>
       </c>
       <c r="C83">
-        <v>-8471.110336630809</v>
+        <v>-8265.455083969022</v>
       </c>
       <c r="D83">
-        <v>2181.516339200408</v>
+        <v>2387.171591862196</v>
       </c>
       <c r="E83">
         <v>5547.48510073095</v>
@@ -8087,37 +8212,37 @@
         <v>1122.12</v>
       </c>
       <c r="M83">
-        <v>2577.456216644377</v>
+        <v>2398.300316506909</v>
       </c>
       <c r="N83">
-        <v>-1455.336216644377</v>
+        <v>-1276.180316506909</v>
       </c>
       <c r="O83">
-        <v>-375.4767438942493</v>
+        <v>-329.2545216587824</v>
       </c>
       <c r="P83">
-        <v>-1079.859472750128</v>
+        <v>-946.9257948481262</v>
       </c>
       <c r="Q83">
-        <v>-762.6594727501279</v>
+        <v>-629.7257948481262</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1734554907824647</v>
+        <v>0.1724195968049599</v>
       </c>
       <c r="T83">
-        <v>2.946268352235775</v>
+        <v>2.924240110969051</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1123227460200712</v>
+        <v>0.1207133893980646</v>
       </c>
       <c r="W83">
-        <v>0.1915607514088687</v>
+        <v>0.1765607514088686</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4353594806979504</v>
+        <v>0.4678813542560643</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8261,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1898207518898519</v>
+        <v>0.177323932034126</v>
       </c>
       <c r="C84">
-        <v>-8644.314053834736</v>
+        <v>-8441.041143795981</v>
       </c>
       <c r="D84">
-        <v>2155.766037747484</v>
+        <v>2359.038947786239</v>
       </c>
       <c r="E84">
         <v>5694.938516481952</v>
@@ -8169,37 +8294,37 @@
         <v>1122.12</v>
       </c>
       <c r="M84">
-        <v>2609.276663763444</v>
+        <v>2427.90896238971</v>
       </c>
       <c r="N84">
-        <v>-1487.156663763444</v>
+        <v>-1305.78896238971</v>
       </c>
       <c r="O84">
-        <v>-383.6864192509685</v>
+        <v>-336.8935522965452</v>
       </c>
       <c r="P84">
-        <v>-1103.470244512475</v>
+        <v>-968.8954100931647</v>
       </c>
       <c r="Q84">
-        <v>-786.2702445124753</v>
+        <v>-651.6954100931647</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1805474624926016</v>
+        <v>0.1794540188496798</v>
       </c>
       <c r="T84">
-        <v>3.109949927359985</v>
+        <v>3.086697894911775</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1109529564344606</v>
+        <v>0.1192412748932101</v>
       </c>
       <c r="W84">
-        <v>0.1918563520014434</v>
+        <v>0.1768563520014434</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4300502187382192</v>
+        <v>0.4621754840822099</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8343,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1915207518898519</v>
+        <v>0.178873932034126</v>
       </c>
       <c r="C85">
-        <v>-8816.916957332969</v>
+        <v>-8615.971844640892</v>
       </c>
       <c r="D85">
-        <v>2130.616550000255</v>
+        <v>2331.561662692333</v>
       </c>
       <c r="E85">
         <v>5842.391932232957</v>
@@ -8251,37 +8376,37 @@
         <v>1122.12</v>
       </c>
       <c r="M85">
-        <v>2641.09711088251</v>
+        <v>2457.517608272512</v>
       </c>
       <c r="N85">
-        <v>-1518.97711088251</v>
+        <v>-1335.397608272512</v>
       </c>
       <c r="O85">
-        <v>-391.8960946076876</v>
+        <v>-344.532582934308</v>
       </c>
       <c r="P85">
-        <v>-1127.081016274823</v>
+        <v>-990.8650253382036</v>
       </c>
       <c r="Q85">
-        <v>-809.8810162748225</v>
+        <v>-673.6650253382036</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1884737838156959</v>
+        <v>0.1873160199584846</v>
       </c>
       <c r="T85">
-        <v>3.292888158381161</v>
+        <v>3.268268359318351</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1096161738268165</v>
+        <v>0.1178046330270269</v>
       </c>
       <c r="W85">
-        <v>0.192144829688173</v>
+        <v>0.177144829688173</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4248688908016142</v>
+        <v>0.456607104755918</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8425,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1932207518898519</v>
+        <v>0.180423932034126</v>
       </c>
       <c r="C86">
-        <v>-8988.939832190425</v>
+        <v>-8790.26982303813</v>
       </c>
       <c r="D86">
-        <v>2106.047090893801</v>
+        <v>2304.717100046095</v>
       </c>
       <c r="E86">
         <v>5989.845347983957</v>
@@ -8333,37 +8458,37 @@
         <v>1122.12</v>
       </c>
       <c r="M86">
-        <v>2672.917558001576</v>
+        <v>2487.126254155312</v>
       </c>
       <c r="N86">
-        <v>-1550.797558001576</v>
+        <v>-1365.006254155312</v>
       </c>
       <c r="O86">
-        <v>-400.1057699644067</v>
+        <v>-352.1716135720706</v>
       </c>
       <c r="P86">
-        <v>-1150.69178803717</v>
+        <v>-1012.834640583242</v>
       </c>
       <c r="Q86">
-        <v>-833.4917880371697</v>
+        <v>-695.6346405832419</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1973908953041768</v>
+        <v>0.1961607712058898</v>
       </c>
       <c r="T86">
-        <v>3.498693668279982</v>
+        <v>3.472535131775746</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1083112193764972</v>
+        <v>0.1164021969195623</v>
       </c>
       <c r="W86">
-        <v>0.1924264388585519</v>
+        <v>0.1774264388585519</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4198109278158807</v>
+        <v>0.4511713058897763</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8507,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1949207518898519</v>
+        <v>0.181973932034126</v>
       </c>
       <c r="C87">
-        <v>-9160.402515660007</v>
+        <v>-8963.956684880533</v>
       </c>
       <c r="D87">
-        <v>2082.037823175221</v>
+        <v>2278.483653954694</v>
       </c>
       <c r="E87">
         <v>6137.29876373496</v>
@@ -8415,37 +8540,37 @@
         <v>1122.12</v>
       </c>
       <c r="M87">
-        <v>2704.738005120642</v>
+        <v>2516.734900038114</v>
       </c>
       <c r="N87">
-        <v>-1582.618005120642</v>
+        <v>-1394.614900038114</v>
       </c>
       <c r="O87">
-        <v>-408.3154453211258</v>
+        <v>-359.8106442098334</v>
       </c>
       <c r="P87">
-        <v>-1174.302559799517</v>
+        <v>-1034.80425582828</v>
       </c>
       <c r="Q87">
-        <v>-857.1025597995167</v>
+        <v>-717.6042558282804</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2074969549911219</v>
+        <v>0.2061848226196158</v>
       </c>
       <c r="T87">
-        <v>3.731939912831982</v>
+        <v>3.704037473894129</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1070369697367737</v>
+        <v>0.1150327593087439</v>
       </c>
       <c r="W87">
-        <v>0.1927014219308043</v>
+        <v>0.1777014219308042</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4148719757239292</v>
+        <v>0.445863408173426</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8589,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1966207518898519</v>
+        <v>0.183523932034126</v>
       </c>
       <c r="C88">
-        <v>-9331.323950599661</v>
+        <v>-9137.053063415628</v>
       </c>
       <c r="D88">
-        <v>2058.56980398657</v>
+        <v>2252.840691170602</v>
       </c>
       <c r="E88">
         <v>6284.752179485962</v>
@@ -8497,37 +8622,37 @@
         <v>1122.12</v>
       </c>
       <c r="M88">
-        <v>2736.558452239709</v>
+        <v>2546.343545920915</v>
       </c>
       <c r="N88">
-        <v>-1614.438452239709</v>
+        <v>-1424.223545920915</v>
       </c>
       <c r="O88">
-        <v>-416.5251206778449</v>
+        <v>-367.4496748475961</v>
       </c>
       <c r="P88">
-        <v>-1197.913331561864</v>
+        <v>-1056.773871073319</v>
       </c>
       <c r="Q88">
-        <v>-880.7133315618642</v>
+        <v>-739.573871073319</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2190467374904878</v>
+        <v>0.2176408813781597</v>
       </c>
       <c r="T88">
-        <v>3.998507049462837</v>
+        <v>3.968611579172281</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1057923538096019</v>
+        <v>0.1136951690842236</v>
       </c>
       <c r="W88">
-        <v>0.1929700100478879</v>
+        <v>0.1779700100478879</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4100478829829532</v>
+        <v>0.4406789499388513</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8671,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1983207518898519</v>
+        <v>0.1850739320341259</v>
       </c>
       <c r="C89">
-        <v>-9501.722235317113</v>
+        <v>-9309.578673369197</v>
       </c>
       <c r="D89">
-        <v>2035.624935020119</v>
+        <v>2227.768496968037</v>
       </c>
       <c r="E89">
         <v>6432.205595236965</v>
@@ -8579,37 +8704,37 @@
         <v>1122.12</v>
       </c>
       <c r="M89">
-        <v>2768.378899358775</v>
+        <v>2575.952191803716</v>
       </c>
       <c r="N89">
-        <v>-1646.258899358775</v>
+        <v>-1453.832191803716</v>
       </c>
       <c r="O89">
-        <v>-424.734796034564</v>
+        <v>-375.0887054853588</v>
       </c>
       <c r="P89">
-        <v>-1221.524103324211</v>
+        <v>-1078.743486318358</v>
       </c>
       <c r="Q89">
-        <v>-904.3241033242111</v>
+        <v>-761.5434863183575</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2323734096051407</v>
+        <v>0.2308594107149413</v>
       </c>
       <c r="T89">
-        <v>4.306084514806132</v>
+        <v>4.273889392954764</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1045763497428249</v>
+        <v>0.112388328060267</v>
       </c>
       <c r="W89">
-        <v>0.1932324237254984</v>
+        <v>0.1782324237254984</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.405334688925678</v>
+        <v>0.4356136746521978</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8753,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2000207518898519</v>
+        <v>0.186623932034126</v>
       </c>
       <c r="C90">
-        <v>-9671.614670117939</v>
+        <v>-9481.552361494527</v>
       </c>
       <c r="D90">
-        <v>2013.185915970297</v>
+        <v>2203.24822459371</v>
       </c>
       <c r="E90">
         <v>6579.659010987969</v>
@@ -8661,37 +8786,37 @@
         <v>1122.12</v>
       </c>
       <c r="M90">
-        <v>2800.199346477842</v>
+        <v>2605.560837686518</v>
       </c>
       <c r="N90">
-        <v>-1678.079346477842</v>
+        <v>-1483.440837686518</v>
       </c>
       <c r="O90">
-        <v>-432.9444713912833</v>
+        <v>-382.7277361231217</v>
       </c>
       <c r="P90">
-        <v>-1245.134875086559</v>
+        <v>-1100.713101563396</v>
       </c>
       <c r="Q90">
-        <v>-927.9348750865588</v>
+        <v>-783.5131015633963</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2479211937389025</v>
+        <v>0.2462810282745197</v>
       </c>
       <c r="T90">
-        <v>4.664924891039977</v>
+        <v>4.630046842367662</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.103387982132111</v>
+        <v>0.1111111879686731</v>
       </c>
       <c r="W90">
-        <v>0.1934888734558905</v>
+        <v>0.1784888734558905</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4007286129151588</v>
+        <v>0.4306635192584227</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8835,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2017207518898519</v>
+        <v>0.188173932034126</v>
       </c>
       <c r="C91">
-        <v>-9841.017800808535</v>
+        <v>-9652.99215381973</v>
       </c>
       <c r="D91">
-        <v>1991.236201030704</v>
+        <v>2179.261848019509</v>
       </c>
       <c r="E91">
         <v>6727.112426738971</v>
@@ -8743,37 +8868,37 @@
         <v>1122.12</v>
       </c>
       <c r="M91">
-        <v>2832.019793596908</v>
+        <v>2635.169483569319</v>
       </c>
       <c r="N91">
-        <v>-1709.899793596908</v>
+        <v>-1513.049483569319</v>
       </c>
       <c r="O91">
-        <v>-441.1541467480023</v>
+        <v>-390.3667667608844</v>
       </c>
       <c r="P91">
-        <v>-1268.745646848906</v>
+        <v>-1122.682716808435</v>
       </c>
       <c r="Q91">
-        <v>-951.5456468489058</v>
+        <v>-805.482716808435</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2662958477151662</v>
+        <v>0.2645065762994761</v>
       </c>
       <c r="T91">
-        <v>5.089008972043611</v>
+        <v>5.050960191673814</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1022263194115255</v>
+        <v>0.1098627476544183</v>
       </c>
       <c r="W91">
-        <v>0.1937395602709928</v>
+        <v>0.1787395602709928</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3962260442307188</v>
+        <v>0.4258246033116989</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8917,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2034207518898519</v>
+        <v>0.189723932034126</v>
       </c>
       <c r="C92">
-        <v>-10009.94745938395</v>
+        <v>-9823.915299842063</v>
       </c>
       <c r="D92">
-        <v>1969.759958206295</v>
+        <v>2155.792117748179</v>
       </c>
       <c r="E92">
         <v>6874.565842489974</v>
@@ -8825,37 +8950,37 @@
         <v>1122.12</v>
       </c>
       <c r="M92">
-        <v>2863.840240715975</v>
+        <v>2664.778129452121</v>
       </c>
       <c r="N92">
-        <v>-1741.720240715975</v>
+        <v>-1542.658129452121</v>
       </c>
       <c r="O92">
-        <v>-449.3638221047215</v>
+        <v>-398.0057973986471</v>
       </c>
       <c r="P92">
-        <v>-1292.356418611253</v>
+        <v>-1144.652332053473</v>
       </c>
       <c r="Q92">
-        <v>-975.1564186112532</v>
+        <v>-827.4523320534734</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2883454324866829</v>
+        <v>0.2863772339294237</v>
       </c>
       <c r="T92">
-        <v>5.597909869247973</v>
+        <v>5.556056210841195</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1010904714180641</v>
+        <v>0.1086420504582581</v>
       </c>
       <c r="W92">
-        <v>0.1939846762679818</v>
+        <v>0.1789846762679818</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3918235326281553</v>
+        <v>0.4210932188304578</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8999,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2051207518898519</v>
+        <v>0.191273932034126</v>
       </c>
       <c r="C93">
-        <v>-10178.41880211075</v>
+        <v>-9994.338313896944</v>
       </c>
       <c r="D93">
-        <v>1948.742031230494</v>
+        <v>2132.8225194443</v>
       </c>
       <c r="E93">
         <v>7022.019258240976</v>
@@ -8907,37 +9032,37 @@
         <v>1122.12</v>
       </c>
       <c r="M93">
-        <v>2895.660687835041</v>
+        <v>2694.386775334922</v>
       </c>
       <c r="N93">
-        <v>-1773.540687835041</v>
+        <v>-1572.266775334922</v>
       </c>
       <c r="O93">
-        <v>-457.5734974614406</v>
+        <v>-405.6448280364099</v>
       </c>
       <c r="P93">
-        <v>-1315.9671903736</v>
+        <v>-1166.621947298512</v>
       </c>
       <c r="Q93">
-        <v>-998.7671903736002</v>
+        <v>-849.4219472985121</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3152949249852033</v>
+        <v>0.3131080376993597</v>
       </c>
       <c r="T93">
-        <v>6.21989985471997</v>
+        <v>6.17339578982355</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09997958711676667</v>
+        <v>0.1074481817719036</v>
       </c>
       <c r="W93">
-        <v>0.1942244051002018</v>
+        <v>0.1792244051002018</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3875177795223514</v>
+        <v>0.4164658208213319</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +9081,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2068207518898519</v>
+        <v>0.192823932034126</v>
       </c>
       <c r="C94">
-        <v>-10346.44634519758</v>
+        <v>-10164.27701391018</v>
       </c>
       <c r="D94">
-        <v>1928.16790389467</v>
+        <v>2110.337235182066</v>
       </c>
       <c r="E94">
         <v>7169.472673991979</v>
@@ -8989,37 +9114,37 @@
         <v>1122.12</v>
       </c>
       <c r="M94">
-        <v>2927.481134954107</v>
+        <v>2723.995421217723</v>
       </c>
       <c r="N94">
-        <v>-1805.361134954107</v>
+        <v>-1601.875421217723</v>
       </c>
       <c r="O94">
-        <v>-465.7831728181598</v>
+        <v>-413.2838586741726</v>
       </c>
       <c r="P94">
-        <v>-1339.577962135948</v>
+        <v>-1188.59156254355</v>
       </c>
       <c r="Q94">
-        <v>-1022.377962135948</v>
+        <v>-871.3915625435504</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3489817906083538</v>
+        <v>0.3465215424117797</v>
       </c>
       <c r="T94">
-        <v>6.997387336559969</v>
+        <v>6.945070263551496</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09889285247419312</v>
+        <v>0.1062802667526438</v>
       </c>
       <c r="W94">
-        <v>0.1944589224360692</v>
+        <v>0.1794589224360691</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3833056297449345</v>
+        <v>0.4119390184211</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9163,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2085207518898519</v>
+        <v>0.194373932034126</v>
       </c>
       <c r="C95">
-        <v>-10514.04399822964</v>
+        <v>-10333.74655772449</v>
       </c>
       <c r="D95">
-        <v>1908.023666613614</v>
+        <v>2088.321107118759</v>
       </c>
       <c r="E95">
         <v>7316.926089742983</v>
@@ -9071,37 +9196,37 @@
         <v>1122.12</v>
       </c>
       <c r="M95">
-        <v>2959.301582073174</v>
+        <v>2753.604067100525</v>
       </c>
       <c r="N95">
-        <v>-1837.181582073174</v>
+        <v>-1631.484067100525</v>
       </c>
       <c r="O95">
-        <v>-473.9928481748789</v>
+        <v>-420.9228893119354</v>
       </c>
       <c r="P95">
-        <v>-1363.188733898295</v>
+        <v>-1210.561177788589</v>
       </c>
       <c r="Q95">
-        <v>-1045.988733898295</v>
+        <v>-893.3611777885894</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3922934749809758</v>
+        <v>0.3894817627563197</v>
       </c>
       <c r="T95">
-        <v>7.99701409892568</v>
+        <v>7.937223158344568</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09782948846909426</v>
+        <v>0.1051374681854111</v>
       </c>
       <c r="W95">
-        <v>0.1946883963883695</v>
+        <v>0.1796883963883695</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3791840638336987</v>
+        <v>0.4075095666101204</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9245,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2102207518898519</v>
+        <v>0.1959239320341259</v>
       </c>
       <c r="C96">
-        <v>-10681.22509552911</v>
+        <v>-10502.76147717564</v>
       </c>
       <c r="D96">
-        <v>1888.295985065143</v>
+        <v>2066.759603418615</v>
       </c>
       <c r="E96">
         <v>7464.379505493986</v>
@@ -9153,37 +9278,37 @@
         <v>1122.12</v>
       </c>
       <c r="M96">
-        <v>2991.12202919224</v>
+        <v>2783.212712983326</v>
       </c>
       <c r="N96">
-        <v>-1869.00202919224</v>
+        <v>-1661.092712983326</v>
       </c>
       <c r="O96">
-        <v>-482.202523531598</v>
+        <v>-428.5619199496982</v>
       </c>
       <c r="P96">
-        <v>-1386.799505660642</v>
+        <v>-1232.530793033628</v>
       </c>
       <c r="Q96">
-        <v>-1069.599505660642</v>
+        <v>-915.330793033628</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4500423874778052</v>
+        <v>0.4467620565490398</v>
       </c>
       <c r="T96">
-        <v>9.329849782079963</v>
+        <v>9.260093684735331</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09678874923006135</v>
+        <v>0.104018984481311</v>
       </c>
       <c r="W96">
-        <v>0.1949129879161528</v>
+        <v>0.1799129879161528</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3751501908141913</v>
+        <v>0.4031743584546936</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9327,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2119207518898519</v>
+        <v>0.197473932034126</v>
       </c>
       <c r="C97">
-        <v>-10848.00242558998</v>
+        <v>-10671.33571007918</v>
       </c>
       <c r="D97">
-        <v>1868.972070755273</v>
+        <v>2045.63878626608</v>
       </c>
       <c r="E97">
         <v>7611.832921244988</v>
@@ -9235,37 +9360,37 @@
         <v>1122.12</v>
       </c>
       <c r="M97">
-        <v>3022.942476311307</v>
+        <v>2812.821358866127</v>
       </c>
       <c r="N97">
-        <v>-1900.822476311307</v>
+        <v>-1690.701358866128</v>
       </c>
       <c r="O97">
-        <v>-490.4121988883171</v>
+        <v>-436.2009505874609</v>
       </c>
       <c r="P97">
-        <v>-1410.41027742299</v>
+        <v>-1254.500408278667</v>
       </c>
       <c r="Q97">
-        <v>-1093.21027742299</v>
+        <v>-937.3004082786665</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5308908649733665</v>
+        <v>0.526954467858848</v>
       </c>
       <c r="T97">
-        <v>11.19581973849596</v>
+        <v>11.1121124216824</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09576992029079755</v>
+        <v>0.1029240478025603</v>
       </c>
       <c r="W97">
-        <v>0.1951328512012459</v>
+        <v>0.1801328512012459</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3712012414371998</v>
+        <v>0.3989304178393811</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9409,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2136207518898519</v>
+        <v>0.1990239320341259</v>
       </c>
       <c r="C98">
-        <v>-11014.38825872384</v>
+        <v>-10839.48263027572</v>
       </c>
       <c r="D98">
-        <v>1850.039653372414</v>
+        <v>2024.945281820533</v>
       </c>
       <c r="E98">
         <v>7759.286336995989</v>
@@ -9317,37 +9442,37 @@
         <v>1122.12</v>
       </c>
       <c r="M98">
-        <v>3054.762923430373</v>
+        <v>2842.430004748928</v>
       </c>
       <c r="N98">
-        <v>-1932.642923430373</v>
+        <v>-1720.310004748928</v>
       </c>
       <c r="O98">
-        <v>-498.6218742450362</v>
+        <v>-443.8399812252235</v>
       </c>
       <c r="P98">
-        <v>-1434.021049185337</v>
+        <v>-1276.470023523705</v>
       </c>
       <c r="Q98">
-        <v>-1116.821049185337</v>
+        <v>-959.2700235237048</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6521635812167067</v>
+        <v>0.6472430848235586</v>
       </c>
       <c r="T98">
-        <v>13.99477467311992</v>
+        <v>13.89014052710297</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09477231695443508</v>
+        <v>0.101851922304617</v>
       </c>
       <c r="W98">
-        <v>0.1953481340012329</v>
+        <v>0.1803481340012329</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3673345618388957</v>
+        <v>0.3947748926535543</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9491,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2153207518898519</v>
+        <v>0.200573932034126</v>
       </c>
       <c r="C99">
-        <v>-11180.39437304226</v>
+        <v>-11007.21507587091</v>
       </c>
       <c r="D99">
-        <v>1831.486954805004</v>
+        <v>2004.666251976348</v>
       </c>
       <c r="E99">
         <v>7906.739752746991</v>
@@ -9399,37 +9524,37 @@
         <v>1122.12</v>
       </c>
       <c r="M99">
-        <v>3086.583370549439</v>
+        <v>2872.03865063173</v>
       </c>
       <c r="N99">
-        <v>-1964.463370549439</v>
+        <v>-1749.91865063173</v>
       </c>
       <c r="O99">
-        <v>-506.8315496017552</v>
+        <v>-451.4790118629864</v>
       </c>
       <c r="P99">
-        <v>-1457.631820947684</v>
+        <v>-1298.439638768744</v>
       </c>
       <c r="Q99">
-        <v>-1140.431820947683</v>
+        <v>-981.2396387687436</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8542847749556091</v>
+        <v>0.8477241130980783</v>
       </c>
       <c r="T99">
-        <v>18.65969956415989</v>
+        <v>18.52018736947063</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09379528275902854</v>
+        <v>0.1008019024870436</v>
       </c>
       <c r="W99">
-        <v>0.1955589779806017</v>
+        <v>0.1805589779806017</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3635476075931339</v>
+        <v>0.3907050483993939</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9573,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2170207518898519</v>
+        <v>0.202123932034126</v>
       </c>
       <c r="C100">
-        <v>-11346.03207889129</v>
+        <v>-11174.54537579525</v>
       </c>
       <c r="D100">
-        <v>1813.302664706971</v>
+        <v>1984.789367803009</v>
       </c>
       <c r="E100">
         <v>8054.193168497995</v>
@@ -9481,37 +9606,37 @@
         <v>1122.12</v>
       </c>
       <c r="M100">
-        <v>3118.403817668506</v>
+        <v>2901.647296514531</v>
       </c>
       <c r="N100">
-        <v>-1996.283817668506</v>
+        <v>-1779.527296514531</v>
       </c>
       <c r="O100">
-        <v>-515.0412249584746</v>
+        <v>-459.1180425007491</v>
       </c>
       <c r="P100">
-        <v>-1481.242592710031</v>
+        <v>-1320.409254013782</v>
       </c>
       <c r="Q100">
-        <v>-1164.042592710031</v>
+        <v>-1003.209254013782</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.258527162433414</v>
+        <v>1.248686169647117</v>
       </c>
       <c r="T100">
-        <v>27.98954934623984</v>
+        <v>27.78028105420595</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09283818803699762</v>
+        <v>0.09977331164533909</v>
       </c>
       <c r="W100">
-        <v>0.1957655190216159</v>
+        <v>0.1807655190216159</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9644,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3598379381278978</v>
+        <v>0.3867182621912368</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9655,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2187207518898519</v>
+        <v>0.203673932034126</v>
       </c>
       <c r="C101">
-        <v>-11511.31224184477</v>
+        <v>-11341.48537479947</v>
       </c>
       <c r="D101">
-        <v>1795.475917504499</v>
+        <v>1965.302784549798</v>
       </c>
       <c r="E101">
         <v>8201.646584248998</v>
@@ -9563,37 +9688,37 @@
         <v>1122.12</v>
       </c>
       <c r="M101">
-        <v>3150.224264787572</v>
+        <v>2931.255942397333</v>
       </c>
       <c r="N101">
-        <v>-2028.104264787572</v>
+        <v>-1809.135942397333</v>
       </c>
       <c r="O101">
-        <v>-523.2509003151936</v>
+        <v>-466.7570731385118</v>
       </c>
       <c r="P101">
-        <v>-1504.853364472378</v>
+        <v>-1342.378869258821</v>
       </c>
       <c r="Q101">
-        <v>-1187.653364472378</v>
+        <v>-1025.178869258821</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.471254324866827</v>
+        <v>2.451572339294235</v>
       </c>
       <c r="T101">
-        <v>55.97909869247967</v>
+        <v>55.56056210841189</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.09190042856187644</v>
+        <v>0.09876550041659829</v>
       </c>
       <c r="W101">
-        <v>0.1959678875163471</v>
+        <v>0.1809678875163471</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9726,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3562032114801412</v>
+        <v>0.382812017118598</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_food_processing.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_food_processing.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07246496635070977</v>
+        <v>0.07231139673752494</v>
       </c>
       <c r="C2">
-        <v>12926.96985836322</v>
+        <v>12846.91824912242</v>
       </c>
       <c r="D2">
-        <v>11635.86985836322</v>
+        <v>11703.27166487343</v>
       </c>
       <c r="E2">
-        <v>-6396.241575100268</v>
+        <v>-6248.788159349266</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>147.4534157510027</v>
       </c>
       <c r="G2">
         <v>1291.1</v>
@@ -1570,28 +1570,28 @@
         <v>1122.12</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.416906812275435</v>
       </c>
       <c r="N2">
-        <v>1122.12</v>
+        <v>1114.703093187725</v>
       </c>
       <c r="O2">
-        <v>289.50696</v>
+        <v>287.593398042433</v>
       </c>
       <c r="P2">
-        <v>832.61304</v>
+        <v>827.1096951452917</v>
       </c>
       <c r="Q2">
-        <v>1149.81304</v>
+        <v>1144.309695145292</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07246496635070977</v>
+        <v>0.07266481892679287</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.6204346172469486</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>151.2921799344738</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07231139673752494</v>
+        <v>0.07215782712434012</v>
       </c>
       <c r="C3">
-        <v>12846.91824912242</v>
+        <v>12767.65205131216</v>
       </c>
       <c r="D3">
-        <v>11703.27166487343</v>
+        <v>11771.45888281416</v>
       </c>
       <c r="E3">
-        <v>-6248.788159349266</v>
+        <v>-6101.334743598263</v>
       </c>
       <c r="F3">
-        <v>147.4534157510027</v>
+        <v>294.9068315020054</v>
       </c>
       <c r="G3">
         <v>1291.1</v>
@@ -1652,28 +1652,28 @@
         <v>1122.12</v>
       </c>
       <c r="M3">
-        <v>7.416906812275435</v>
+        <v>14.83381362455087</v>
       </c>
       <c r="N3">
-        <v>1114.703093187725</v>
+        <v>1107.286186375449</v>
       </c>
       <c r="O3">
-        <v>287.593398042433</v>
+        <v>285.6798360848658</v>
       </c>
       <c r="P3">
-        <v>827.1096951452917</v>
+        <v>821.6063502905831</v>
       </c>
       <c r="Q3">
-        <v>1144.309695145292</v>
+        <v>1138.806350290583</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07266481892679287</v>
+        <v>0.07286875012687767</v>
       </c>
       <c r="T3">
-        <v>0.6204346172469486</v>
+        <v>0.625144344731586</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>151.2921799344738</v>
+        <v>75.64608996723692</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07215782712434012</v>
+        <v>0.07200425751115527</v>
       </c>
       <c r="C4">
-        <v>12767.65205131216</v>
+        <v>12689.18507360411</v>
       </c>
       <c r="D4">
-        <v>11771.45888281416</v>
+        <v>11840.44532085712</v>
       </c>
       <c r="E4">
-        <v>-6101.334743598263</v>
+        <v>-5953.88132784726</v>
       </c>
       <c r="F4">
-        <v>294.9068315020054</v>
+        <v>442.360247253008</v>
       </c>
       <c r="G4">
         <v>1291.1</v>
@@ -1734,28 +1734,28 @@
         <v>1122.12</v>
       </c>
       <c r="M4">
-        <v>14.83381362455087</v>
+        <v>22.2507204368263</v>
       </c>
       <c r="N4">
-        <v>1107.286186375449</v>
+        <v>1099.869279563174</v>
       </c>
       <c r="O4">
-        <v>285.6798360848658</v>
+        <v>283.7662741272988</v>
       </c>
       <c r="P4">
-        <v>821.6063502905831</v>
+        <v>816.1030054358748</v>
       </c>
       <c r="Q4">
-        <v>1138.806350290583</v>
+        <v>1133.303005435875</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07286875012687767</v>
+        <v>0.07307688609397452</v>
       </c>
       <c r="T4">
-        <v>0.625144344731586</v>
+        <v>0.6299511799994115</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.64608996723692</v>
+        <v>50.43072664482462</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07200425751115527</v>
+        <v>0.07185068789797046</v>
       </c>
       <c r="C5">
-        <v>12689.18507360411</v>
+        <v>12611.53145028015</v>
       </c>
       <c r="D5">
-        <v>11840.44532085712</v>
+        <v>11910.24511328416</v>
       </c>
       <c r="E5">
-        <v>-5953.88132784726</v>
+        <v>-5806.427912096257</v>
       </c>
       <c r="F5">
-        <v>442.360247253008</v>
+        <v>589.8136630040108</v>
       </c>
       <c r="G5">
         <v>1291.1</v>
@@ -1816,28 +1816,28 @@
         <v>1122.12</v>
       </c>
       <c r="M5">
-        <v>22.2507204368263</v>
+        <v>29.66762724910174</v>
       </c>
       <c r="N5">
-        <v>1099.869279563174</v>
+        <v>1092.452372750898</v>
       </c>
       <c r="O5">
-        <v>283.7662741272988</v>
+        <v>281.8527121697317</v>
       </c>
       <c r="P5">
-        <v>816.1030054358748</v>
+        <v>810.5996605811664</v>
       </c>
       <c r="Q5">
-        <v>1133.303005435875</v>
+        <v>1127.799660581166</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07307688609397452</v>
+        <v>0.07328935822705256</v>
       </c>
       <c r="T5">
-        <v>0.6299511799994115</v>
+        <v>0.6348581576686503</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.43072664482462</v>
+        <v>37.82304498361846</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07185068789797046</v>
+        <v>0.0716971182847856</v>
       </c>
       <c r="C6">
-        <v>12611.53145028015</v>
+        <v>12534.70565088669</v>
       </c>
       <c r="D6">
-        <v>11910.24511328416</v>
+        <v>11980.87272964171</v>
       </c>
       <c r="E6">
-        <v>-5806.427912096257</v>
+        <v>-5658.974496345255</v>
       </c>
       <c r="F6">
-        <v>589.8136630040108</v>
+        <v>737.2670787550135</v>
       </c>
       <c r="G6">
         <v>1291.1</v>
@@ -1898,28 +1898,28 @@
         <v>1122.12</v>
       </c>
       <c r="M6">
-        <v>29.66762724910174</v>
+        <v>37.08453406137718</v>
       </c>
       <c r="N6">
-        <v>1092.452372750898</v>
+        <v>1085.035465938623</v>
       </c>
       <c r="O6">
-        <v>281.8527121697317</v>
+        <v>279.9391502121647</v>
       </c>
       <c r="P6">
-        <v>810.5996605811664</v>
+        <v>805.0963157264581</v>
       </c>
       <c r="Q6">
-        <v>1127.799660581166</v>
+        <v>1122.296315726458</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07328935822705256</v>
+        <v>0.07350630345766906</v>
       </c>
       <c r="T6">
-        <v>0.6348581576686503</v>
+        <v>0.6398684401309256</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.82304498361846</v>
+        <v>30.25843598689477</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0716971182847856</v>
+        <v>0.07154354867160079</v>
       </c>
       <c r="C7">
-        <v>12534.70565088669</v>
+        <v>12458.72249023449</v>
       </c>
       <c r="D7">
-        <v>11980.87272964171</v>
+        <v>12052.3429847405</v>
       </c>
       <c r="E7">
-        <v>-5658.974496345255</v>
+        <v>-5511.521080594252</v>
       </c>
       <c r="F7">
-        <v>737.2670787550135</v>
+        <v>884.7204945060162</v>
       </c>
       <c r="G7">
         <v>1291.1</v>
@@ -1980,28 +1980,28 @@
         <v>1122.12</v>
       </c>
       <c r="M7">
-        <v>37.08453406137718</v>
+        <v>44.50144087365261</v>
       </c>
       <c r="N7">
-        <v>1085.035465938623</v>
+        <v>1077.618559126347</v>
       </c>
       <c r="O7">
-        <v>279.9391502121647</v>
+        <v>278.0255882545976</v>
       </c>
       <c r="P7">
-        <v>805.0963157264581</v>
+        <v>799.5929708717497</v>
       </c>
       <c r="Q7">
-        <v>1122.296315726458</v>
+        <v>1116.79297087175</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07350630345766906</v>
+        <v>0.07372786454425616</v>
       </c>
       <c r="T7">
-        <v>0.6398684401309256</v>
+        <v>0.6449853243477174</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.25843598689477</v>
+        <v>25.2153633224123</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07154354867160079</v>
+        <v>0.07138997905841596</v>
       </c>
       <c r="C8">
-        <v>12458.72249023449</v>
+        <v>12383.59713875866</v>
       </c>
       <c r="D8">
-        <v>12052.3429847405</v>
+        <v>12124.67104901568</v>
       </c>
       <c r="E8">
-        <v>-5511.521080594252</v>
+        <v>-5364.067664843249</v>
       </c>
       <c r="F8">
-        <v>884.7204945060161</v>
+        <v>1032.173910257019</v>
       </c>
       <c r="G8">
         <v>1291.1</v>
@@ -2062,28 +2062,28 @@
         <v>1122.12</v>
       </c>
       <c r="M8">
-        <v>44.50144087365261</v>
+        <v>51.91834768592803</v>
       </c>
       <c r="N8">
-        <v>1077.618559126347</v>
+        <v>1070.201652314072</v>
       </c>
       <c r="O8">
-        <v>278.0255882545976</v>
+        <v>276.1120262970306</v>
       </c>
       <c r="P8">
-        <v>799.5929708717497</v>
+        <v>794.0896260170414</v>
       </c>
       <c r="Q8">
-        <v>1116.79297087175</v>
+        <v>1111.289626017041</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07372786454425616</v>
+        <v>0.0739541903853935</v>
       </c>
       <c r="T8">
-        <v>0.6449853243477174</v>
+        <v>0.6502122490853004</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.21536332241231</v>
+        <v>21.6131685620677</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07138997905841594</v>
+        <v>0.07123640944523113</v>
       </c>
       <c r="C9">
-        <v>12383.59713875867</v>
+        <v>12309.34513325386</v>
       </c>
       <c r="D9">
-        <v>12124.67104901569</v>
+        <v>12197.87245926188</v>
       </c>
       <c r="E9">
-        <v>-5364.067664843249</v>
+        <v>-5216.614249092247</v>
       </c>
       <c r="F9">
-        <v>1032.173910257019</v>
+        <v>1179.627326008022</v>
       </c>
       <c r="G9">
         <v>1291.1</v>
@@ -2144,28 +2144,28 @@
         <v>1122.12</v>
       </c>
       <c r="M9">
-        <v>51.91834768592805</v>
+        <v>59.33525449820348</v>
       </c>
       <c r="N9">
-        <v>1070.201652314072</v>
+        <v>1062.784745501796</v>
       </c>
       <c r="O9">
-        <v>276.1120262970306</v>
+        <v>274.1984643394634</v>
       </c>
       <c r="P9">
-        <v>794.0896260170414</v>
+        <v>788.5862811623329</v>
       </c>
       <c r="Q9">
-        <v>1111.289626017041</v>
+        <v>1105.786281162333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0739541903853935</v>
+        <v>0.07418543635351209</v>
       </c>
       <c r="T9">
-        <v>0.6502122490853004</v>
+        <v>0.6555528026215265</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.61316856206769</v>
+        <v>18.91152249180923</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07123640944523113</v>
+        <v>0.0710828398320463</v>
       </c>
       <c r="C10">
-        <v>12309.34513325386</v>
+        <v>12235.98238800073</v>
       </c>
       <c r="D10">
-        <v>12197.87245926188</v>
+        <v>12271.96312975975</v>
       </c>
       <c r="E10">
-        <v>-5216.614249092247</v>
+        <v>-5069.160833341244</v>
       </c>
       <c r="F10">
-        <v>1179.627326008022</v>
+        <v>1327.080741759024</v>
       </c>
       <c r="G10">
         <v>1291.1</v>
@@ -2226,28 +2226,28 @@
         <v>1122.12</v>
       </c>
       <c r="M10">
-        <v>59.33525449820348</v>
+        <v>66.75216131047891</v>
       </c>
       <c r="N10">
-        <v>1062.784745501796</v>
+        <v>1055.367838689521</v>
       </c>
       <c r="O10">
-        <v>274.1984643394634</v>
+        <v>272.2849023818964</v>
       </c>
       <c r="P10">
-        <v>788.5862811623329</v>
+        <v>783.0829363076245</v>
       </c>
       <c r="Q10">
-        <v>1105.786281162333</v>
+        <v>1100.282936307625</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07418543635351209</v>
+        <v>0.07442176465060032</v>
       </c>
       <c r="T10">
-        <v>0.6555528026215265</v>
+        <v>0.6610107309607466</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.91152249180923</v>
+        <v>16.81024221494154</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0710828398320463</v>
+        <v>0.07092927021886147</v>
       </c>
       <c r="C11">
-        <v>12235.98238800073</v>
+        <v>12163.52520630037</v>
       </c>
       <c r="D11">
-        <v>12271.96312975975</v>
+        <v>12346.9593638104</v>
       </c>
       <c r="E11">
-        <v>-5069.160833341244</v>
+        <v>-4921.707417590242</v>
       </c>
       <c r="F11">
-        <v>1327.080741759024</v>
+        <v>1474.534157510027</v>
       </c>
       <c r="G11">
         <v>1291.1</v>
@@ -2308,28 +2308,28 @@
         <v>1122.12</v>
       </c>
       <c r="M11">
-        <v>66.75216131047891</v>
+        <v>74.16906812275434</v>
       </c>
       <c r="N11">
-        <v>1055.367838689521</v>
+        <v>1047.950931877245</v>
       </c>
       <c r="O11">
-        <v>272.2849023818964</v>
+        <v>270.3713404243293</v>
       </c>
       <c r="P11">
-        <v>783.0829363076245</v>
+        <v>777.5795914529161</v>
       </c>
       <c r="Q11">
-        <v>1100.282936307625</v>
+        <v>1094.779591452916</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07442176465060032</v>
+        <v>0.07466334468762385</v>
       </c>
       <c r="T11">
-        <v>0.6610107309607466</v>
+        <v>0.6665899465963939</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.81024221494154</v>
+        <v>15.12921799344739</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07092927021886147</v>
+        <v>0.07077570060567663</v>
       </c>
       <c r="C12">
-        <v>12163.52520630037</v>
+        <v>12091.99029243429</v>
       </c>
       <c r="D12">
-        <v>12346.9593638104</v>
+        <v>12422.87786569532</v>
       </c>
       <c r="E12">
-        <v>-4921.707417590242</v>
+        <v>-4774.254001839238</v>
       </c>
       <c r="F12">
-        <v>1474.534157510027</v>
+        <v>1621.98757326103</v>
       </c>
       <c r="G12">
         <v>1291.1</v>
@@ -2390,28 +2390,28 @@
         <v>1122.12</v>
       </c>
       <c r="M12">
-        <v>74.16906812275435</v>
+        <v>81.58597493502978</v>
       </c>
       <c r="N12">
-        <v>1047.950931877245</v>
+        <v>1040.53402506497</v>
       </c>
       <c r="O12">
-        <v>270.3713404243293</v>
+        <v>268.4577784667623</v>
       </c>
       <c r="P12">
-        <v>777.5795914529161</v>
+        <v>772.0762465982078</v>
       </c>
       <c r="Q12">
-        <v>1094.779591452916</v>
+        <v>1089.276246598208</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07466334468762385</v>
+        <v>0.0749103534895243</v>
       </c>
       <c r="T12">
-        <v>0.6665899465963939</v>
+        <v>0.6722945378643027</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.12921799344738</v>
+        <v>13.75383453949762</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07077570060567663</v>
+        <v>0.0706221309924918</v>
       </c>
       <c r="C13">
-        <v>12091.99029243429</v>
+        <v>12021.39476406831</v>
       </c>
       <c r="D13">
-        <v>12422.87786569532</v>
+        <v>12499.73575308034</v>
       </c>
       <c r="E13">
-        <v>-4774.254001839238</v>
+        <v>-4626.800586088236</v>
       </c>
       <c r="F13">
-        <v>1621.98757326103</v>
+        <v>1769.440989012032</v>
       </c>
       <c r="G13">
         <v>1291.1</v>
@@ -2472,28 +2472,28 @@
         <v>1122.12</v>
       </c>
       <c r="M13">
-        <v>81.58597493502978</v>
+        <v>89.00288174730521</v>
       </c>
       <c r="N13">
-        <v>1040.53402506497</v>
+        <v>1033.117118252695</v>
       </c>
       <c r="O13">
-        <v>268.4577784667623</v>
+        <v>266.5442165091952</v>
       </c>
       <c r="P13">
-        <v>772.0762465982078</v>
+        <v>766.5729017434994</v>
       </c>
       <c r="Q13">
-        <v>1089.276246598208</v>
+        <v>1083.772901743499</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0749103534895243</v>
+        <v>0.0751629761278316</v>
       </c>
       <c r="T13">
-        <v>0.6722945378643027</v>
+        <v>0.6781287789337552</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.75383453949762</v>
+        <v>12.60768166120615</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0706221309924918</v>
+        <v>0.07046856137930696</v>
       </c>
       <c r="C14">
-        <v>12021.39476406831</v>
+        <v>11951.75616511986</v>
       </c>
       <c r="D14">
-        <v>12499.73575308034</v>
+        <v>12577.5505698829</v>
       </c>
       <c r="E14">
-        <v>-4626.800586088236</v>
+        <v>-4479.347170337233</v>
       </c>
       <c r="F14">
-        <v>1769.440989012032</v>
+        <v>1916.894404763035</v>
       </c>
       <c r="G14">
         <v>1291.1</v>
@@ -2554,28 +2554,28 @@
         <v>1122.12</v>
       </c>
       <c r="M14">
-        <v>89.00288174730521</v>
+        <v>96.41978855958065</v>
       </c>
       <c r="N14">
-        <v>1033.117118252695</v>
+        <v>1025.700211440419</v>
       </c>
       <c r="O14">
-        <v>266.5442165091952</v>
+        <v>264.6306545516282</v>
       </c>
       <c r="P14">
-        <v>766.5729017434994</v>
+        <v>761.0695568887911</v>
       </c>
       <c r="Q14">
-        <v>1083.772901743499</v>
+        <v>1078.269556888791</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0751629761278316</v>
+        <v>0.07542140618311145</v>
       </c>
       <c r="T14">
-        <v>0.6781287789337552</v>
+        <v>0.6840971404875626</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.60768166120615</v>
+        <v>11.63785999495953</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07046856137930696</v>
+        <v>0.07031499176612215</v>
       </c>
       <c r="C15">
-        <v>11951.75616511986</v>
+        <v>11883.09247910879</v>
       </c>
       <c r="D15">
-        <v>12577.5505698829</v>
+        <v>12656.34029962283</v>
       </c>
       <c r="E15">
-        <v>-4479.347170337233</v>
+        <v>-4331.89375458623</v>
       </c>
       <c r="F15">
-        <v>1916.894404763035</v>
+        <v>2064.347820514038</v>
       </c>
       <c r="G15">
         <v>1291.1</v>
@@ -2636,28 +2636,28 @@
         <v>1122.12</v>
       </c>
       <c r="M15">
-        <v>96.41978855958065</v>
+        <v>103.8366953718561</v>
       </c>
       <c r="N15">
-        <v>1025.700211440419</v>
+        <v>1018.283304628144</v>
       </c>
       <c r="O15">
-        <v>264.6306545516282</v>
+        <v>262.7170925940611</v>
       </c>
       <c r="P15">
-        <v>761.0695568887911</v>
+        <v>755.5662120340827</v>
       </c>
       <c r="Q15">
-        <v>1078.269556888791</v>
+        <v>1072.766212034083</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07542140618311145</v>
+        <v>0.0756858462396769</v>
       </c>
       <c r="T15">
-        <v>0.6840971404875626</v>
+        <v>0.6902043011472728</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.63785999495953</v>
+        <v>10.80658428103385</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07031499176612215</v>
+        <v>0.0701614221529373</v>
       </c>
       <c r="C16">
-        <v>11883.09247910879</v>
+        <v>11815.42214301328</v>
       </c>
       <c r="D16">
-        <v>12656.34029962283</v>
+        <v>12736.12337927832</v>
       </c>
       <c r="E16">
-        <v>-4331.89375458623</v>
+        <v>-4184.440338835228</v>
       </c>
       <c r="F16">
-        <v>2064.347820514038</v>
+        <v>2211.801236265041</v>
       </c>
       <c r="G16">
         <v>1291.1</v>
@@ -2718,28 +2718,28 @@
         <v>1122.12</v>
       </c>
       <c r="M16">
-        <v>103.8366953718561</v>
+        <v>111.2536021841315</v>
       </c>
       <c r="N16">
-        <v>1018.283304628144</v>
+        <v>1010.866397815868</v>
       </c>
       <c r="O16">
-        <v>262.7170925940611</v>
+        <v>260.803530636494</v>
       </c>
       <c r="P16">
-        <v>755.5662120340827</v>
+        <v>750.0628671793743</v>
       </c>
       <c r="Q16">
-        <v>1072.766212034083</v>
+        <v>1067.262867179374</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0756858462396769</v>
+        <v>0.07595650841522036</v>
       </c>
       <c r="T16">
-        <v>0.6902043011472728</v>
+        <v>0.6964551597048584</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.80658428103385</v>
+        <v>10.08614532896492</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0701614221529373</v>
+        <v>0.07000785253975247</v>
       </c>
       <c r="C17">
-        <v>11815.42214301328</v>
+        <v>11748.76406165297</v>
       </c>
       <c r="D17">
-        <v>12736.12337927832</v>
+        <v>12816.91871366901</v>
       </c>
       <c r="E17">
-        <v>-4184.440338835228</v>
+        <v>-4036.986923084225</v>
       </c>
       <c r="F17">
-        <v>2211.80123626504</v>
+        <v>2359.254652016043</v>
       </c>
       <c r="G17">
         <v>1291.1</v>
@@ -2800,28 +2800,28 @@
         <v>1122.12</v>
       </c>
       <c r="M17">
-        <v>111.2536021841315</v>
+        <v>118.670508996407</v>
       </c>
       <c r="N17">
-        <v>1010.866397815868</v>
+        <v>1003.449491003593</v>
       </c>
       <c r="O17">
-        <v>260.803530636494</v>
+        <v>258.889968678927</v>
       </c>
       <c r="P17">
-        <v>750.0628671793743</v>
+        <v>744.559522324666</v>
       </c>
       <c r="Q17">
-        <v>1067.262867179374</v>
+        <v>1061.759522324666</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07595650841522036</v>
+        <v>0.07623361492827675</v>
       </c>
       <c r="T17">
-        <v>0.6964551597048584</v>
+        <v>0.7028548482281007</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.08614532896492</v>
+        <v>9.455761245904615</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07000785253975247</v>
+        <v>0.06985428292656765</v>
       </c>
       <c r="C18">
-        <v>11748.76406165297</v>
+        <v>11683.13762262326</v>
       </c>
       <c r="D18">
-        <v>12816.91871366901</v>
+        <v>12898.7456903903</v>
       </c>
       <c r="E18">
-        <v>-4036.986923084225</v>
+        <v>-3889.533507333222</v>
       </c>
       <c r="F18">
-        <v>2359.254652016043</v>
+        <v>2506.708067767046</v>
       </c>
       <c r="G18">
         <v>1291.1</v>
@@ -2882,28 +2882,28 @@
         <v>1122.12</v>
       </c>
       <c r="M18">
-        <v>118.670508996407</v>
+        <v>126.0874158086824</v>
       </c>
       <c r="N18">
-        <v>1003.449491003593</v>
+        <v>996.0325841913175</v>
       </c>
       <c r="O18">
-        <v>258.889968678927</v>
+        <v>256.9764067213599</v>
       </c>
       <c r="P18">
-        <v>744.559522324666</v>
+        <v>739.0561774699576</v>
       </c>
       <c r="Q18">
-        <v>1061.759522324666</v>
+        <v>1056.256177469957</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07623361492827675</v>
+        <v>0.07651739870670801</v>
       </c>
       <c r="T18">
-        <v>0.7028548482281007</v>
+        <v>0.709408746113349</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.455761245904615</v>
+        <v>8.899539996145519</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06985428292656765</v>
+        <v>0.06990105331338281</v>
       </c>
       <c r="C19">
-        <v>11683.13762262326</v>
+        <v>11510.65296373422</v>
       </c>
       <c r="D19">
-        <v>12898.7456903903</v>
+        <v>12873.71444725227</v>
       </c>
       <c r="E19">
-        <v>-3889.533507333222</v>
+        <v>-3742.08009158222</v>
       </c>
       <c r="F19">
-        <v>2506.708067767046</v>
+        <v>2654.161483518048</v>
       </c>
       <c r="G19">
         <v>1291.1</v>
@@ -2964,45 +2964,45 @@
         <v>1122.12</v>
       </c>
       <c r="M19">
-        <v>126.0874158086824</v>
+        <v>137.4855648462349</v>
       </c>
       <c r="N19">
-        <v>996.0325841913175</v>
+        <v>984.634435153765</v>
       </c>
       <c r="O19">
-        <v>256.9764067213599</v>
+        <v>254.0356842696714</v>
       </c>
       <c r="P19">
-        <v>739.0561774699576</v>
+        <v>730.5987508840936</v>
       </c>
       <c r="Q19">
-        <v>1056.256177469957</v>
+        <v>1047.798750884094</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07651739870670801</v>
+        <v>0.07680810404071074</v>
       </c>
       <c r="T19">
-        <v>0.709408746113349</v>
+        <v>0.71612249516653</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>8.899539996145519</v>
+        <v>8.161729569609644</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06990105331338281</v>
+        <v>0.06975861370019799</v>
       </c>
       <c r="C20">
-        <v>11510.65296373422</v>
+        <v>11439.73681883972</v>
       </c>
       <c r="D20">
-        <v>12873.71444725227</v>
+        <v>12950.25171810877</v>
       </c>
       <c r="E20">
-        <v>-3742.08009158222</v>
+        <v>-3594.626675831217</v>
       </c>
       <c r="F20">
-        <v>2654.161483518048</v>
+        <v>2801.614899269051</v>
       </c>
       <c r="G20">
         <v>1291.1</v>
@@ -3046,28 +3046,28 @@
         <v>1122.12</v>
       </c>
       <c r="M20">
-        <v>137.4855648462349</v>
+        <v>145.1236517821368</v>
       </c>
       <c r="N20">
-        <v>984.634435153765</v>
+        <v>976.996348217863</v>
       </c>
       <c r="O20">
-        <v>254.0356842696714</v>
+        <v>252.0650578402087</v>
       </c>
       <c r="P20">
-        <v>730.5987508840936</v>
+        <v>724.9312903776544</v>
       </c>
       <c r="Q20">
-        <v>1047.798750884094</v>
+        <v>1042.131290377654</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07680810404071074</v>
+        <v>0.07710598728419504</v>
       </c>
       <c r="T20">
-        <v>0.71612249516653</v>
+        <v>0.7230020158012713</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.161729569609648</v>
+        <v>7.732164855419664</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06975861370019799</v>
+        <v>0.06961617408701315</v>
       </c>
       <c r="C21">
-        <v>11439.73681883972</v>
+        <v>11369.73618113083</v>
       </c>
       <c r="D21">
-        <v>12950.25171810877</v>
+        <v>13027.70449615089</v>
       </c>
       <c r="E21">
-        <v>-3594.626675831217</v>
+        <v>-3447.173260080214</v>
       </c>
       <c r="F21">
-        <v>2801.614899269051</v>
+        <v>2949.068315020054</v>
       </c>
       <c r="G21">
         <v>1291.1</v>
@@ -3128,28 +3128,28 @@
         <v>1122.12</v>
       </c>
       <c r="M21">
-        <v>145.1236517821368</v>
+        <v>152.7617387180388</v>
       </c>
       <c r="N21">
-        <v>976.996348217863</v>
+        <v>969.3582612819611</v>
       </c>
       <c r="O21">
-        <v>252.0650578402087</v>
+        <v>250.094431410746</v>
       </c>
       <c r="P21">
-        <v>724.9312903776544</v>
+        <v>719.2638298712151</v>
       </c>
       <c r="Q21">
-        <v>1042.131290377654</v>
+        <v>1036.463829871215</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07710598728419504</v>
+        <v>0.07741131760876643</v>
       </c>
       <c r="T21">
-        <v>0.7230020158012713</v>
+        <v>0.730053524451881</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.732164855419664</v>
+        <v>7.34555661264868</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06961617408701315</v>
+        <v>0.06947373447382832</v>
       </c>
       <c r="C22">
-        <v>11369.73618113083</v>
+        <v>11300.66757581899</v>
       </c>
       <c r="D22">
-        <v>13027.70449615089</v>
+        <v>13106.08930659005</v>
       </c>
       <c r="E22">
-        <v>-3447.173260080214</v>
+        <v>-3299.719844329211</v>
       </c>
       <c r="F22">
-        <v>2949.068315020054</v>
+        <v>3096.521730771057</v>
       </c>
       <c r="G22">
         <v>1291.1</v>
@@ -3210,28 +3210,28 @@
         <v>1122.12</v>
       </c>
       <c r="M22">
-        <v>152.7617387180388</v>
+        <v>160.3998256539408</v>
       </c>
       <c r="N22">
-        <v>969.3582612819611</v>
+        <v>961.7201743460591</v>
       </c>
       <c r="O22">
-        <v>250.094431410746</v>
+        <v>248.1238049812833</v>
       </c>
       <c r="P22">
-        <v>719.2638298712151</v>
+        <v>713.5963693647759</v>
       </c>
       <c r="Q22">
-        <v>1036.463829871215</v>
+        <v>1030.796369364776</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07741131760876643</v>
+        <v>0.07772437781497256</v>
       </c>
       <c r="T22">
-        <v>0.730053524451881</v>
+        <v>0.7372835523088352</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.34555661264868</v>
+        <v>6.995768202522552</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06947373447382831</v>
+        <v>0.0696088028606435</v>
       </c>
       <c r="C23">
-        <v>11300.667575819</v>
+        <v>11078.86273843381</v>
       </c>
       <c r="D23">
-        <v>13106.08930659005</v>
+        <v>13031.73788495587</v>
       </c>
       <c r="E23">
-        <v>-3299.719844329212</v>
+        <v>-3152.266428578209</v>
       </c>
       <c r="F23">
-        <v>3096.521730771056</v>
+        <v>3243.975146522059</v>
       </c>
       <c r="G23">
         <v>1291.1</v>
@@ -3292,45 +3292,45 @@
         <v>1122.12</v>
       </c>
       <c r="M23">
-        <v>160.3998256539407</v>
+        <v>173.5526703389302</v>
       </c>
       <c r="N23">
-        <v>961.7201743460591</v>
+        <v>948.5673296610697</v>
       </c>
       <c r="O23">
-        <v>248.1238049812833</v>
+        <v>244.730371052556</v>
       </c>
       <c r="P23">
-        <v>713.5963693647759</v>
+        <v>703.8369586085137</v>
       </c>
       <c r="Q23">
-        <v>1030.796369364776</v>
+        <v>1021.036958608514</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07772437781497255</v>
+        <v>0.07804546520595319</v>
       </c>
       <c r="T23">
-        <v>0.7372835523088351</v>
+        <v>0.7446989654954549</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.995768202522553</v>
+        <v>6.465587638661031</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0696088028606435</v>
+        <v>0.06947897724745866</v>
       </c>
       <c r="C24">
-        <v>11078.86273843381</v>
+        <v>11002.85891884136</v>
       </c>
       <c r="D24">
-        <v>13031.73788495587</v>
+        <v>13103.18748111442</v>
       </c>
       <c r="E24">
-        <v>-3152.266428578209</v>
+        <v>-3004.813012827206</v>
       </c>
       <c r="F24">
-        <v>3243.975146522059</v>
+        <v>3391.428562273062</v>
       </c>
       <c r="G24">
         <v>1291.1</v>
@@ -3374,28 +3374,28 @@
         <v>1122.12</v>
       </c>
       <c r="M24">
-        <v>173.5526703389302</v>
+        <v>181.4414280816088</v>
       </c>
       <c r="N24">
-        <v>948.5673296610697</v>
+        <v>940.6785719183911</v>
       </c>
       <c r="O24">
-        <v>244.730371052556</v>
+        <v>242.6950715549449</v>
       </c>
       <c r="P24">
-        <v>703.8369586085137</v>
+        <v>697.9835003634462</v>
       </c>
       <c r="Q24">
-        <v>1021.036958608514</v>
+        <v>1015.183500363446</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07804546520595319</v>
+        <v>0.07837489252916709</v>
       </c>
       <c r="T24">
-        <v>0.7446989654954549</v>
+        <v>0.752306986816792</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.465587638661031</v>
+        <v>6.184475132632291</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06947897724745866</v>
+        <v>0.06934915163427383</v>
       </c>
       <c r="C25">
-        <v>11002.85891884136</v>
+        <v>10927.64289727893</v>
       </c>
       <c r="D25">
-        <v>13103.18748111442</v>
+        <v>13175.42487530299</v>
       </c>
       <c r="E25">
-        <v>-3004.813012827206</v>
+        <v>-2857.359597076203</v>
       </c>
       <c r="F25">
-        <v>3391.428562273062</v>
+        <v>3538.881978024065</v>
       </c>
       <c r="G25">
         <v>1291.1</v>
@@ -3456,28 +3456,28 @@
         <v>1122.12</v>
       </c>
       <c r="M25">
-        <v>181.4414280816088</v>
+        <v>189.3301858242875</v>
       </c>
       <c r="N25">
-        <v>940.6785719183911</v>
+        <v>932.7898141757124</v>
       </c>
       <c r="O25">
-        <v>242.6950715549449</v>
+        <v>240.6597720573338</v>
       </c>
       <c r="P25">
-        <v>697.9835003634462</v>
+        <v>692.1300421183786</v>
       </c>
       <c r="Q25">
-        <v>1015.183500363446</v>
+        <v>1009.330042118379</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07837489252916709</v>
+        <v>0.07871298899246557</v>
       </c>
       <c r="T25">
-        <v>0.752306986816792</v>
+        <v>0.7601152192255327</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.184475132632291</v>
+        <v>5.926788668772612</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06934915163427383</v>
+        <v>0.069219326021089</v>
       </c>
       <c r="C26">
-        <v>10927.64289727893</v>
+        <v>10853.22777528012</v>
       </c>
       <c r="D26">
-        <v>13175.42487530299</v>
+        <v>13248.46316905519</v>
       </c>
       <c r="E26">
-        <v>-2857.359597076204</v>
+        <v>-2709.906181325201</v>
       </c>
       <c r="F26">
-        <v>3538.881978024064</v>
+        <v>3686.335393775067</v>
       </c>
       <c r="G26">
         <v>1291.1</v>
@@ -3538,28 +3538,28 @@
         <v>1122.12</v>
       </c>
       <c r="M26">
-        <v>189.3301858242874</v>
+        <v>197.2189435669661</v>
       </c>
       <c r="N26">
-        <v>932.7898141757124</v>
+        <v>924.9010564330338</v>
       </c>
       <c r="O26">
-        <v>240.6597720573338</v>
+        <v>238.6244725597227</v>
       </c>
       <c r="P26">
-        <v>692.1300421183786</v>
+        <v>686.276583873311</v>
       </c>
       <c r="Q26">
-        <v>1009.330042118379</v>
+        <v>1003.476583873311</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07871298899246557</v>
+        <v>0.079060101361452</v>
       </c>
       <c r="T26">
-        <v>0.7601152192255327</v>
+        <v>0.7681316711651732</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.926788668772613</v>
+        <v>5.689717122021707</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.069219326021089</v>
+        <v>0.06924383640790416</v>
       </c>
       <c r="C27">
-        <v>10853.22777528012</v>
+        <v>10691.92317274681</v>
       </c>
       <c r="D27">
-        <v>13248.46316905519</v>
+        <v>13234.61198227288</v>
       </c>
       <c r="E27">
-        <v>-2709.906181325201</v>
+        <v>-2562.452765574198</v>
       </c>
       <c r="F27">
-        <v>3686.335393775067</v>
+        <v>3833.78880952607</v>
       </c>
       <c r="G27">
         <v>1291.1</v>
@@ -3620,45 +3620,45 @@
         <v>1122.12</v>
       </c>
       <c r="M27">
-        <v>197.2189435669661</v>
+        <v>208.1747323572656</v>
       </c>
       <c r="N27">
-        <v>924.9010564330338</v>
+        <v>913.9452676427343</v>
       </c>
       <c r="O27">
-        <v>238.6244725597227</v>
+        <v>235.7978790518254</v>
       </c>
       <c r="P27">
-        <v>686.276583873311</v>
+        <v>678.1473885909088</v>
       </c>
       <c r="Q27">
-        <v>1003.476583873311</v>
+        <v>995.3473885909088</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.079060101361452</v>
+        <v>0.07941659514581643</v>
       </c>
       <c r="T27">
-        <v>0.7681316711651732</v>
+        <v>0.7763647839680472</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>5.689717122021707</v>
+        <v>5.390279537260259</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06924383640790416</v>
+        <v>0.06911994679471933</v>
       </c>
       <c r="C28">
-        <v>10691.92317274681</v>
+        <v>10614.77999284533</v>
       </c>
       <c r="D28">
-        <v>13234.61198227288</v>
+        <v>13304.9222181224</v>
       </c>
       <c r="E28">
-        <v>-2562.452765574198</v>
+        <v>-2414.999349823195</v>
       </c>
       <c r="F28">
-        <v>3833.78880952607</v>
+        <v>3981.242225277073</v>
       </c>
       <c r="G28">
         <v>1291.1</v>
@@ -3702,28 +3702,28 @@
         <v>1122.12</v>
       </c>
       <c r="M28">
-        <v>208.1747323572656</v>
+        <v>216.1814528325451</v>
       </c>
       <c r="N28">
-        <v>913.9452676427343</v>
+        <v>905.9385471674548</v>
       </c>
       <c r="O28">
-        <v>235.7978790518254</v>
+        <v>233.7321451692033</v>
       </c>
       <c r="P28">
-        <v>678.1473885909088</v>
+        <v>672.2064019982514</v>
       </c>
       <c r="Q28">
-        <v>995.3473885909088</v>
+        <v>989.4064019982515</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07941659514581643</v>
+        <v>0.07978285588317717</v>
       </c>
       <c r="T28">
-        <v>0.7763647839680472</v>
+        <v>0.7848234615052466</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.390279537260259</v>
+        <v>5.190639554398767</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06911994679471933</v>
+        <v>0.0689960571815345</v>
       </c>
       <c r="C29">
-        <v>10614.77999284533</v>
+        <v>10538.38786368098</v>
       </c>
       <c r="D29">
-        <v>13304.9222181224</v>
+        <v>13375.98350470906</v>
       </c>
       <c r="E29">
-        <v>-2414.999349823195</v>
+        <v>-2267.545934072193</v>
       </c>
       <c r="F29">
-        <v>3981.242225277073</v>
+        <v>4128.695641028075</v>
       </c>
       <c r="G29">
         <v>1291.1</v>
@@ -3784,28 +3784,28 @@
         <v>1122.12</v>
       </c>
       <c r="M29">
-        <v>216.1814528325451</v>
+        <v>224.1881733078245</v>
       </c>
       <c r="N29">
-        <v>905.9385471674548</v>
+        <v>897.9318266921754</v>
       </c>
       <c r="O29">
-        <v>233.7321451692033</v>
+        <v>231.6664112865813</v>
       </c>
       <c r="P29">
-        <v>672.2064019982514</v>
+        <v>666.2654154055941</v>
       </c>
       <c r="Q29">
-        <v>989.4064019982515</v>
+        <v>983.4654154055942</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07978285588317717</v>
+        <v>0.08015929052990903</v>
       </c>
       <c r="T29">
-        <v>0.7848234615052466</v>
+        <v>0.793517102307368</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.190639554398767</v>
+        <v>5.005259570313097</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0689960571815345</v>
+        <v>0.06887216756834968</v>
       </c>
       <c r="C30">
-        <v>10538.38786368098</v>
+        <v>10462.75888390703</v>
       </c>
       <c r="D30">
-        <v>13375.98350470906</v>
+        <v>13447.80794068611</v>
       </c>
       <c r="E30">
-        <v>-2267.545934072193</v>
+        <v>-2120.092518321189</v>
       </c>
       <c r="F30">
-        <v>4128.695641028075</v>
+        <v>4276.149056779079</v>
       </c>
       <c r="G30">
         <v>1291.1</v>
@@ -3866,28 +3866,28 @@
         <v>1122.12</v>
       </c>
       <c r="M30">
-        <v>224.1881733078245</v>
+        <v>232.194893783104</v>
       </c>
       <c r="N30">
-        <v>897.9318266921754</v>
+        <v>889.9251062168959</v>
       </c>
       <c r="O30">
-        <v>231.6664112865813</v>
+        <v>229.6006774039591</v>
       </c>
       <c r="P30">
-        <v>666.2654154055941</v>
+        <v>660.3244288129367</v>
       </c>
       <c r="Q30">
-        <v>983.4654154055942</v>
+        <v>977.5244288129368</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08015929052990903</v>
+        <v>0.08054632896950659</v>
       </c>
       <c r="T30">
-        <v>0.793517102307368</v>
+        <v>0.8024556343996901</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.005259570313097</v>
+        <v>4.832664412716094</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06887216756834967</v>
+        <v>0.06874827795516483</v>
       </c>
       <c r="C31">
-        <v>10462.75888390704</v>
+        <v>10387.90541344216</v>
       </c>
       <c r="D31">
-        <v>13447.80794068612</v>
+        <v>13520.40788597224</v>
       </c>
       <c r="E31">
-        <v>-2120.09251832119</v>
+        <v>-1972.639102570188</v>
       </c>
       <c r="F31">
-        <v>4276.149056779078</v>
+        <v>4423.60247253008</v>
       </c>
       <c r="G31">
         <v>1291.1</v>
@@ -3948,28 +3948,28 @@
         <v>1122.12</v>
       </c>
       <c r="M31">
-        <v>232.1948937831039</v>
+        <v>240.2016142583834</v>
       </c>
       <c r="N31">
-        <v>889.925106216896</v>
+        <v>881.9183857416165</v>
       </c>
       <c r="O31">
-        <v>229.6006774039592</v>
+        <v>227.5349435213371</v>
       </c>
       <c r="P31">
-        <v>660.3244288129368</v>
+        <v>654.3834422202794</v>
       </c>
       <c r="Q31">
-        <v>977.5244288129369</v>
+        <v>971.5834422202795</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08054632896950659</v>
+        <v>0.08094442565023549</v>
       </c>
       <c r="T31">
-        <v>0.8024556343996901</v>
+        <v>0.8116495531232215</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.832664412716094</v>
+        <v>4.671575598958892</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06874827795516483</v>
+        <v>0.06862438834197999</v>
       </c>
       <c r="C32">
-        <v>10387.90541344216</v>
+        <v>10313.84008056098</v>
       </c>
       <c r="D32">
-        <v>13520.40788597224</v>
+        <v>13593.79596884206</v>
       </c>
       <c r="E32">
-        <v>-1972.639102570188</v>
+        <v>-1825.185686819185</v>
       </c>
       <c r="F32">
-        <v>4423.60247253008</v>
+        <v>4571.055888281083</v>
       </c>
       <c r="G32">
         <v>1291.1</v>
@@ -4030,28 +4030,28 @@
         <v>1122.12</v>
       </c>
       <c r="M32">
-        <v>240.2016142583834</v>
+        <v>248.2083347336628</v>
       </c>
       <c r="N32">
-        <v>881.9183857416165</v>
+        <v>873.9116652663371</v>
       </c>
       <c r="O32">
-        <v>227.5349435213371</v>
+        <v>225.469209638715</v>
       </c>
       <c r="P32">
-        <v>654.3834422202794</v>
+        <v>648.4424556276222</v>
       </c>
       <c r="Q32">
-        <v>971.5834422202795</v>
+        <v>965.6424556276222</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08094442565023549</v>
+        <v>0.08135406136518841</v>
       </c>
       <c r="T32">
-        <v>0.8116495531232215</v>
+        <v>0.8211099622445365</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.671575598958892</v>
+        <v>4.520879611895701</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06862438834197999</v>
+        <v>0.06850049872879517</v>
       </c>
       <c r="C33">
-        <v>10313.84008056098</v>
+        <v>10240.57578921705</v>
       </c>
       <c r="D33">
-        <v>13593.79596884206</v>
+        <v>13667.98509324914</v>
       </c>
       <c r="E33">
-        <v>-1825.185686819185</v>
+        <v>-1677.732271068182</v>
       </c>
       <c r="F33">
-        <v>4571.055888281083</v>
+        <v>4718.509304032086</v>
       </c>
       <c r="G33">
         <v>1291.1</v>
@@ -4112,28 +4112,28 @@
         <v>1122.12</v>
       </c>
       <c r="M33">
-        <v>248.2083347336628</v>
+        <v>256.2150552089423</v>
       </c>
       <c r="N33">
-        <v>873.9116652663371</v>
+        <v>865.9049447910577</v>
       </c>
       <c r="O33">
-        <v>225.469209638715</v>
+        <v>223.4034757560929</v>
       </c>
       <c r="P33">
-        <v>648.4424556276222</v>
+        <v>642.5014690349648</v>
       </c>
       <c r="Q33">
-        <v>965.6424556276222</v>
+        <v>959.7014690349648</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08135406136518841</v>
+        <v>0.08177574518940467</v>
       </c>
       <c r="T33">
-        <v>0.8211099622445365</v>
+        <v>0.8308486186929488</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.520879611895701</v>
+        <v>4.379602124023961</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06850049872879517</v>
+        <v>0.06862146911561035</v>
       </c>
       <c r="C34">
-        <v>10240.57578921705</v>
+        <v>10020.67211028017</v>
       </c>
       <c r="D34">
-        <v>13667.98509324914</v>
+        <v>13595.53483006326</v>
       </c>
       <c r="E34">
-        <v>-1677.732271068182</v>
+        <v>-1530.278855317179</v>
       </c>
       <c r="F34">
-        <v>4718.509304032086</v>
+        <v>4865.962719783089</v>
       </c>
       <c r="G34">
         <v>1291.1</v>
@@ -4194,45 +4194,45 @@
         <v>1122.12</v>
       </c>
       <c r="M34">
-        <v>256.2150552089423</v>
+        <v>269.0877384040048</v>
       </c>
       <c r="N34">
-        <v>865.9049447910577</v>
+        <v>853.0322615959951</v>
       </c>
       <c r="O34">
-        <v>223.4034757560929</v>
+        <v>220.0823234917667</v>
       </c>
       <c r="P34">
-        <v>642.5014690349648</v>
+        <v>632.9499381042284</v>
       </c>
       <c r="Q34">
-        <v>959.7014690349648</v>
+        <v>950.1499381042285</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08177574518940467</v>
+        <v>0.0822100165904632</v>
       </c>
       <c r="T34">
-        <v>0.8308486186929488</v>
+        <v>0.8408779813040002</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.379602124023961</v>
+        <v>4.170089676532431</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06862146911561035</v>
+        <v>0.0685049995024255</v>
       </c>
       <c r="C35">
-        <v>10020.67211028017</v>
+        <v>9942.959576158759</v>
       </c>
       <c r="D35">
-        <v>13595.53483006326</v>
+        <v>13665.27571169285</v>
       </c>
       <c r="E35">
-        <v>-1530.278855317179</v>
+        <v>-1382.825439566176</v>
       </c>
       <c r="F35">
-        <v>4865.962719783089</v>
+        <v>5013.416135534092</v>
       </c>
       <c r="G35">
         <v>1291.1</v>
@@ -4276,28 +4276,28 @@
         <v>1122.12</v>
       </c>
       <c r="M35">
-        <v>269.0877384040048</v>
+        <v>277.2419122950353</v>
       </c>
       <c r="N35">
-        <v>853.0322615959951</v>
+        <v>844.8780877049646</v>
       </c>
       <c r="O35">
-        <v>220.0823234917667</v>
+        <v>217.9785466278809</v>
       </c>
       <c r="P35">
-        <v>632.9499381042284</v>
+        <v>626.8995410770838</v>
       </c>
       <c r="Q35">
-        <v>950.1499381042285</v>
+        <v>944.0995410770838</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0822100165904632</v>
+        <v>0.08265744773094774</v>
       </c>
       <c r="T35">
-        <v>0.8408779813040002</v>
+        <v>0.8512112639941745</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.170089676532431</v>
+        <v>4.04743998016383</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0685049995024255</v>
+        <v>0.06838852988924067</v>
       </c>
       <c r="C36">
-        <v>9942.959576158759</v>
+        <v>9865.96622947861</v>
       </c>
       <c r="D36">
-        <v>13665.27571169285</v>
+        <v>13735.73578076371</v>
       </c>
       <c r="E36">
-        <v>-1382.825439566176</v>
+        <v>-1235.372023815174</v>
       </c>
       <c r="F36">
-        <v>5013.416135534092</v>
+        <v>5160.869551285095</v>
       </c>
       <c r="G36">
         <v>1291.1</v>
@@ -4358,28 +4358,28 @@
         <v>1122.12</v>
       </c>
       <c r="M36">
-        <v>277.2419122950353</v>
+        <v>285.3960861860658</v>
       </c>
       <c r="N36">
-        <v>844.8780877049646</v>
+        <v>836.7239138139341</v>
       </c>
       <c r="O36">
-        <v>217.9785466278809</v>
+        <v>215.874769763995</v>
       </c>
       <c r="P36">
-        <v>626.8995410770838</v>
+        <v>620.8491440499391</v>
       </c>
       <c r="Q36">
-        <v>944.0995410770838</v>
+        <v>938.0491440499392</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08265744773094774</v>
+        <v>0.0831186459834472</v>
       </c>
       <c r="T36">
-        <v>0.8512112639941745</v>
+        <v>0.8618624938440465</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.04743998016383</v>
+        <v>3.931798837873434</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06838852988924067</v>
+        <v>0.06827206027605585</v>
       </c>
       <c r="C37">
-        <v>9865.96622947861</v>
+        <v>9789.703252589992</v>
       </c>
       <c r="D37">
-        <v>13735.73578076371</v>
+        <v>13806.92621962609</v>
       </c>
       <c r="E37">
-        <v>-1235.372023815174</v>
+        <v>-1087.918608064171</v>
       </c>
       <c r="F37">
-        <v>5160.869551285095</v>
+        <v>5308.322967036097</v>
       </c>
       <c r="G37">
         <v>1291.1</v>
@@ -4440,28 +4440,28 @@
         <v>1122.12</v>
       </c>
       <c r="M37">
-        <v>285.3960861860658</v>
+        <v>293.5502600770962</v>
       </c>
       <c r="N37">
-        <v>836.7239138139341</v>
+        <v>828.5697399229036</v>
       </c>
       <c r="O37">
-        <v>215.874769763995</v>
+        <v>213.7709929001091</v>
       </c>
       <c r="P37">
-        <v>620.8491440499391</v>
+        <v>614.7987470227945</v>
       </c>
       <c r="Q37">
-        <v>938.0491440499392</v>
+        <v>931.9987470227945</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0831186459834472</v>
+        <v>0.08359425668133727</v>
       </c>
       <c r="T37">
-        <v>0.8618624938440465</v>
+        <v>0.8728465746267269</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.931798837873434</v>
+        <v>3.822582203488061</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06827206027605585</v>
+        <v>0.06815559066287102</v>
       </c>
       <c r="C38">
-        <v>9789.703252589992</v>
+        <v>9714.182060877341</v>
       </c>
       <c r="D38">
-        <v>13806.92621962609</v>
+        <v>13878.85844366444</v>
       </c>
       <c r="E38">
-        <v>-1087.918608064172</v>
+        <v>-940.4651923131687</v>
       </c>
       <c r="F38">
-        <v>5308.322967036096</v>
+        <v>5455.776382787099</v>
       </c>
       <c r="G38">
         <v>1291.1</v>
@@ -4522,28 +4522,28 @@
         <v>1122.12</v>
       </c>
       <c r="M38">
-        <v>293.5502600770961</v>
+        <v>301.7044339681266</v>
       </c>
       <c r="N38">
-        <v>828.5697399229038</v>
+        <v>820.4155660318733</v>
       </c>
       <c r="O38">
-        <v>213.7709929001092</v>
+        <v>211.6672160362233</v>
       </c>
       <c r="P38">
-        <v>614.7987470227946</v>
+        <v>608.74834999565</v>
       </c>
       <c r="Q38">
-        <v>931.9987470227946</v>
+        <v>925.94834999565</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08359425668133727</v>
+        <v>0.0840849661315413</v>
       </c>
       <c r="T38">
-        <v>0.8728465746267269</v>
+        <v>0.8841793563866354</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.822582203488062</v>
+        <v>3.719269170961357</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06815559066287102</v>
+        <v>0.06803912104968619</v>
       </c>
       <c r="C39">
-        <v>9714.182060877341</v>
+        <v>9639.414308861393</v>
       </c>
       <c r="D39">
-        <v>13878.85844366444</v>
+        <v>13951.54410739949</v>
       </c>
       <c r="E39">
-        <v>-940.4651923131687</v>
+        <v>-793.0117765621662</v>
       </c>
       <c r="F39">
-        <v>5455.776382787099</v>
+        <v>5603.229798538102</v>
       </c>
       <c r="G39">
         <v>1291.1</v>
@@ -4604,28 +4604,28 @@
         <v>1122.12</v>
       </c>
       <c r="M39">
-        <v>301.7044339681266</v>
+        <v>309.8586078591571</v>
       </c>
       <c r="N39">
-        <v>820.4155660318733</v>
+        <v>812.2613921408429</v>
       </c>
       <c r="O39">
-        <v>211.6672160362233</v>
+        <v>209.5634391723375</v>
       </c>
       <c r="P39">
-        <v>608.74834999565</v>
+        <v>602.6979529685054</v>
       </c>
       <c r="Q39">
-        <v>925.94834999565</v>
+        <v>919.8979529685055</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0840849661315413</v>
+        <v>0.08459150491884869</v>
       </c>
       <c r="T39">
-        <v>0.8841793563866354</v>
+        <v>0.8958777117517021</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.719269170961357</v>
+        <v>3.621393666462374</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06803912104968619</v>
+        <v>0.06792265143650136</v>
       </c>
       <c r="C40">
-        <v>9639.414308861393</v>
+        <v>9565.411896494137</v>
       </c>
       <c r="D40">
-        <v>13951.54410739949</v>
+        <v>14024.99511078324</v>
       </c>
       <c r="E40">
-        <v>-793.0117765621662</v>
+        <v>-645.5583608111629</v>
       </c>
       <c r="F40">
-        <v>5603.229798538102</v>
+        <v>5750.683214289105</v>
       </c>
       <c r="G40">
         <v>1291.1</v>
@@ -4686,28 +4686,28 @@
         <v>1122.12</v>
       </c>
       <c r="M40">
-        <v>309.8586078591571</v>
+        <v>318.0127817501875</v>
       </c>
       <c r="N40">
-        <v>812.2613921408429</v>
+        <v>804.1072182498124</v>
       </c>
       <c r="O40">
-        <v>209.5634391723375</v>
+        <v>207.4596623084516</v>
       </c>
       <c r="P40">
-        <v>602.6979529685054</v>
+        <v>596.6475559413608</v>
       </c>
       <c r="Q40">
-        <v>919.8979529685055</v>
+        <v>913.8475559413608</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08459150491884869</v>
+        <v>0.08511465153524814</v>
       </c>
       <c r="T40">
-        <v>0.8958777117517021</v>
+        <v>0.907959619751689</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.621393666462374</v>
+        <v>3.528537418604365</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06792265143650136</v>
+        <v>0.06780618182331653</v>
       </c>
       <c r="C41">
-        <v>9565.411896494137</v>
+        <v>9492.186975653656</v>
       </c>
       <c r="D41">
-        <v>14024.99511078324</v>
+        <v>14099.22360569376</v>
       </c>
       <c r="E41">
-        <v>-645.5583608111629</v>
+        <v>-498.1049450601604</v>
       </c>
       <c r="F41">
-        <v>5750.683214289105</v>
+        <v>5898.136630040108</v>
       </c>
       <c r="G41">
         <v>1291.1</v>
@@ -4768,28 +4768,28 @@
         <v>1122.12</v>
       </c>
       <c r="M41">
-        <v>318.0127817501875</v>
+        <v>326.166955641218</v>
       </c>
       <c r="N41">
-        <v>804.1072182498124</v>
+        <v>795.9530443587819</v>
       </c>
       <c r="O41">
-        <v>207.4596623084516</v>
+        <v>205.3558854445657</v>
       </c>
       <c r="P41">
-        <v>596.6475559413608</v>
+        <v>590.5971589142162</v>
       </c>
       <c r="Q41">
-        <v>913.8475559413608</v>
+        <v>907.7971589142162</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08511465153524814</v>
+        <v>0.08565523637219422</v>
       </c>
       <c r="T41">
-        <v>0.907959619751689</v>
+        <v>0.9204442580183423</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.528537418604365</v>
+        <v>3.440323983139256</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06780618182331653</v>
+        <v>0.0676897122101317</v>
       </c>
       <c r="C42">
-        <v>9492.186975653656</v>
+        <v>9419.751956846287</v>
       </c>
       <c r="D42">
-        <v>14099.22360569376</v>
+        <v>14174.2420026374</v>
       </c>
       <c r="E42">
-        <v>-498.1049450601604</v>
+        <v>-350.6515293091579</v>
       </c>
       <c r="F42">
-        <v>5898.136630040108</v>
+        <v>6045.59004579111</v>
       </c>
       <c r="G42">
         <v>1291.1</v>
@@ -4850,28 +4850,28 @@
         <v>1122.12</v>
       </c>
       <c r="M42">
-        <v>326.166955641218</v>
+        <v>334.3211295322484</v>
       </c>
       <c r="N42">
-        <v>795.9530443587819</v>
+        <v>787.7988704677515</v>
       </c>
       <c r="O42">
-        <v>205.3558854445657</v>
+        <v>203.2521085806799</v>
       </c>
       <c r="P42">
-        <v>590.5971589142162</v>
+        <v>584.5467618870716</v>
       </c>
       <c r="Q42">
-        <v>907.7971589142162</v>
+        <v>901.7467618870717</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08565523637219422</v>
+        <v>0.08621414611886728</v>
       </c>
       <c r="T42">
-        <v>0.9204442580183423</v>
+        <v>0.9333521043618311</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.440323983139256</v>
+        <v>3.356413642087079</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0676897122101317</v>
+        <v>0.06757324259694686</v>
       </c>
       <c r="C43">
-        <v>9419.751956846287</v>
+        <v>9348.119516123923</v>
       </c>
       <c r="D43">
-        <v>14174.2420026374</v>
+        <v>14250.06297766604</v>
       </c>
       <c r="E43">
-        <v>-350.6515293091579</v>
+        <v>-203.1981135581545</v>
       </c>
       <c r="F43">
-        <v>6045.59004579111</v>
+        <v>6193.043461542114</v>
       </c>
       <c r="G43">
         <v>1291.1</v>
@@ -4932,28 +4932,28 @@
         <v>1122.12</v>
       </c>
       <c r="M43">
-        <v>334.3211295322484</v>
+        <v>342.4753034232789</v>
       </c>
       <c r="N43">
-        <v>787.7988704677515</v>
+        <v>779.644696576721</v>
       </c>
       <c r="O43">
-        <v>203.2521085806799</v>
+        <v>201.148331716794</v>
       </c>
       <c r="P43">
-        <v>584.5467618870716</v>
+        <v>578.496364859927</v>
       </c>
       <c r="Q43">
-        <v>901.7467618870717</v>
+        <v>895.696364859927</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08621414611886728</v>
+        <v>0.08679232861542563</v>
       </c>
       <c r="T43">
-        <v>0.9333521043618311</v>
+        <v>0.9467050488550955</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.356413642087079</v>
+        <v>3.276499031561196</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06757324259694687</v>
+        <v>0.06745677298376203</v>
       </c>
       <c r="C44">
-        <v>9348.119516123914</v>
+        <v>9277.30260222445</v>
       </c>
       <c r="D44">
-        <v>14250.06297766603</v>
+        <v>14326.69947951757</v>
       </c>
       <c r="E44">
-        <v>-203.1981135581555</v>
+        <v>-55.74469780715299</v>
       </c>
       <c r="F44">
-        <v>6193.043461542113</v>
+        <v>6340.496877293115</v>
       </c>
       <c r="G44">
         <v>1291.1</v>
@@ -5014,28 +5014,28 @@
         <v>1122.12</v>
       </c>
       <c r="M44">
-        <v>342.4753034232788</v>
+        <v>350.6294773143093</v>
       </c>
       <c r="N44">
-        <v>779.6446965767211</v>
+        <v>771.4905226856906</v>
       </c>
       <c r="O44">
-        <v>201.148331716794</v>
+        <v>199.0445548529082</v>
       </c>
       <c r="P44">
-        <v>578.4963648599271</v>
+        <v>572.4459678327825</v>
       </c>
       <c r="Q44">
-        <v>895.6963648599271</v>
+        <v>889.6459678327825</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08679232861542563</v>
+        <v>0.08739079821712636</v>
       </c>
       <c r="T44">
-        <v>0.9467050488550955</v>
+        <v>0.9605265177165446</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.276499031561196</v>
+        <v>3.200301379664424</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06745677298376203</v>
+        <v>0.0673403033705772</v>
       </c>
       <c r="C45">
-        <v>9277.30260222445</v>
+        <v>9207.314443943957</v>
       </c>
       <c r="D45">
-        <v>14326.69947951757</v>
+        <v>14404.16473698808</v>
       </c>
       <c r="E45">
-        <v>-55.74469780715299</v>
+        <v>91.70871794385039</v>
       </c>
       <c r="F45">
-        <v>6340.496877293115</v>
+        <v>6487.950293044119</v>
       </c>
       <c r="G45">
         <v>1291.1</v>
@@ -5096,28 +5096,28 @@
         <v>1122.12</v>
       </c>
       <c r="M45">
-        <v>350.6294773143093</v>
+        <v>358.7836512053398</v>
       </c>
       <c r="N45">
-        <v>771.4905226856906</v>
+        <v>763.3363487946601</v>
       </c>
       <c r="O45">
-        <v>199.0445548529082</v>
+        <v>196.9407779890223</v>
       </c>
       <c r="P45">
-        <v>572.4459678327825</v>
+        <v>566.3955708056378</v>
       </c>
       <c r="Q45">
-        <v>889.6459678327825</v>
+        <v>883.5955708056379</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08739079821712636</v>
+        <v>0.08801064173317358</v>
       </c>
       <c r="T45">
-        <v>0.9605265177165446</v>
+        <v>0.9748416104659026</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.200301379664424</v>
+        <v>3.127567257399323</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0673403033705772</v>
+        <v>0.06722383375739238</v>
       </c>
       <c r="C46">
-        <v>9207.314443943957</v>
+        <v>9138.168557749308</v>
       </c>
       <c r="D46">
-        <v>14404.16473698808</v>
+        <v>14482.47226654443</v>
       </c>
       <c r="E46">
-        <v>91.70871794385039</v>
+        <v>239.1621336948529</v>
       </c>
       <c r="F46">
-        <v>6487.950293044119</v>
+        <v>6635.403708795121</v>
       </c>
       <c r="G46">
         <v>1291.1</v>
@@ -5178,28 +5178,28 @@
         <v>1122.12</v>
       </c>
       <c r="M46">
-        <v>358.7836512053398</v>
+        <v>366.9378250963702</v>
       </c>
       <c r="N46">
-        <v>763.3363487946601</v>
+        <v>755.1821749036296</v>
       </c>
       <c r="O46">
-        <v>196.9407779890223</v>
+        <v>194.8370011251365</v>
       </c>
       <c r="P46">
-        <v>566.3955708056378</v>
+        <v>560.3451737784932</v>
       </c>
       <c r="Q46">
-        <v>883.5955708056379</v>
+        <v>877.5451737784932</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08801064173317358</v>
+        <v>0.08865302501344068</v>
       </c>
       <c r="T46">
-        <v>0.9748416104659026</v>
+        <v>0.98967725204251</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.127567257399323</v>
+        <v>3.05806576279045</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06722383375739238</v>
+        <v>0.06796066414420755</v>
       </c>
       <c r="C47">
-        <v>9138.168557749308</v>
+        <v>8509.180582710866</v>
       </c>
       <c r="D47">
-        <v>14482.47226654443</v>
+        <v>14000.93770725699</v>
       </c>
       <c r="E47">
-        <v>239.1621336948529</v>
+        <v>386.6155494458553</v>
       </c>
       <c r="F47">
-        <v>6635.403708795121</v>
+        <v>6782.857124546123</v>
       </c>
       <c r="G47">
         <v>1291.1</v>
@@ -5260,45 +5260,45 @@
         <v>1122.12</v>
       </c>
       <c r="M47">
-        <v>366.9378250963702</v>
+        <v>392.049141798766</v>
       </c>
       <c r="N47">
-        <v>755.1821749036296</v>
+        <v>730.0708582012339</v>
       </c>
       <c r="O47">
-        <v>194.8370011251365</v>
+        <v>188.3582814159184</v>
       </c>
       <c r="P47">
-        <v>560.3451737784932</v>
+        <v>541.7125767853156</v>
       </c>
       <c r="Q47">
-        <v>877.5451737784932</v>
+        <v>858.9125767853157</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08865302501344068</v>
+        <v>0.08931920026705101</v>
       </c>
       <c r="T47">
-        <v>0.98967725204251</v>
+        <v>1.005062361825658</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.05806576279045</v>
+        <v>2.862192211036571</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06796066414420755</v>
+        <v>0.06786274453102271</v>
       </c>
       <c r="C48">
-        <v>8509.180582710866</v>
+        <v>8423.866598551969</v>
       </c>
       <c r="D48">
-        <v>14000.93770725699</v>
+        <v>14063.0771388491</v>
       </c>
       <c r="E48">
-        <v>386.6155494458553</v>
+        <v>534.0689651968587</v>
       </c>
       <c r="F48">
-        <v>6782.857124546123</v>
+        <v>6930.310540297127</v>
       </c>
       <c r="G48">
         <v>1291.1</v>
@@ -5342,28 +5342,28 @@
         <v>1122.12</v>
       </c>
       <c r="M48">
-        <v>392.049141798766</v>
+        <v>400.571949229174</v>
       </c>
       <c r="N48">
-        <v>730.0708582012339</v>
+        <v>721.548050770826</v>
       </c>
       <c r="O48">
-        <v>188.3582814159184</v>
+        <v>186.1593970988731</v>
       </c>
       <c r="P48">
-        <v>541.7125767853156</v>
+        <v>535.3886536719529</v>
       </c>
       <c r="Q48">
-        <v>858.9125767853157</v>
+        <v>852.5886536719529</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08931920026705101</v>
+        <v>0.09001051420947681</v>
       </c>
       <c r="T48">
-        <v>1.005062361825658</v>
+        <v>1.021028041789303</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.862192211036571</v>
+        <v>2.801294504418771</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06786274453102271</v>
+        <v>0.06776482491783788</v>
       </c>
       <c r="C49">
-        <v>8423.866598551969</v>
+        <v>8339.106651962487</v>
       </c>
       <c r="D49">
-        <v>14063.0771388491</v>
+        <v>14125.77060801062</v>
       </c>
       <c r="E49">
-        <v>534.0689651968587</v>
+        <v>681.5223809478612</v>
       </c>
       <c r="F49">
-        <v>6930.310540297127</v>
+        <v>7077.763956048129</v>
       </c>
       <c r="G49">
         <v>1291.1</v>
@@ -5424,28 +5424,28 @@
         <v>1122.12</v>
       </c>
       <c r="M49">
-        <v>400.571949229174</v>
+        <v>409.0947566595819</v>
       </c>
       <c r="N49">
-        <v>721.548050770826</v>
+        <v>713.025243340418</v>
       </c>
       <c r="O49">
-        <v>186.1593970988731</v>
+        <v>183.9605127818278</v>
       </c>
       <c r="P49">
-        <v>535.3886536719529</v>
+        <v>529.0647305585901</v>
       </c>
       <c r="Q49">
-        <v>852.5886536719529</v>
+        <v>846.2647305585901</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09001051420947681</v>
+        <v>0.09072841714968821</v>
       </c>
       <c r="T49">
-        <v>1.021028041789303</v>
+        <v>1.037607786366934</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.801294504418771</v>
+        <v>2.74293420224338</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06776482491783788</v>
+        <v>0.06766690530465305</v>
       </c>
       <c r="C50">
-        <v>8339.106651962487</v>
+        <v>8254.908185853566</v>
       </c>
       <c r="D50">
-        <v>14125.77060801062</v>
+        <v>14189.0255576527</v>
       </c>
       <c r="E50">
-        <v>681.5223809478603</v>
+        <v>828.9757966988636</v>
       </c>
       <c r="F50">
-        <v>7077.763956048128</v>
+        <v>7225.217371799132</v>
       </c>
       <c r="G50">
         <v>1291.1</v>
@@ -5506,28 +5506,28 @@
         <v>1122.12</v>
       </c>
       <c r="M50">
-        <v>409.0947566595818</v>
+        <v>417.6175640899899</v>
       </c>
       <c r="N50">
-        <v>713.025243340418</v>
+        <v>704.50243591001</v>
       </c>
       <c r="O50">
-        <v>183.9605127818278</v>
+        <v>181.7616284647826</v>
       </c>
       <c r="P50">
-        <v>529.0647305585901</v>
+        <v>522.7408074452275</v>
       </c>
       <c r="Q50">
-        <v>846.2647305585901</v>
+        <v>839.9408074452275</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09072841714968821</v>
+        <v>0.09147447314637852</v>
       </c>
       <c r="T50">
-        <v>1.037607786366934</v>
+        <v>1.054837717006432</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.74293420224338</v>
+        <v>2.686955953218005</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06766690530465305</v>
+        <v>0.06756898569146821</v>
       </c>
       <c r="C51">
-        <v>8254.908185853566</v>
+        <v>8171.278777052948</v>
       </c>
       <c r="D51">
-        <v>14189.0255576527</v>
+        <v>14252.84956460308</v>
       </c>
       <c r="E51">
-        <v>828.9757966988636</v>
+        <v>976.4292124498661</v>
       </c>
       <c r="F51">
-        <v>7225.217371799132</v>
+        <v>7372.670787550134</v>
       </c>
       <c r="G51">
         <v>1291.1</v>
@@ -5588,28 +5588,28 @@
         <v>1122.12</v>
       </c>
       <c r="M51">
-        <v>417.6175640899899</v>
+        <v>426.1403715203978</v>
       </c>
       <c r="N51">
-        <v>704.50243591001</v>
+        <v>695.9796284796021</v>
       </c>
       <c r="O51">
-        <v>181.7616284647826</v>
+        <v>179.5627441477373</v>
       </c>
       <c r="P51">
-        <v>522.7408074452275</v>
+        <v>516.4168843318647</v>
       </c>
       <c r="Q51">
-        <v>839.9408074452275</v>
+        <v>833.6168843318648</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09147447314637852</v>
+        <v>0.09225037138293643</v>
       </c>
       <c r="T51">
-        <v>1.054837717006432</v>
+        <v>1.072756844871511</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.686955953218005</v>
+        <v>2.633216834153645</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06756898569146821</v>
+        <v>0.06747106607828339</v>
       </c>
       <c r="C52">
-        <v>8171.278777052948</v>
+        <v>8088.226139330398</v>
       </c>
       <c r="D52">
-        <v>14252.84956460308</v>
+        <v>14317.25034263153</v>
       </c>
       <c r="E52">
-        <v>976.4292124498661</v>
+        <v>1123.882628200869</v>
       </c>
       <c r="F52">
-        <v>7372.670787550134</v>
+        <v>7520.124203301137</v>
       </c>
       <c r="G52">
         <v>1291.1</v>
@@ -5670,28 +5670,28 @@
         <v>1122.12</v>
       </c>
       <c r="M52">
-        <v>426.1403715203978</v>
+        <v>434.6631789508057</v>
       </c>
       <c r="N52">
-        <v>695.9796284796021</v>
+        <v>687.4568210491941</v>
       </c>
       <c r="O52">
-        <v>179.5627441477373</v>
+        <v>177.3638598306921</v>
       </c>
       <c r="P52">
-        <v>516.4168843318647</v>
+        <v>510.092961218502</v>
       </c>
       <c r="Q52">
-        <v>833.6168843318648</v>
+        <v>827.2929612185021</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09225037138293643</v>
+        <v>0.09305793893527221</v>
       </c>
       <c r="T52">
-        <v>1.072756844871511</v>
+        <v>1.091407365710675</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.633216834153645</v>
+        <v>2.581585131523181</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06747106607828339</v>
+        <v>0.06737314646509855</v>
       </c>
       <c r="C53">
-        <v>8088.226139330398</v>
+        <v>8005.758126505621</v>
       </c>
       <c r="D53">
-        <v>14317.25034263153</v>
+        <v>14382.23574555776</v>
       </c>
       <c r="E53">
-        <v>1123.882628200869</v>
+        <v>1271.336043951872</v>
       </c>
       <c r="F53">
-        <v>7520.124203301137</v>
+        <v>7667.57761905214</v>
       </c>
       <c r="G53">
         <v>1291.1</v>
@@ -5752,28 +5752,28 @@
         <v>1122.12</v>
       </c>
       <c r="M53">
-        <v>434.6631789508057</v>
+        <v>443.1859863812138</v>
       </c>
       <c r="N53">
-        <v>687.4568210491941</v>
+        <v>678.9340136187861</v>
       </c>
       <c r="O53">
-        <v>177.3638598306921</v>
+        <v>175.1649755136468</v>
       </c>
       <c r="P53">
-        <v>510.092961218502</v>
+        <v>503.7690381051393</v>
       </c>
       <c r="Q53">
-        <v>827.2929612185021</v>
+        <v>820.9690381051394</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09305793893527221</v>
+        <v>0.09389915513562198</v>
       </c>
       <c r="T53">
-        <v>1.091407365710675</v>
+        <v>1.110834991584803</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.581585131523181</v>
+        <v>2.531939263609273</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06737314646509855</v>
+        <v>0.06865163685191372</v>
       </c>
       <c r="C54">
-        <v>8005.758126505621</v>
+        <v>7053.655561953482</v>
       </c>
       <c r="D54">
-        <v>14382.23574555776</v>
+        <v>13577.58659675662</v>
       </c>
       <c r="E54">
-        <v>1271.336043951872</v>
+        <v>1418.789459702874</v>
       </c>
       <c r="F54">
-        <v>7667.57761905214</v>
+        <v>7815.031034803143</v>
       </c>
       <c r="G54">
         <v>1291.1</v>
@@ -5834,45 +5834,45 @@
         <v>1122.12</v>
       </c>
       <c r="M54">
-        <v>443.1859863812138</v>
+        <v>479.0614024334326</v>
       </c>
       <c r="N54">
-        <v>678.9340136187861</v>
+        <v>643.0585975665672</v>
       </c>
       <c r="O54">
-        <v>175.1649755136468</v>
+        <v>165.9091181721743</v>
       </c>
       <c r="P54">
-        <v>503.7690381051393</v>
+        <v>477.1494793943929</v>
       </c>
       <c r="Q54">
-        <v>820.9690381051394</v>
+        <v>794.3494793943929</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09389915513562198</v>
+        <v>0.0947761677700292</v>
       </c>
       <c r="T54">
-        <v>1.110834991584803</v>
+        <v>1.131089324942938</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.531939263609273</v>
+        <v>2.342330219675593</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06865163685191372</v>
+        <v>0.06857968723872888</v>
       </c>
       <c r="C55">
-        <v>7053.655561953482</v>
+        <v>6949.086936207821</v>
       </c>
       <c r="D55">
-        <v>13577.58659675662</v>
+        <v>13620.47138676197</v>
       </c>
       <c r="E55">
-        <v>1418.789459702874</v>
+        <v>1566.242875453878</v>
       </c>
       <c r="F55">
-        <v>7815.031034803143</v>
+        <v>7962.484450554146</v>
       </c>
       <c r="G55">
         <v>1291.1</v>
@@ -5916,28 +5916,28 @@
         <v>1122.12</v>
       </c>
       <c r="M55">
-        <v>479.0614024334326</v>
+        <v>488.1002968189691</v>
       </c>
       <c r="N55">
-        <v>643.0585975665672</v>
+        <v>634.0197031810308</v>
       </c>
       <c r="O55">
-        <v>165.9091181721743</v>
+        <v>163.5770834207059</v>
       </c>
       <c r="P55">
-        <v>477.1494793943929</v>
+        <v>470.4426197603248</v>
       </c>
       <c r="Q55">
-        <v>794.3494793943929</v>
+        <v>787.6426197603248</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0947761677700292</v>
+        <v>0.09569131138854106</v>
       </c>
       <c r="T55">
-        <v>1.131089324942938</v>
+        <v>1.152224281490556</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.342330219675593</v>
+        <v>2.298953734126045</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06857968723872888</v>
+        <v>0.06850773762554406</v>
       </c>
       <c r="C56">
-        <v>6949.086936207821</v>
+        <v>6844.79007192983</v>
       </c>
       <c r="D56">
-        <v>13620.47138676197</v>
+        <v>13663.62793823498</v>
       </c>
       <c r="E56">
-        <v>1566.242875453878</v>
+        <v>1713.69629120488</v>
       </c>
       <c r="F56">
-        <v>7962.484450554146</v>
+        <v>8109.937866305148</v>
       </c>
       <c r="G56">
         <v>1291.1</v>
@@ -5998,28 +5998,28 @@
         <v>1122.12</v>
       </c>
       <c r="M56">
-        <v>488.1002968189691</v>
+        <v>497.1391912045056</v>
       </c>
       <c r="N56">
-        <v>634.0197031810308</v>
+        <v>624.9808087954943</v>
       </c>
       <c r="O56">
-        <v>163.5770834207059</v>
+        <v>161.2450486692375</v>
       </c>
       <c r="P56">
-        <v>470.4426197603248</v>
+        <v>463.7357601262568</v>
       </c>
       <c r="Q56">
-        <v>787.6426197603248</v>
+        <v>780.9357601262568</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09569131138854106</v>
+        <v>0.09664712805676458</v>
       </c>
       <c r="T56">
-        <v>1.152224281490556</v>
+        <v>1.174298569440291</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.298953734126045</v>
+        <v>2.257154575323753</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06850773762554406</v>
+        <v>0.06959924401235923</v>
       </c>
       <c r="C57">
-        <v>6844.79007192983</v>
+        <v>6070.680735767884</v>
       </c>
       <c r="D57">
-        <v>13663.62793823498</v>
+        <v>13036.97201782403</v>
       </c>
       <c r="E57">
-        <v>1713.69629120488</v>
+        <v>1861.149706955883</v>
       </c>
       <c r="F57">
-        <v>8109.937866305148</v>
+        <v>8257.391282056151</v>
       </c>
       <c r="G57">
         <v>1291.1</v>
@@ -6080,45 +6080,45 @@
         <v>1122.12</v>
       </c>
       <c r="M57">
-        <v>497.1391912045056</v>
+        <v>529.2987811797993</v>
       </c>
       <c r="N57">
-        <v>624.9808087954943</v>
+        <v>592.8212188202006</v>
       </c>
       <c r="O57">
-        <v>161.2450486692375</v>
+        <v>152.9478744556118</v>
       </c>
       <c r="P57">
-        <v>463.7357601262568</v>
+        <v>439.8733443645888</v>
       </c>
       <c r="Q57">
-        <v>780.9357601262568</v>
+        <v>757.0733443645888</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09664712805676458</v>
+        <v>0.09764639093718007</v>
       </c>
       <c r="T57">
-        <v>1.174298569440291</v>
+        <v>1.197376234115013</v>
       </c>
       <c r="U57">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.257154575323753</v>
+        <v>2.120012438907965</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06959924401235923</v>
+        <v>0.06954807039917441</v>
       </c>
       <c r="C58">
-        <v>6070.680735767884</v>
+        <v>5951.32008511011</v>
       </c>
       <c r="D58">
-        <v>13036.97201782403</v>
+        <v>13065.06478291726</v>
       </c>
       <c r="E58">
-        <v>1861.149706955883</v>
+        <v>2008.603122706885</v>
       </c>
       <c r="F58">
-        <v>8257.391282056151</v>
+        <v>8404.844697807153</v>
       </c>
       <c r="G58">
         <v>1291.1</v>
@@ -6162,28 +6162,28 @@
         <v>1122.12</v>
       </c>
       <c r="M58">
-        <v>529.2987811797993</v>
+        <v>538.7505451294386</v>
       </c>
       <c r="N58">
-        <v>592.8212188202006</v>
+        <v>583.3694548705613</v>
       </c>
       <c r="O58">
-        <v>152.9478744556118</v>
+        <v>150.5093193566048</v>
       </c>
       <c r="P58">
-        <v>439.8733443645888</v>
+        <v>432.8601355139565</v>
       </c>
       <c r="Q58">
-        <v>757.0733443645888</v>
+        <v>750.0601355139565</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09764639093718007</v>
+        <v>0.09869213116087069</v>
       </c>
       <c r="T58">
-        <v>1.197376234115013</v>
+        <v>1.221527278542049</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.120012438907965</v>
+        <v>2.08281923822537</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06954807039917441</v>
+        <v>0.06949689678598957</v>
       </c>
       <c r="C59">
-        <v>5951.32008511011</v>
+        <v>5832.080767494994</v>
       </c>
       <c r="D59">
-        <v>13065.06478291726</v>
+        <v>13093.27888105315</v>
       </c>
       <c r="E59">
-        <v>2008.603122706885</v>
+        <v>2156.056538457889</v>
       </c>
       <c r="F59">
-        <v>8404.844697807153</v>
+        <v>8552.298113558158</v>
       </c>
       <c r="G59">
         <v>1291.1</v>
@@ -6244,28 +6244,28 @@
         <v>1122.12</v>
       </c>
       <c r="M59">
-        <v>538.7505451294386</v>
+        <v>548.202309079078</v>
       </c>
       <c r="N59">
-        <v>583.3694548705613</v>
+        <v>573.9176909209219</v>
       </c>
       <c r="O59">
-        <v>150.5093193566048</v>
+        <v>148.0707642575979</v>
       </c>
       <c r="P59">
-        <v>432.8601355139565</v>
+        <v>425.8469266633241</v>
       </c>
       <c r="Q59">
-        <v>750.0601355139565</v>
+        <v>743.0469266633241</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09869213116087069</v>
+        <v>0.09978766853807039</v>
       </c>
       <c r="T59">
-        <v>1.221527278542049</v>
+        <v>1.246828372703705</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.08281923822537</v>
+        <v>2.046908561704242</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06949689678598957</v>
+        <v>0.06944572317280473</v>
       </c>
       <c r="C60">
-        <v>5832.080767494996</v>
+        <v>5712.963570682341</v>
       </c>
       <c r="D60">
-        <v>13093.27888105315</v>
+        <v>13121.6150999915</v>
       </c>
       <c r="E60">
-        <v>2156.056538457888</v>
+        <v>2303.50995420889</v>
       </c>
       <c r="F60">
-        <v>8552.298113558156</v>
+        <v>8699.751529309158</v>
       </c>
       <c r="G60">
         <v>1291.1</v>
@@ -6326,28 +6326,28 @@
         <v>1122.12</v>
       </c>
       <c r="M60">
-        <v>548.2023090790778</v>
+        <v>557.6540730287171</v>
       </c>
       <c r="N60">
-        <v>573.917690920922</v>
+        <v>564.4659269712828</v>
       </c>
       <c r="O60">
-        <v>148.0707642575979</v>
+        <v>145.632209158591</v>
       </c>
       <c r="P60">
-        <v>425.8469266633242</v>
+        <v>418.8337178126918</v>
       </c>
       <c r="Q60">
-        <v>743.0469266633243</v>
+        <v>736.0337178126919</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09978766853807039</v>
+        <v>0.1009366467629384</v>
       </c>
       <c r="T60">
-        <v>1.246828372703704</v>
+        <v>1.273363666580563</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.046908561704242</v>
+        <v>2.012215196251629</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06944572317280473</v>
+        <v>0.07286710955961989</v>
       </c>
       <c r="C61">
-        <v>5712.963570682341</v>
+        <v>3906.887715869188</v>
       </c>
       <c r="D61">
-        <v>13121.6150999915</v>
+        <v>11462.99266092935</v>
       </c>
       <c r="E61">
-        <v>2303.50995420889</v>
+        <v>2450.963369959893</v>
       </c>
       <c r="F61">
-        <v>8699.751529309158</v>
+        <v>8847.204945060161</v>
       </c>
       <c r="G61">
         <v>1291.1</v>
@@ -6408,45 +6408,45 @@
         <v>1122.12</v>
       </c>
       <c r="M61">
-        <v>557.6540730287171</v>
+        <v>636.1140355498256</v>
       </c>
       <c r="N61">
-        <v>564.4659269712828</v>
+        <v>486.0059644501742</v>
       </c>
       <c r="O61">
-        <v>145.632209158591</v>
+        <v>125.389538828145</v>
       </c>
       <c r="P61">
-        <v>418.8337178126918</v>
+        <v>360.6164256220293</v>
       </c>
       <c r="Q61">
-        <v>736.0337178126919</v>
+        <v>677.8164256220293</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1009366467629384</v>
+        <v>0.1021430738990497</v>
       </c>
       <c r="T61">
-        <v>1.273363666580563</v>
+        <v>1.301225725151264</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.012215196251629</v>
+        <v>1.764023331178497</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07286710955961989</v>
+        <v>0.07463902994643508</v>
       </c>
       <c r="C62">
-        <v>3906.887715869188</v>
+        <v>3055.128003147045</v>
       </c>
       <c r="D62">
-        <v>11462.99266092935</v>
+        <v>10758.68636395821</v>
       </c>
       <c r="E62">
-        <v>2450.963369959893</v>
+        <v>2598.416785710895</v>
       </c>
       <c r="F62">
-        <v>8847.204945060161</v>
+        <v>8994.658360811163</v>
       </c>
       <c r="G62">
         <v>1291.1</v>
@@ -6490,45 +6490,45 @@
         <v>1122.12</v>
       </c>
       <c r="M62">
-        <v>636.1140355498256</v>
+        <v>681.7951037494862</v>
       </c>
       <c r="N62">
-        <v>486.0059644501742</v>
+        <v>440.3248962505137</v>
       </c>
       <c r="O62">
-        <v>125.389538828145</v>
+        <v>113.6038232326325</v>
       </c>
       <c r="P62">
-        <v>360.6164256220293</v>
+        <v>326.7210730178812</v>
       </c>
       <c r="Q62">
-        <v>677.8164256220293</v>
+        <v>643.9210730178812</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1021430738990497</v>
+        <v>0.1034113690934233</v>
       </c>
       <c r="T62">
-        <v>1.301225725151264</v>
+        <v>1.330516607238413</v>
       </c>
       <c r="U62">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.764023331178497</v>
+        <v>1.645831707838582</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07463902994643508</v>
+        <v>0.07467467033325023</v>
       </c>
       <c r="C63">
-        <v>3055.128003147045</v>
+        <v>2894.394998773594</v>
       </c>
       <c r="D63">
-        <v>10758.68636395821</v>
+        <v>10745.40677533576</v>
       </c>
       <c r="E63">
-        <v>2598.416785710895</v>
+        <v>2745.870201461898</v>
       </c>
       <c r="F63">
-        <v>8994.658360811163</v>
+        <v>9142.111776562166</v>
       </c>
       <c r="G63">
         <v>1291.1</v>
@@ -6572,28 +6572,28 @@
         <v>1122.12</v>
       </c>
       <c r="M63">
-        <v>681.7951037494862</v>
+        <v>692.9720726634122</v>
       </c>
       <c r="N63">
-        <v>440.3248962505137</v>
+        <v>429.1479273365877</v>
       </c>
       <c r="O63">
-        <v>113.6038232326325</v>
+        <v>110.7201652528396</v>
       </c>
       <c r="P63">
-        <v>326.7210730178812</v>
+        <v>318.4277620837481</v>
       </c>
       <c r="Q63">
-        <v>643.9210730178812</v>
+        <v>635.6277620837482</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1034113690934233</v>
+        <v>0.104746416666448</v>
       </c>
       <c r="T63">
-        <v>1.330516607238413</v>
+        <v>1.361349114698568</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.645831707838582</v>
+        <v>1.619286035131508</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07467467033325023</v>
+        <v>0.07471031072006541</v>
       </c>
       <c r="C64">
-        <v>2894.394998773594</v>
+        <v>2733.69473632946</v>
       </c>
       <c r="D64">
-        <v>10745.40677533576</v>
+        <v>10732.15992864263</v>
       </c>
       <c r="E64">
-        <v>2745.870201461898</v>
+        <v>2893.323617212902</v>
       </c>
       <c r="F64">
-        <v>9142.111776562166</v>
+        <v>9289.56519231317</v>
       </c>
       <c r="G64">
         <v>1291.1</v>
@@ -6654,28 +6654,28 @@
         <v>1122.12</v>
       </c>
       <c r="M64">
-        <v>692.9720726634122</v>
+        <v>704.1490415773384</v>
       </c>
       <c r="N64">
-        <v>429.1479273365877</v>
+        <v>417.9709584226615</v>
       </c>
       <c r="O64">
-        <v>110.7201652528396</v>
+        <v>107.8365072730467</v>
       </c>
       <c r="P64">
-        <v>318.4277620837481</v>
+        <v>310.1344511496148</v>
       </c>
       <c r="Q64">
-        <v>635.6277620837482</v>
+        <v>627.3344511496149</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.104746416666448</v>
+        <v>0.1061536289731498</v>
       </c>
       <c r="T64">
-        <v>1.361349114698568</v>
+        <v>1.393848244183597</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.619286035131508</v>
+        <v>1.593583082192912</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07471031072006541</v>
+        <v>0.07474595110688056</v>
       </c>
       <c r="C65">
-        <v>2733.69473632946</v>
+        <v>2573.027094871844</v>
       </c>
       <c r="D65">
-        <v>10732.15992864263</v>
+        <v>10718.94570293602</v>
       </c>
       <c r="E65">
-        <v>2893.323617212902</v>
+        <v>3040.777032963904</v>
       </c>
       <c r="F65">
-        <v>9289.56519231317</v>
+        <v>9437.018608064172</v>
       </c>
       <c r="G65">
         <v>1291.1</v>
@@ -6736,28 +6736,28 @@
         <v>1122.12</v>
       </c>
       <c r="M65">
-        <v>704.1490415773384</v>
+        <v>715.3260104912644</v>
       </c>
       <c r="N65">
-        <v>417.9709584226615</v>
+        <v>406.7939895087355</v>
       </c>
       <c r="O65">
-        <v>107.8365072730467</v>
+        <v>104.9528492932538</v>
       </c>
       <c r="P65">
-        <v>310.1344511496148</v>
+        <v>301.8411402154817</v>
       </c>
       <c r="Q65">
-        <v>627.3344511496149</v>
+        <v>619.0411402154818</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1061536289731498</v>
+        <v>0.1076390197413349</v>
       </c>
       <c r="T65">
-        <v>1.393848244183597</v>
+        <v>1.428152880862239</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.593583082192912</v>
+        <v>1.568683346533648</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07474595110688056</v>
+        <v>0.07478159149369575</v>
       </c>
       <c r="C66">
-        <v>2573.027094871844</v>
+        <v>2412.391954052822</v>
       </c>
       <c r="D66">
-        <v>10718.94570293602</v>
+        <v>10705.763977868</v>
       </c>
       <c r="E66">
-        <v>3040.777032963904</v>
+        <v>3188.230448714907</v>
       </c>
       <c r="F66">
-        <v>9437.018608064172</v>
+        <v>9584.472023815175</v>
       </c>
       <c r="G66">
         <v>1291.1</v>
@@ -6818,28 +6818,28 @@
         <v>1122.12</v>
       </c>
       <c r="M66">
-        <v>715.3260104912644</v>
+        <v>726.5029794051903</v>
       </c>
       <c r="N66">
-        <v>406.7939895087355</v>
+        <v>395.6170205948096</v>
       </c>
       <c r="O66">
-        <v>104.9528492932538</v>
+        <v>102.0691913134609</v>
       </c>
       <c r="P66">
-        <v>301.8411402154817</v>
+        <v>293.5478292813487</v>
       </c>
       <c r="Q66">
-        <v>619.0411402154818</v>
+        <v>610.7478292813487</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1076390197413349</v>
+        <v>0.1092092899819878</v>
       </c>
       <c r="T66">
-        <v>1.428152880862239</v>
+        <v>1.464417782493946</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.568683346533648</v>
+        <v>1.544549756586977</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07478159149369575</v>
+        <v>0.07481723188051093</v>
       </c>
       <c r="C67">
-        <v>2412.391954052822</v>
+        <v>2251.78919411577</v>
       </c>
       <c r="D67">
-        <v>10705.763977868</v>
+        <v>10692.61463368195</v>
       </c>
       <c r="E67">
-        <v>3188.230448714907</v>
+        <v>3335.683864465909</v>
       </c>
       <c r="F67">
-        <v>9584.472023815175</v>
+        <v>9731.925439566177</v>
       </c>
       <c r="G67">
         <v>1291.1</v>
@@ -6900,28 +6900,28 @@
         <v>1122.12</v>
       </c>
       <c r="M67">
-        <v>726.5029794051903</v>
+        <v>737.6799483191163</v>
       </c>
       <c r="N67">
-        <v>395.6170205948096</v>
+        <v>384.4400516808836</v>
       </c>
       <c r="O67">
-        <v>102.0691913134609</v>
+        <v>99.18553333366796</v>
       </c>
       <c r="P67">
-        <v>293.5478292813487</v>
+        <v>285.2545183472156</v>
       </c>
       <c r="Q67">
-        <v>610.7478292813487</v>
+        <v>602.4545183472156</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1092092899819878</v>
+        <v>0.1108719290603262</v>
       </c>
       <c r="T67">
-        <v>1.464417782493946</v>
+        <v>1.502815913633401</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.544549756586977</v>
+        <v>1.52114748754778</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07481723188051093</v>
+        <v>0.08191226026732609</v>
       </c>
       <c r="C68">
-        <v>2251.78919411577</v>
+        <v>3.542203173081361</v>
       </c>
       <c r="D68">
-        <v>10692.61463368195</v>
+        <v>8591.821058490261</v>
       </c>
       <c r="E68">
-        <v>3335.683864465909</v>
+        <v>3483.137280216912</v>
       </c>
       <c r="F68">
-        <v>9731.925439566177</v>
+        <v>9879.37885531718</v>
       </c>
       <c r="G68">
         <v>1291.1</v>
@@ -6982,45 +6982,45 @@
         <v>1122.12</v>
       </c>
       <c r="M68">
-        <v>737.6799483191163</v>
+        <v>889.1440969785461</v>
       </c>
       <c r="N68">
-        <v>384.4400516808836</v>
+        <v>232.9759030214537</v>
       </c>
       <c r="O68">
-        <v>99.18553333366796</v>
+        <v>60.10778297953507</v>
       </c>
       <c r="P68">
-        <v>285.2545183472156</v>
+        <v>172.8681200419187</v>
       </c>
       <c r="Q68">
-        <v>602.4545183472156</v>
+        <v>490.0681200419187</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1108719290603262</v>
+        <v>0.1126353341434124</v>
       </c>
       <c r="T68">
-        <v>1.502815913633401</v>
+        <v>1.543541204235852</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.258</v>
       </c>
       <c r="W68">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.52114748754778</v>
+        <v>1.262022661808297</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08191226026732609</v>
+        <v>0.09792088843270538</v>
       </c>
       <c r="C69">
-        <v>3.542203173081361</v>
+        <v>-2782.839149626267</v>
       </c>
       <c r="D69">
-        <v>8591.821058490261</v>
+        <v>5952.893121441918</v>
       </c>
       <c r="E69">
-        <v>3483.137280216912</v>
+        <v>3630.590695967916</v>
       </c>
       <c r="F69">
-        <v>9879.37885531718</v>
+        <v>10026.83227106818</v>
       </c>
       <c r="G69">
         <v>1291.1</v>
@@ -7064,45 +7064,45 @@
         <v>1122.12</v>
       </c>
       <c r="M69">
-        <v>889.1440969785461</v>
+        <v>1189.182307348687</v>
       </c>
       <c r="N69">
-        <v>232.9759030214537</v>
+        <v>-67.06230734868677</v>
       </c>
       <c r="O69">
-        <v>60.10778297953507</v>
+        <v>-17.30207529596119</v>
       </c>
       <c r="P69">
-        <v>172.8681200419187</v>
+        <v>-49.76023205272558</v>
       </c>
       <c r="Q69">
-        <v>490.0681200419187</v>
+        <v>267.4397679472744</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1126353341434124</v>
+        <v>0.1153333743485056</v>
       </c>
       <c r="T69">
-        <v>1.543541204235852</v>
+        <v>1.605851601582115</v>
       </c>
       <c r="U69">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.258</v>
+        <v>0.243450443393716</v>
       </c>
       <c r="W69">
-        <v>0.06677999999999999</v>
+        <v>0.08972677741350531</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.262022661808297</v>
+        <v>0.9436063697430851</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09792088843270538</v>
+        <v>0.09864888843270538</v>
       </c>
       <c r="C70">
-        <v>-2782.839149626267</v>
+        <v>-3012.294407250027</v>
       </c>
       <c r="D70">
-        <v>5952.893121441918</v>
+        <v>5870.89127956916</v>
       </c>
       <c r="E70">
-        <v>3630.590695967916</v>
+        <v>3778.044111718918</v>
       </c>
       <c r="F70">
-        <v>10026.83227106818</v>
+        <v>10174.28568681919</v>
       </c>
       <c r="G70">
         <v>1291.1</v>
@@ -7146,37 +7146,37 @@
         <v>1122.12</v>
       </c>
       <c r="M70">
-        <v>1189.182307348687</v>
+        <v>1206.670282456756</v>
       </c>
       <c r="N70">
-        <v>-67.06230734868677</v>
+        <v>-84.55028245675567</v>
       </c>
       <c r="O70">
-        <v>-17.30207529596119</v>
+        <v>-21.81397287384296</v>
       </c>
       <c r="P70">
-        <v>-49.76023205272558</v>
+        <v>-62.7363095829127</v>
       </c>
       <c r="Q70">
-        <v>267.4397679472744</v>
+        <v>254.4636904170873</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1153333743485056</v>
+        <v>0.1175763864242638</v>
       </c>
       <c r="T70">
-        <v>1.605851601582115</v>
+        <v>1.65765326614928</v>
       </c>
       <c r="U70">
         <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.243450443393716</v>
+        <v>0.2399221760981549</v>
       </c>
       <c r="W70">
-        <v>0.08972677741350531</v>
+        <v>0.09014522991475883</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9436063697430851</v>
+        <v>0.9299309151091274</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09864888843270538</v>
+        <v>0.0993768884327054</v>
       </c>
       <c r="C71">
-        <v>-3012.294407250027</v>
+        <v>-3239.521191267735</v>
       </c>
       <c r="D71">
-        <v>5870.89127956916</v>
+        <v>5791.117911302454</v>
       </c>
       <c r="E71">
-        <v>3778.044111718918</v>
+        <v>3925.497527469921</v>
       </c>
       <c r="F71">
-        <v>10174.28568681919</v>
+        <v>10321.73910257019</v>
       </c>
       <c r="G71">
         <v>1291.1</v>
@@ -7228,37 +7228,37 @@
         <v>1122.12</v>
       </c>
       <c r="M71">
-        <v>1206.670282456756</v>
+        <v>1224.158257564824</v>
       </c>
       <c r="N71">
-        <v>-84.55028245675567</v>
+        <v>-102.0382575648246</v>
       </c>
       <c r="O71">
-        <v>-21.81397287384296</v>
+        <v>-26.32587045172474</v>
       </c>
       <c r="P71">
-        <v>-62.7363095829127</v>
+        <v>-75.71238711309982</v>
       </c>
       <c r="Q71">
-        <v>254.4636904170873</v>
+        <v>241.4876128869002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1175763864242638</v>
+        <v>0.119968932638406</v>
       </c>
       <c r="T71">
-        <v>1.65765326614928</v>
+        <v>1.712908375020923</v>
       </c>
       <c r="U71">
         <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2399221760981549</v>
+        <v>0.2364947164396098</v>
       </c>
       <c r="W71">
-        <v>0.09014522991475883</v>
+        <v>0.09055172663026229</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9299309151091274</v>
+        <v>0.9166461877504256</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0993768884327054</v>
+        <v>0.1001048884327054</v>
       </c>
       <c r="C72">
-        <v>-3239.521191267735</v>
+        <v>-3464.609125035517</v>
       </c>
       <c r="D72">
-        <v>5791.117911302454</v>
+        <v>5713.483393285675</v>
       </c>
       <c r="E72">
-        <v>3925.497527469921</v>
+        <v>4072.950943220923</v>
       </c>
       <c r="F72">
-        <v>10321.73910257019</v>
+        <v>10469.19251832119</v>
       </c>
       <c r="G72">
         <v>1291.1</v>
@@ -7310,37 +7310,37 @@
         <v>1122.12</v>
       </c>
       <c r="M72">
-        <v>1224.158257564824</v>
+        <v>1241.646232672893</v>
       </c>
       <c r="N72">
-        <v>-102.0382575648246</v>
+        <v>-119.5262326728935</v>
       </c>
       <c r="O72">
-        <v>-26.32587045172474</v>
+        <v>-30.83776802960651</v>
       </c>
       <c r="P72">
-        <v>-75.71238711309982</v>
+        <v>-88.68846464328695</v>
       </c>
       <c r="Q72">
-        <v>241.4876128869002</v>
+        <v>228.5115353567131</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.119968932638406</v>
+        <v>0.1225264820397303</v>
       </c>
       <c r="T72">
-        <v>1.712908375020923</v>
+        <v>1.771974181056128</v>
       </c>
       <c r="U72">
         <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.2364947164396098</v>
+        <v>0.2331638049404604</v>
       </c>
       <c r="W72">
-        <v>0.09055172663026229</v>
+        <v>0.0909467727340614</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9166461877504256</v>
+        <v>0.9037356780637998</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1001048884327054</v>
+        <v>0.1008328884327054</v>
       </c>
       <c r="C73">
-        <v>-3464.609125035515</v>
+        <v>-3687.643089595949</v>
       </c>
       <c r="D73">
-        <v>5713.483393285675</v>
+        <v>5637.902844476243</v>
       </c>
       <c r="E73">
-        <v>4072.950943220922</v>
+        <v>4220.404358971924</v>
       </c>
       <c r="F73">
-        <v>10469.19251832119</v>
+        <v>10616.64593407219</v>
       </c>
       <c r="G73">
         <v>1291.1</v>
@@ -7392,37 +7392,37 @@
         <v>1122.12</v>
       </c>
       <c r="M73">
-        <v>1241.646232672893</v>
+        <v>1259.134207780962</v>
       </c>
       <c r="N73">
-        <v>-119.5262326728932</v>
+        <v>-137.0142077809621</v>
       </c>
       <c r="O73">
-        <v>-30.83776802960645</v>
+        <v>-35.34966560748823</v>
       </c>
       <c r="P73">
-        <v>-88.68846464328678</v>
+        <v>-101.6645421734739</v>
       </c>
       <c r="Q73">
-        <v>228.5115353567133</v>
+        <v>215.5354578265261</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1225264820397303</v>
+        <v>0.1252667135411492</v>
       </c>
       <c r="T73">
-        <v>1.771974181056127</v>
+        <v>1.835258973236703</v>
       </c>
       <c r="U73">
         <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.2331638049404604</v>
+        <v>0.2299254187607318</v>
       </c>
       <c r="W73">
-        <v>0.0909467727340614</v>
+        <v>0.09133084533497722</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9037356780638001</v>
+        <v>0.8911837936462472</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1008328884327054</v>
+        <v>0.1015608884327054</v>
       </c>
       <c r="C74">
-        <v>-3687.643089595949</v>
+        <v>-3908.703533250249</v>
       </c>
       <c r="D74">
-        <v>5637.902844476243</v>
+        <v>5564.295816572948</v>
       </c>
       <c r="E74">
-        <v>4220.404358971924</v>
+        <v>4367.857774722928</v>
       </c>
       <c r="F74">
-        <v>10616.64593407219</v>
+        <v>10764.0993498232</v>
       </c>
       <c r="G74">
         <v>1291.1</v>
@@ -7474,37 +7474,37 @@
         <v>1122.12</v>
       </c>
       <c r="M74">
-        <v>1259.134207780962</v>
+        <v>1276.622182889031</v>
       </c>
       <c r="N74">
-        <v>-137.0142077809621</v>
+        <v>-154.5021828890312</v>
       </c>
       <c r="O74">
-        <v>-35.34966560748823</v>
+        <v>-39.86156318537006</v>
       </c>
       <c r="P74">
-        <v>-101.6645421734739</v>
+        <v>-114.6406197036612</v>
       </c>
       <c r="Q74">
-        <v>215.5354578265261</v>
+        <v>202.5593802963389</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1252667135411492</v>
+        <v>0.1282099251537844</v>
       </c>
       <c r="T74">
-        <v>1.835258973236703</v>
+        <v>1.903231527801025</v>
       </c>
       <c r="U74">
         <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.2299254187607318</v>
+        <v>0.2267757554900368</v>
       </c>
       <c r="W74">
-        <v>0.09133084533497722</v>
+        <v>0.09170439539888164</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8911837936462472</v>
+        <v>0.8789757964730108</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1015608884327054</v>
+        <v>0.1022888884327054</v>
       </c>
       <c r="C75">
-        <v>-3908.703533250249</v>
+        <v>-4127.866757192834</v>
       </c>
       <c r="D75">
-        <v>5564.295816572948</v>
+        <v>5492.586008381365</v>
       </c>
       <c r="E75">
-        <v>4367.857774722928</v>
+        <v>4515.311190473931</v>
       </c>
       <c r="F75">
-        <v>10764.0993498232</v>
+        <v>10911.5527655742</v>
       </c>
       <c r="G75">
         <v>1291.1</v>
@@ -7556,37 +7556,37 @@
         <v>1122.12</v>
       </c>
       <c r="M75">
-        <v>1276.622182889031</v>
+        <v>1294.1101579971</v>
       </c>
       <c r="N75">
-        <v>-154.5021828890312</v>
+        <v>-171.9901579971001</v>
       </c>
       <c r="O75">
-        <v>-39.86156318537006</v>
+        <v>-44.37346076325183</v>
       </c>
       <c r="P75">
-        <v>-114.6406197036612</v>
+        <v>-127.6166972338483</v>
       </c>
       <c r="Q75">
-        <v>202.5593802963389</v>
+        <v>189.5833027661517</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1282099251537844</v>
+        <v>0.1313795376596991</v>
       </c>
       <c r="T75">
-        <v>1.903231527801025</v>
+        <v>1.976432740408757</v>
       </c>
       <c r="U75">
         <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.2267757554900368</v>
+        <v>0.223711218253685</v>
       </c>
       <c r="W75">
-        <v>0.09170439539888164</v>
+        <v>0.09206784951511297</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8789757964730108</v>
+        <v>0.8670977451693216</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1022888884327054</v>
+        <v>0.1030168884327054</v>
       </c>
       <c r="C76">
-        <v>-4127.866757192834</v>
+        <v>-4345.205179340235</v>
       </c>
       <c r="D76">
-        <v>5492.586008381365</v>
+        <v>5422.701001984966</v>
       </c>
       <c r="E76">
-        <v>4515.311190473931</v>
+        <v>4662.764606224933</v>
       </c>
       <c r="F76">
-        <v>10911.5527655742</v>
+        <v>11059.0061813252</v>
       </c>
       <c r="G76">
         <v>1291.1</v>
@@ -7638,37 +7638,37 @@
         <v>1122.12</v>
       </c>
       <c r="M76">
-        <v>1294.1101579971</v>
+        <v>1311.598133105169</v>
       </c>
       <c r="N76">
-        <v>-171.9901579971001</v>
+        <v>-189.478133105169</v>
       </c>
       <c r="O76">
-        <v>-44.37346076325183</v>
+        <v>-48.88535834113361</v>
       </c>
       <c r="P76">
-        <v>-127.6166972338483</v>
+        <v>-140.5927747640354</v>
       </c>
       <c r="Q76">
-        <v>189.5833027661517</v>
+        <v>176.6072252359646</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1313795376596991</v>
+        <v>0.1348027191660871</v>
       </c>
       <c r="T76">
-        <v>1.976432740408757</v>
+        <v>2.055490050025107</v>
       </c>
       <c r="U76">
         <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.223711218253685</v>
+        <v>0.2207284020103025</v>
       </c>
       <c r="W76">
-        <v>0.09206784951511297</v>
+        <v>0.09242161152157813</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8670977451693216</v>
+        <v>0.8555364419003972</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1030168884327054</v>
+        <v>0.1037448884327054</v>
       </c>
       <c r="C77">
-        <v>-4345.205179340235</v>
+        <v>-4560.787578272037</v>
       </c>
       <c r="D77">
-        <v>5422.701001984966</v>
+        <v>5354.572018804167</v>
       </c>
       <c r="E77">
-        <v>4662.764606224933</v>
+        <v>4810.218021975936</v>
       </c>
       <c r="F77">
-        <v>11059.0061813252</v>
+        <v>11206.4595970762</v>
       </c>
       <c r="G77">
         <v>1291.1</v>
@@ -7720,37 +7720,37 @@
         <v>1122.12</v>
       </c>
       <c r="M77">
-        <v>1311.598133105169</v>
+        <v>1329.086108213238</v>
       </c>
       <c r="N77">
-        <v>-189.478133105169</v>
+        <v>-206.9661082132379</v>
       </c>
       <c r="O77">
-        <v>-48.88535834113361</v>
+        <v>-53.39725591901539</v>
       </c>
       <c r="P77">
-        <v>-140.5927747640354</v>
+        <v>-153.5688522942226</v>
       </c>
       <c r="Q77">
-        <v>176.6072252359646</v>
+        <v>163.6311477057775</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1348027191660871</v>
+        <v>0.1385111657980074</v>
       </c>
       <c r="T77">
-        <v>2.055490050025107</v>
+        <v>2.141135468776154</v>
       </c>
       <c r="U77">
         <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.2207284020103025</v>
+        <v>0.2178240809312196</v>
       </c>
       <c r="W77">
-        <v>0.09242161152157813</v>
+        <v>0.09276606400155737</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8555364419003972</v>
+        <v>0.8442793834543394</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1037448884327054</v>
+        <v>0.1044728884327054</v>
       </c>
       <c r="C78">
-        <v>-4560.787578272037</v>
+        <v>-4774.679319011255</v>
       </c>
       <c r="D78">
-        <v>5354.572018804167</v>
+        <v>5288.133693815951</v>
       </c>
       <c r="E78">
-        <v>4810.218021975936</v>
+        <v>4957.671437726938</v>
       </c>
       <c r="F78">
-        <v>11206.4595970762</v>
+        <v>11353.91301282721</v>
       </c>
       <c r="G78">
         <v>1291.1</v>
@@ -7802,37 +7802,37 @@
         <v>1122.12</v>
       </c>
       <c r="M78">
-        <v>1329.086108213238</v>
+        <v>1346.574083321307</v>
       </c>
       <c r="N78">
-        <v>-206.9661082132379</v>
+        <v>-224.4540833213068</v>
       </c>
       <c r="O78">
-        <v>-53.39725591901539</v>
+        <v>-57.90915349689716</v>
       </c>
       <c r="P78">
-        <v>-153.5688522942226</v>
+        <v>-166.5449298244097</v>
       </c>
       <c r="Q78">
-        <v>163.6311477057775</v>
+        <v>150.6550701755904</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1385111657980074</v>
+        <v>0.1425420860500947</v>
       </c>
       <c r="T78">
-        <v>2.141135468776154</v>
+        <v>2.234228315244682</v>
       </c>
       <c r="U78">
         <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.2178240809312196</v>
+        <v>0.2149951967632817</v>
       </c>
       <c r="W78">
-        <v>0.09276606400155737</v>
+        <v>0.0931015696638748</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8442793834543394</v>
+        <v>0.8333147161367507</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1044728884327054</v>
+        <v>0.1052008884327054</v>
       </c>
       <c r="C79">
-        <v>-4774.679319011255</v>
+        <v>-4986.942562202119</v>
       </c>
       <c r="D79">
-        <v>5288.133693815951</v>
+        <v>5223.323866376092</v>
       </c>
       <c r="E79">
-        <v>4957.671437726938</v>
+        <v>5105.124853477942</v>
       </c>
       <c r="F79">
-        <v>11353.91301282721</v>
+        <v>11501.36642857821</v>
       </c>
       <c r="G79">
         <v>1291.1</v>
@@ -7884,37 +7884,37 @@
         <v>1122.12</v>
       </c>
       <c r="M79">
-        <v>1346.574083321307</v>
+        <v>1364.062058429376</v>
       </c>
       <c r="N79">
-        <v>-224.4540833213068</v>
+        <v>-241.9420584293759</v>
       </c>
       <c r="O79">
-        <v>-57.90915349689716</v>
+        <v>-62.42105107477899</v>
       </c>
       <c r="P79">
-        <v>-166.5449298244097</v>
+        <v>-179.5210073545969</v>
       </c>
       <c r="Q79">
-        <v>150.6550701755904</v>
+        <v>137.6789926454031</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1425420860500947</v>
+        <v>0.1469394535978263</v>
       </c>
       <c r="T79">
-        <v>2.234228315244682</v>
+        <v>2.335784147755804</v>
       </c>
       <c r="U79">
         <v>0.1186</v>
       </c>
       <c r="V79">
-        <v>0.2149951967632817</v>
+        <v>0.2122388480868293</v>
       </c>
       <c r="W79">
-        <v>0.0931015696638748</v>
+        <v>0.09342847261690204</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8333147161367507</v>
+        <v>0.8226311941349973</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1052008884327054</v>
+        <v>0.1059288884327054</v>
       </c>
       <c r="C80">
-        <v>-4986.942562202119</v>
+        <v>-5197.636458092344</v>
       </c>
       <c r="D80">
-        <v>5223.323866376092</v>
+        <v>5160.08338623687</v>
       </c>
       <c r="E80">
-        <v>5105.124853477942</v>
+        <v>5252.578269228945</v>
       </c>
       <c r="F80">
-        <v>11501.36642857821</v>
+        <v>11648.81984432921</v>
       </c>
       <c r="G80">
         <v>1291.1</v>
@@ -7966,37 +7966,37 @@
         <v>1122.12</v>
       </c>
       <c r="M80">
-        <v>1364.062058429376</v>
+        <v>1381.550033537445</v>
       </c>
       <c r="N80">
-        <v>-241.9420584293759</v>
+        <v>-259.4300335374448</v>
       </c>
       <c r="O80">
-        <v>-62.42105107477899</v>
+        <v>-66.93294865266077</v>
       </c>
       <c r="P80">
-        <v>-179.5210073545969</v>
+        <v>-192.4970848847841</v>
       </c>
       <c r="Q80">
-        <v>137.6789926454031</v>
+        <v>124.702915115216</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1469394535978263</v>
+        <v>0.1517556180548656</v>
       </c>
       <c r="T80">
-        <v>2.335784147755804</v>
+        <v>2.447011964315605</v>
       </c>
       <c r="U80">
         <v>0.1186</v>
       </c>
       <c r="V80">
-        <v>0.2122388480868293</v>
+        <v>0.2095522803895277</v>
       </c>
       <c r="W80">
-        <v>0.09342847261690204</v>
+        <v>0.09374709954580203</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8226311941349973</v>
+        <v>0.8122181410446809</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1059288884327054</v>
+        <v>0.1066568884327054</v>
       </c>
       <c r="C81">
-        <v>-5197.636458092344</v>
+        <v>-5406.817326592334</v>
       </c>
       <c r="D81">
-        <v>5160.08338623687</v>
+        <v>5098.355933487881</v>
       </c>
       <c r="E81">
-        <v>5252.578269228945</v>
+        <v>5400.031684979947</v>
       </c>
       <c r="F81">
-        <v>11648.81984432921</v>
+        <v>11796.27326008022</v>
       </c>
       <c r="G81">
         <v>1291.1</v>
@@ -8048,37 +8048,37 @@
         <v>1122.12</v>
       </c>
       <c r="M81">
-        <v>1381.550033537445</v>
+        <v>1399.038008645514</v>
       </c>
       <c r="N81">
-        <v>-259.4300335374448</v>
+        <v>-276.9180086455137</v>
       </c>
       <c r="O81">
-        <v>-66.93294865266077</v>
+        <v>-71.44484623054255</v>
       </c>
       <c r="P81">
-        <v>-192.4970848847841</v>
+        <v>-205.4731624149712</v>
       </c>
       <c r="Q81">
-        <v>124.702915115216</v>
+        <v>111.7268375850289</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1517556180548656</v>
+        <v>0.1570533989576089</v>
       </c>
       <c r="T81">
-        <v>2.447011964315605</v>
+        <v>2.569362562531385</v>
       </c>
       <c r="U81">
         <v>0.1186</v>
       </c>
       <c r="V81">
-        <v>0.2095522803895277</v>
+        <v>0.2069328768846586</v>
       </c>
       <c r="W81">
-        <v>0.09374709954580203</v>
+        <v>0.0940577608014795</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8122181410446809</v>
+        <v>0.8020654142816224</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1066568884327054</v>
+        <v>0.175773932034126</v>
       </c>
       <c r="C82">
-        <v>-5406.817326592334</v>
+        <v>-8265.455083969022</v>
       </c>
       <c r="D82">
-        <v>5098.355933487881</v>
+        <v>2387.171591862196</v>
       </c>
       <c r="E82">
-        <v>5400.031684979947</v>
+        <v>5547.48510073095</v>
       </c>
       <c r="F82">
-        <v>11796.27326008022</v>
+        <v>11943.72667583122</v>
       </c>
       <c r="G82">
         <v>1291.1</v>
@@ -8130,45 +8130,45 @@
         <v>1122.12</v>
       </c>
       <c r="M82">
-        <v>1399.038008645514</v>
+        <v>2398.300316506909</v>
       </c>
       <c r="N82">
-        <v>-276.9180086455137</v>
+        <v>-1276.180316506909</v>
       </c>
       <c r="O82">
-        <v>-71.44484623054255</v>
+        <v>-329.2545216587824</v>
       </c>
       <c r="P82">
-        <v>-205.4731624149712</v>
+        <v>-946.9257948481262</v>
       </c>
       <c r="Q82">
-        <v>111.7268375850289</v>
+        <v>-629.7257948481262</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1570533989576089</v>
+        <v>0.1724195968049599</v>
       </c>
       <c r="T82">
-        <v>2.569362562531385</v>
+        <v>2.924240110969051</v>
       </c>
       <c r="U82">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.2069328768846586</v>
+        <v>0.1207133893980646</v>
       </c>
       <c r="W82">
-        <v>0.0940577608014795</v>
+        <v>0.1765607514088686</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8020654142816224</v>
+        <v>0.4678813542560643</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.175773932034126</v>
+        <v>0.177323932034126</v>
       </c>
       <c r="C83">
-        <v>-8265.455083969022</v>
+        <v>-8441.041143795981</v>
       </c>
       <c r="D83">
-        <v>2387.171591862196</v>
+        <v>2359.038947786239</v>
       </c>
       <c r="E83">
-        <v>5547.48510073095</v>
+        <v>5694.938516481952</v>
       </c>
       <c r="F83">
-        <v>11943.72667583122</v>
+        <v>12091.18009158222</v>
       </c>
       <c r="G83">
         <v>1291.1</v>
@@ -8212,37 +8212,37 @@
         <v>1122.12</v>
       </c>
       <c r="M83">
-        <v>2398.300316506909</v>
+        <v>2427.90896238971</v>
       </c>
       <c r="N83">
-        <v>-1276.180316506909</v>
+        <v>-1305.78896238971</v>
       </c>
       <c r="O83">
-        <v>-329.2545216587824</v>
+        <v>-336.8935522965452</v>
       </c>
       <c r="P83">
-        <v>-946.9257948481262</v>
+        <v>-968.8954100931647</v>
       </c>
       <c r="Q83">
-        <v>-629.7257948481262</v>
+        <v>-651.6954100931647</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1724195968049599</v>
+        <v>0.1794540188496798</v>
       </c>
       <c r="T83">
-        <v>2.924240110969051</v>
+        <v>3.086697894911775</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1207133893980646</v>
+        <v>0.1192412748932101</v>
       </c>
       <c r="W83">
-        <v>0.1765607514088686</v>
+        <v>0.1768563520014434</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4678813542560643</v>
+        <v>0.4621754840822099</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.177323932034126</v>
+        <v>0.178873932034126</v>
       </c>
       <c r="C84">
-        <v>-8441.041143795981</v>
+        <v>-8615.971844640892</v>
       </c>
       <c r="D84">
-        <v>2359.038947786239</v>
+        <v>2331.561662692333</v>
       </c>
       <c r="E84">
-        <v>5694.938516481952</v>
+        <v>5842.391932232957</v>
       </c>
       <c r="F84">
-        <v>12091.18009158222</v>
+        <v>12238.63350733322</v>
       </c>
       <c r="G84">
         <v>1291.1</v>
@@ -8294,37 +8294,37 @@
         <v>1122.12</v>
       </c>
       <c r="M84">
-        <v>2427.90896238971</v>
+        <v>2457.517608272512</v>
       </c>
       <c r="N84">
-        <v>-1305.78896238971</v>
+        <v>-1335.397608272512</v>
       </c>
       <c r="O84">
-        <v>-336.8935522965452</v>
+        <v>-344.532582934308</v>
       </c>
       <c r="P84">
-        <v>-968.8954100931647</v>
+        <v>-990.8650253382036</v>
       </c>
       <c r="Q84">
-        <v>-651.6954100931647</v>
+        <v>-673.6650253382036</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1794540188496798</v>
+        <v>0.1873160199584846</v>
       </c>
       <c r="T84">
-        <v>3.086697894911775</v>
+        <v>3.268268359318351</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1192412748932101</v>
+        <v>0.1178046330270269</v>
       </c>
       <c r="W84">
-        <v>0.1768563520014434</v>
+        <v>0.177144829688173</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4621754840822099</v>
+        <v>0.456607104755918</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.178873932034126</v>
+        <v>0.180423932034126</v>
       </c>
       <c r="C85">
-        <v>-8615.971844640892</v>
+        <v>-8790.269823038134</v>
       </c>
       <c r="D85">
-        <v>2331.561662692333</v>
+        <v>2304.717100046094</v>
       </c>
       <c r="E85">
-        <v>5842.391932232957</v>
+        <v>5989.845347983959</v>
       </c>
       <c r="F85">
-        <v>12238.63350733322</v>
+        <v>12386.08692308423</v>
       </c>
       <c r="G85">
         <v>1291.1</v>
@@ -8376,37 +8376,37 @@
         <v>1122.12</v>
       </c>
       <c r="M85">
-        <v>2457.517608272512</v>
+        <v>2487.126254155313</v>
       </c>
       <c r="N85">
-        <v>-1335.397608272512</v>
+        <v>-1365.006254155313</v>
       </c>
       <c r="O85">
-        <v>-344.532582934308</v>
+        <v>-352.1716135720707</v>
       </c>
       <c r="P85">
-        <v>-990.8650253382036</v>
+        <v>-1012.834640583242</v>
       </c>
       <c r="Q85">
-        <v>-673.6650253382036</v>
+        <v>-695.6346405832421</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1873160199584846</v>
+        <v>0.1961607712058899</v>
       </c>
       <c r="T85">
-        <v>3.268268359318351</v>
+        <v>3.472535131775748</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1178046330270269</v>
+        <v>0.1164021969195623</v>
       </c>
       <c r="W85">
-        <v>0.177144829688173</v>
+        <v>0.1774264388585519</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.456607104755918</v>
+        <v>0.4511713058897762</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.180423932034126</v>
+        <v>0.181973932034126</v>
       </c>
       <c r="C86">
-        <v>-8790.26982303813</v>
+        <v>-8963.956684880533</v>
       </c>
       <c r="D86">
-        <v>2304.717100046095</v>
+        <v>2278.483653954694</v>
       </c>
       <c r="E86">
-        <v>5989.845347983957</v>
+        <v>6137.29876373496</v>
       </c>
       <c r="F86">
-        <v>12386.08692308423</v>
+        <v>12533.54033883523</v>
       </c>
       <c r="G86">
         <v>1291.1</v>
@@ -8458,37 +8458,37 @@
         <v>1122.12</v>
       </c>
       <c r="M86">
-        <v>2487.126254155312</v>
+        <v>2516.734900038114</v>
       </c>
       <c r="N86">
-        <v>-1365.006254155312</v>
+        <v>-1394.614900038114</v>
       </c>
       <c r="O86">
-        <v>-352.1716135720706</v>
+        <v>-359.8106442098334</v>
       </c>
       <c r="P86">
-        <v>-1012.834640583242</v>
+        <v>-1034.80425582828</v>
       </c>
       <c r="Q86">
-        <v>-695.6346405832419</v>
+        <v>-717.6042558282804</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1961607712058898</v>
+        <v>0.2061848226196158</v>
       </c>
       <c r="T86">
-        <v>3.472535131775746</v>
+        <v>3.704037473894129</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1164021969195623</v>
+        <v>0.1150327593087439</v>
       </c>
       <c r="W86">
-        <v>0.1774264388585519</v>
+        <v>0.1777014219308042</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4511713058897763</v>
+        <v>0.445863408173426</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.181973932034126</v>
+        <v>0.183523932034126</v>
       </c>
       <c r="C87">
-        <v>-8963.956684880533</v>
+        <v>-9137.053063415628</v>
       </c>
       <c r="D87">
-        <v>2278.483653954694</v>
+        <v>2252.840691170602</v>
       </c>
       <c r="E87">
-        <v>6137.29876373496</v>
+        <v>6284.752179485962</v>
       </c>
       <c r="F87">
-        <v>12533.54033883523</v>
+        <v>12680.99375458623</v>
       </c>
       <c r="G87">
         <v>1291.1</v>
@@ -8540,37 +8540,37 @@
         <v>1122.12</v>
       </c>
       <c r="M87">
-        <v>2516.734900038114</v>
+        <v>2546.343545920915</v>
       </c>
       <c r="N87">
-        <v>-1394.614900038114</v>
+        <v>-1424.223545920915</v>
       </c>
       <c r="O87">
-        <v>-359.8106442098334</v>
+        <v>-367.4496748475961</v>
       </c>
       <c r="P87">
-        <v>-1034.80425582828</v>
+        <v>-1056.773871073319</v>
       </c>
       <c r="Q87">
-        <v>-717.6042558282804</v>
+        <v>-739.573871073319</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2061848226196158</v>
+        <v>0.2176408813781597</v>
       </c>
       <c r="T87">
-        <v>3.704037473894129</v>
+        <v>3.968611579172281</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1150327593087439</v>
+        <v>0.1136951690842236</v>
       </c>
       <c r="W87">
-        <v>0.1777014219308042</v>
+        <v>0.1779700100478879</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.445863408173426</v>
+        <v>0.4406789499388513</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.183523932034126</v>
+        <v>0.1850739320341259</v>
       </c>
       <c r="C88">
-        <v>-9137.053063415628</v>
+        <v>-9309.578673369197</v>
       </c>
       <c r="D88">
-        <v>2252.840691170602</v>
+        <v>2227.768496968037</v>
       </c>
       <c r="E88">
-        <v>6284.752179485962</v>
+        <v>6432.205595236965</v>
       </c>
       <c r="F88">
-        <v>12680.99375458623</v>
+        <v>12828.44717033723</v>
       </c>
       <c r="G88">
         <v>1291.1</v>
@@ -8622,37 +8622,37 @@
         <v>1122.12</v>
       </c>
       <c r="M88">
-        <v>2546.343545920915</v>
+        <v>2575.952191803716</v>
       </c>
       <c r="N88">
-        <v>-1424.223545920915</v>
+        <v>-1453.832191803716</v>
       </c>
       <c r="O88">
-        <v>-367.4496748475961</v>
+        <v>-375.0887054853588</v>
       </c>
       <c r="P88">
-        <v>-1056.773871073319</v>
+        <v>-1078.743486318358</v>
       </c>
       <c r="Q88">
-        <v>-739.573871073319</v>
+        <v>-761.5434863183575</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2176408813781597</v>
+        <v>0.2308594107149413</v>
       </c>
       <c r="T88">
-        <v>3.968611579172281</v>
+        <v>4.273889392954764</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1136951690842236</v>
+        <v>0.112388328060267</v>
       </c>
       <c r="W88">
-        <v>0.1779700100478879</v>
+        <v>0.1782324237254984</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4406789499388513</v>
+        <v>0.4356136746521978</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1850739320341259</v>
+        <v>0.186623932034126</v>
       </c>
       <c r="C89">
-        <v>-9309.578673369197</v>
+        <v>-9481.552361494527</v>
       </c>
       <c r="D89">
-        <v>2227.768496968037</v>
+        <v>2203.24822459371</v>
       </c>
       <c r="E89">
-        <v>6432.205595236965</v>
+        <v>6579.659010987969</v>
       </c>
       <c r="F89">
-        <v>12828.44717033723</v>
+        <v>12975.90058608824</v>
       </c>
       <c r="G89">
         <v>1291.1</v>
@@ -8704,37 +8704,37 @@
         <v>1122.12</v>
       </c>
       <c r="M89">
-        <v>2575.952191803716</v>
+        <v>2605.560837686518</v>
       </c>
       <c r="N89">
-        <v>-1453.832191803716</v>
+        <v>-1483.440837686518</v>
       </c>
       <c r="O89">
-        <v>-375.0887054853588</v>
+        <v>-382.7277361231217</v>
       </c>
       <c r="P89">
-        <v>-1078.743486318358</v>
+        <v>-1100.713101563396</v>
       </c>
       <c r="Q89">
-        <v>-761.5434863183575</v>
+        <v>-783.5131015633963</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2308594107149413</v>
+        <v>0.2462810282745197</v>
       </c>
       <c r="T89">
-        <v>4.273889392954764</v>
+        <v>4.630046842367662</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.112388328060267</v>
+        <v>0.1111111879686731</v>
       </c>
       <c r="W89">
-        <v>0.1782324237254984</v>
+        <v>0.1784888734558905</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4356136746521978</v>
+        <v>0.4306635192584227</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.186623932034126</v>
+        <v>0.188173932034126</v>
       </c>
       <c r="C90">
-        <v>-9481.552361494527</v>
+        <v>-9652.99215381973</v>
       </c>
       <c r="D90">
-        <v>2203.24822459371</v>
+        <v>2179.261848019509</v>
       </c>
       <c r="E90">
-        <v>6579.659010987969</v>
+        <v>6727.112426738971</v>
       </c>
       <c r="F90">
-        <v>12975.90058608824</v>
+        <v>13123.35400183924</v>
       </c>
       <c r="G90">
         <v>1291.1</v>
@@ -8786,37 +8786,37 @@
         <v>1122.12</v>
       </c>
       <c r="M90">
-        <v>2605.560837686518</v>
+        <v>2635.169483569319</v>
       </c>
       <c r="N90">
-        <v>-1483.440837686518</v>
+        <v>-1513.049483569319</v>
       </c>
       <c r="O90">
-        <v>-382.7277361231217</v>
+        <v>-390.3667667608844</v>
       </c>
       <c r="P90">
-        <v>-1100.713101563396</v>
+        <v>-1122.682716808435</v>
       </c>
       <c r="Q90">
-        <v>-783.5131015633963</v>
+        <v>-805.482716808435</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2462810282745197</v>
+        <v>0.2645065762994761</v>
       </c>
       <c r="T90">
-        <v>4.630046842367662</v>
+        <v>5.050960191673814</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1111111879686731</v>
+        <v>0.1098627476544183</v>
       </c>
       <c r="W90">
-        <v>0.1784888734558905</v>
+        <v>0.1787395602709928</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4306635192584227</v>
+        <v>0.4258246033116989</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.188173932034126</v>
+        <v>0.189723932034126</v>
       </c>
       <c r="C91">
-        <v>-9652.99215381973</v>
+        <v>-9823.915299842063</v>
       </c>
       <c r="D91">
-        <v>2179.261848019509</v>
+        <v>2155.792117748179</v>
       </c>
       <c r="E91">
-        <v>6727.112426738971</v>
+        <v>6874.565842489974</v>
       </c>
       <c r="F91">
-        <v>13123.35400183924</v>
+        <v>13270.80741759024</v>
       </c>
       <c r="G91">
         <v>1291.1</v>
@@ -8868,37 +8868,37 @@
         <v>1122.12</v>
       </c>
       <c r="M91">
-        <v>2635.169483569319</v>
+        <v>2664.778129452121</v>
       </c>
       <c r="N91">
-        <v>-1513.049483569319</v>
+        <v>-1542.658129452121</v>
       </c>
       <c r="O91">
-        <v>-390.3667667608844</v>
+        <v>-398.0057973986471</v>
       </c>
       <c r="P91">
-        <v>-1122.682716808435</v>
+        <v>-1144.652332053473</v>
       </c>
       <c r="Q91">
-        <v>-805.482716808435</v>
+        <v>-827.4523320534734</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2645065762994761</v>
+        <v>0.2863772339294237</v>
       </c>
       <c r="T91">
-        <v>5.050960191673814</v>
+        <v>5.556056210841195</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1098627476544183</v>
+        <v>0.1086420504582581</v>
       </c>
       <c r="W91">
-        <v>0.1787395602709928</v>
+        <v>0.1789846762679818</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4258246033116989</v>
+        <v>0.4210932188304578</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.189723932034126</v>
+        <v>0.191273932034126</v>
       </c>
       <c r="C92">
-        <v>-9823.915299842063</v>
+        <v>-9994.338313896944</v>
       </c>
       <c r="D92">
-        <v>2155.792117748179</v>
+        <v>2132.8225194443</v>
       </c>
       <c r="E92">
-        <v>6874.565842489974</v>
+        <v>7022.019258240976</v>
       </c>
       <c r="F92">
-        <v>13270.80741759024</v>
+        <v>13418.26083334124</v>
       </c>
       <c r="G92">
         <v>1291.1</v>
@@ -8950,37 +8950,37 @@
         <v>1122.12</v>
       </c>
       <c r="M92">
-        <v>2664.778129452121</v>
+        <v>2694.386775334922</v>
       </c>
       <c r="N92">
-        <v>-1542.658129452121</v>
+        <v>-1572.266775334922</v>
       </c>
       <c r="O92">
-        <v>-398.0057973986471</v>
+        <v>-405.6448280364099</v>
       </c>
       <c r="P92">
-        <v>-1144.652332053473</v>
+        <v>-1166.621947298512</v>
       </c>
       <c r="Q92">
-        <v>-827.4523320534734</v>
+        <v>-849.4219472985121</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2863772339294237</v>
+        <v>0.3131080376993597</v>
       </c>
       <c r="T92">
-        <v>5.556056210841195</v>
+        <v>6.17339578982355</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1086420504582581</v>
+        <v>0.1074481817719036</v>
       </c>
       <c r="W92">
-        <v>0.1789846762679818</v>
+        <v>0.1792244051002018</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4210932188304578</v>
+        <v>0.4164658208213319</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.191273932034126</v>
+        <v>0.192823932034126</v>
       </c>
       <c r="C93">
-        <v>-9994.338313896944</v>
+        <v>-10164.27701391018</v>
       </c>
       <c r="D93">
-        <v>2132.8225194443</v>
+        <v>2110.337235182066</v>
       </c>
       <c r="E93">
-        <v>7022.019258240976</v>
+        <v>7169.472673991979</v>
       </c>
       <c r="F93">
-        <v>13418.26083334124</v>
+        <v>13565.71424909225</v>
       </c>
       <c r="G93">
         <v>1291.1</v>
@@ -9032,37 +9032,37 @@
         <v>1122.12</v>
       </c>
       <c r="M93">
-        <v>2694.386775334922</v>
+        <v>2723.995421217723</v>
       </c>
       <c r="N93">
-        <v>-1572.266775334922</v>
+        <v>-1601.875421217723</v>
       </c>
       <c r="O93">
-        <v>-405.6448280364099</v>
+        <v>-413.2838586741726</v>
       </c>
       <c r="P93">
-        <v>-1166.621947298512</v>
+        <v>-1188.59156254355</v>
       </c>
       <c r="Q93">
-        <v>-849.4219472985121</v>
+        <v>-871.3915625435504</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3131080376993597</v>
+        <v>0.3465215424117797</v>
       </c>
       <c r="T93">
-        <v>6.17339578982355</v>
+        <v>6.945070263551496</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1074481817719036</v>
+        <v>0.1062802667526438</v>
       </c>
       <c r="W93">
-        <v>0.1792244051002018</v>
+        <v>0.1794589224360691</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4164658208213319</v>
+        <v>0.4119390184211</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.192823932034126</v>
+        <v>0.194373932034126</v>
       </c>
       <c r="C94">
-        <v>-10164.27701391018</v>
+        <v>-10333.74655772449</v>
       </c>
       <c r="D94">
-        <v>2110.337235182066</v>
+        <v>2088.321107118759</v>
       </c>
       <c r="E94">
-        <v>7169.472673991979</v>
+        <v>7316.926089742983</v>
       </c>
       <c r="F94">
-        <v>13565.71424909225</v>
+        <v>13713.16766484325</v>
       </c>
       <c r="G94">
         <v>1291.1</v>
@@ -9114,37 +9114,37 @@
         <v>1122.12</v>
       </c>
       <c r="M94">
-        <v>2723.995421217723</v>
+        <v>2753.604067100525</v>
       </c>
       <c r="N94">
-        <v>-1601.875421217723</v>
+        <v>-1631.484067100525</v>
       </c>
       <c r="O94">
-        <v>-413.2838586741726</v>
+        <v>-420.9228893119354</v>
       </c>
       <c r="P94">
-        <v>-1188.59156254355</v>
+        <v>-1210.561177788589</v>
       </c>
       <c r="Q94">
-        <v>-871.3915625435504</v>
+        <v>-893.3611777885894</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3465215424117797</v>
+        <v>0.3894817627563197</v>
       </c>
       <c r="T94">
-        <v>6.945070263551496</v>
+        <v>7.937223158344568</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1062802667526438</v>
+        <v>0.1051374681854111</v>
       </c>
       <c r="W94">
-        <v>0.1794589224360691</v>
+        <v>0.1796883963883695</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4119390184211</v>
+        <v>0.4075095666101204</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.194373932034126</v>
+        <v>0.1959239320341259</v>
       </c>
       <c r="C95">
-        <v>-10333.74655772449</v>
+        <v>-10502.76147717564</v>
       </c>
       <c r="D95">
-        <v>2088.321107118759</v>
+        <v>2066.759603418615</v>
       </c>
       <c r="E95">
-        <v>7316.926089742983</v>
+        <v>7464.379505493986</v>
       </c>
       <c r="F95">
-        <v>13713.16766484325</v>
+        <v>13860.62108059425</v>
       </c>
       <c r="G95">
         <v>1291.1</v>
@@ -9196,37 +9196,37 @@
         <v>1122.12</v>
       </c>
       <c r="M95">
-        <v>2753.604067100525</v>
+        <v>2783.212712983326</v>
       </c>
       <c r="N95">
-        <v>-1631.484067100525</v>
+        <v>-1661.092712983326</v>
       </c>
       <c r="O95">
-        <v>-420.9228893119354</v>
+        <v>-428.5619199496982</v>
       </c>
       <c r="P95">
-        <v>-1210.561177788589</v>
+        <v>-1232.530793033628</v>
       </c>
       <c r="Q95">
-        <v>-893.3611777885894</v>
+        <v>-915.330793033628</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3894817627563197</v>
+        <v>0.4467620565490398</v>
       </c>
       <c r="T95">
-        <v>7.937223158344568</v>
+        <v>9.260093684735331</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1051374681854111</v>
+        <v>0.104018984481311</v>
       </c>
       <c r="W95">
-        <v>0.1796883963883695</v>
+        <v>0.1799129879161528</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4075095666101204</v>
+        <v>0.4031743584546936</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1959239320341259</v>
+        <v>0.197473932034126</v>
       </c>
       <c r="C96">
-        <v>-10502.76147717564</v>
+        <v>-10671.33571007918</v>
       </c>
       <c r="D96">
-        <v>2066.759603418615</v>
+        <v>2045.63878626608</v>
       </c>
       <c r="E96">
-        <v>7464.379505493986</v>
+        <v>7611.832921244988</v>
       </c>
       <c r="F96">
-        <v>13860.62108059425</v>
+        <v>14008.07449634526</v>
       </c>
       <c r="G96">
         <v>1291.1</v>
@@ -9278,37 +9278,37 @@
         <v>1122.12</v>
       </c>
       <c r="M96">
-        <v>2783.212712983326</v>
+        <v>2812.821358866127</v>
       </c>
       <c r="N96">
-        <v>-1661.092712983326</v>
+        <v>-1690.701358866128</v>
       </c>
       <c r="O96">
-        <v>-428.5619199496982</v>
+        <v>-436.2009505874609</v>
       </c>
       <c r="P96">
-        <v>-1232.530793033628</v>
+        <v>-1254.500408278667</v>
       </c>
       <c r="Q96">
-        <v>-915.330793033628</v>
+        <v>-937.3004082786665</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4467620565490398</v>
+        <v>0.526954467858848</v>
       </c>
       <c r="T96">
-        <v>9.260093684735331</v>
+        <v>11.1121124216824</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.104018984481311</v>
+        <v>0.1029240478025603</v>
       </c>
       <c r="W96">
-        <v>0.1799129879161528</v>
+        <v>0.1801328512012459</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4031743584546936</v>
+        <v>0.3989304178393811</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.197473932034126</v>
+        <v>0.1990239320341259</v>
       </c>
       <c r="C97">
-        <v>-10671.33571007918</v>
+        <v>-10839.48263027572</v>
       </c>
       <c r="D97">
-        <v>2045.63878626608</v>
+        <v>2024.945281820533</v>
       </c>
       <c r="E97">
-        <v>7611.832921244988</v>
+        <v>7759.28633699599</v>
       </c>
       <c r="F97">
-        <v>14008.07449634526</v>
+        <v>14155.52791209626</v>
       </c>
       <c r="G97">
         <v>1291.1</v>
@@ -9360,37 +9360,37 @@
         <v>1122.12</v>
       </c>
       <c r="M97">
-        <v>2812.821358866127</v>
+        <v>2842.430004748929</v>
       </c>
       <c r="N97">
-        <v>-1690.701358866128</v>
+        <v>-1720.310004748929</v>
       </c>
       <c r="O97">
-        <v>-436.2009505874609</v>
+        <v>-443.8399812252237</v>
       </c>
       <c r="P97">
-        <v>-1254.500408278667</v>
+        <v>-1276.470023523705</v>
       </c>
       <c r="Q97">
-        <v>-937.3004082786665</v>
+        <v>-959.270023523705</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.526954467858848</v>
+        <v>0.6472430848235602</v>
       </c>
       <c r="T97">
-        <v>11.1121124216824</v>
+        <v>13.89014052710301</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1029240478025603</v>
+        <v>0.101851922304617</v>
       </c>
       <c r="W97">
-        <v>0.1801328512012459</v>
+        <v>0.1803481340012329</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3989304178393811</v>
+        <v>0.3947748926535543</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1990239320341259</v>
+        <v>0.200573932034126</v>
       </c>
       <c r="C98">
-        <v>-10839.48263027572</v>
+        <v>-11007.21507587091</v>
       </c>
       <c r="D98">
-        <v>2024.945281820533</v>
+        <v>2004.666251976348</v>
       </c>
       <c r="E98">
-        <v>7759.286336995989</v>
+        <v>7906.739752746991</v>
       </c>
       <c r="F98">
-        <v>14155.52791209626</v>
+        <v>14302.98132784726</v>
       </c>
       <c r="G98">
         <v>1291.1</v>
@@ -9442,37 +9442,37 @@
         <v>1122.12</v>
       </c>
       <c r="M98">
-        <v>2842.430004748928</v>
+        <v>2872.03865063173</v>
       </c>
       <c r="N98">
-        <v>-1720.310004748928</v>
+        <v>-1749.91865063173</v>
       </c>
       <c r="O98">
-        <v>-443.8399812252235</v>
+        <v>-451.4790118629864</v>
       </c>
       <c r="P98">
-        <v>-1276.470023523705</v>
+        <v>-1298.439638768744</v>
       </c>
       <c r="Q98">
-        <v>-959.2700235237048</v>
+        <v>-981.2396387687436</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6472430848235586</v>
+        <v>0.8477241130980783</v>
       </c>
       <c r="T98">
-        <v>13.89014052710297</v>
+        <v>18.52018736947063</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.101851922304617</v>
+        <v>0.1008019024870436</v>
       </c>
       <c r="W98">
-        <v>0.1803481340012329</v>
+        <v>0.1805589779806017</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3947748926535543</v>
+        <v>0.3907050483993939</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.200573932034126</v>
+        <v>0.202123932034126</v>
       </c>
       <c r="C99">
-        <v>-11007.21507587091</v>
+        <v>-11174.54537579525</v>
       </c>
       <c r="D99">
-        <v>2004.666251976348</v>
+        <v>1984.789367803009</v>
       </c>
       <c r="E99">
-        <v>7906.739752746991</v>
+        <v>8054.193168497995</v>
       </c>
       <c r="F99">
-        <v>14302.98132784726</v>
+        <v>14450.43474359826</v>
       </c>
       <c r="G99">
         <v>1291.1</v>
@@ -9524,37 +9524,37 @@
         <v>1122.12</v>
       </c>
       <c r="M99">
-        <v>2872.03865063173</v>
+        <v>2901.647296514531</v>
       </c>
       <c r="N99">
-        <v>-1749.91865063173</v>
+        <v>-1779.527296514531</v>
       </c>
       <c r="O99">
-        <v>-451.4790118629864</v>
+        <v>-459.1180425007491</v>
       </c>
       <c r="P99">
-        <v>-1298.439638768744</v>
+        <v>-1320.409254013782</v>
       </c>
       <c r="Q99">
-        <v>-981.2396387687436</v>
+        <v>-1003.209254013782</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8477241130980783</v>
+        <v>1.248686169647117</v>
       </c>
       <c r="T99">
-        <v>18.52018736947063</v>
+        <v>27.78028105420595</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1008019024870436</v>
+        <v>0.09977331164533909</v>
       </c>
       <c r="W99">
-        <v>0.1805589779806017</v>
+        <v>0.1807655190216159</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3907050483993939</v>
+        <v>0.3867182621912368</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.202123932034126</v>
+        <v>0.203673932034126</v>
       </c>
       <c r="C100">
-        <v>-11174.54537579525</v>
+        <v>-11341.48537479947</v>
       </c>
       <c r="D100">
-        <v>1984.789367803009</v>
+        <v>1965.302784549798</v>
       </c>
       <c r="E100">
-        <v>8054.193168497995</v>
+        <v>8201.646584248998</v>
       </c>
       <c r="F100">
-        <v>14450.43474359826</v>
+        <v>14597.88815934927</v>
       </c>
       <c r="G100">
         <v>1291.1</v>
@@ -9606,37 +9606,37 @@
         <v>1122.12</v>
       </c>
       <c r="M100">
-        <v>2901.647296514531</v>
+        <v>2931.255942397333</v>
       </c>
       <c r="N100">
-        <v>-1779.527296514531</v>
+        <v>-1809.135942397333</v>
       </c>
       <c r="O100">
-        <v>-459.1180425007491</v>
+        <v>-466.7570731385118</v>
       </c>
       <c r="P100">
-        <v>-1320.409254013782</v>
+        <v>-1342.378869258821</v>
       </c>
       <c r="Q100">
-        <v>-1003.209254013782</v>
+        <v>-1025.178869258821</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.248686169647117</v>
+        <v>2.451572339294235</v>
       </c>
       <c r="T100">
-        <v>27.78028105420595</v>
+        <v>55.56056210841189</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09977331164533909</v>
+        <v>0.09876550041659829</v>
       </c>
       <c r="W100">
-        <v>0.1807655190216159</v>
+        <v>0.1809678875163471</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3867182621912368</v>
+        <v>0.382812017118598</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.203673932034126</v>
-      </c>
-      <c r="C101">
-        <v>-11341.48537479947</v>
-      </c>
-      <c r="D101">
-        <v>1965.302784549798</v>
-      </c>
-      <c r="E101">
-        <v>8201.646584248998</v>
-      </c>
-      <c r="F101">
-        <v>14597.88815934927</v>
-      </c>
-      <c r="G101">
-        <v>1291.1</v>
-      </c>
-      <c r="H101">
-        <v>8349.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1439.32</v>
-      </c>
-      <c r="K101">
-        <v>317.2</v>
-      </c>
-      <c r="L101">
-        <v>1122.12</v>
-      </c>
-      <c r="M101">
-        <v>2931.255942397333</v>
-      </c>
-      <c r="N101">
-        <v>-1809.135942397333</v>
-      </c>
-      <c r="O101">
-        <v>-466.7570731385118</v>
-      </c>
-      <c r="P101">
-        <v>-1342.378869258821</v>
-      </c>
-      <c r="Q101">
-        <v>-1025.178869258821</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.451572339294235</v>
-      </c>
-      <c r="T101">
-        <v>55.56056210841189</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09876550041659829</v>
-      </c>
-      <c r="W101">
-        <v>0.1809678875163471</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.382812017118598</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
